--- a/research/traditional_assets/database/data/france/france_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/france/france_telecom_services.xlsx
@@ -650,10 +650,10 @@
         <v>0.07464350546634681</v>
       </c>
       <c r="X2">
-        <v>0.1091118662209753</v>
+        <v>0.1090822989552619</v>
       </c>
       <c r="Y2">
-        <v>-0.03446836075462846</v>
+        <v>-0.03443879348891514</v>
       </c>
       <c r="Z2">
         <v>0.9117031175935671</v>
@@ -662,10 +662,10 @@
         <v>0.09315177902887165</v>
       </c>
       <c r="AB2">
-        <v>0.06939752568770874</v>
+        <v>0.06938678869279742</v>
       </c>
       <c r="AC2">
-        <v>0.02375425334116291</v>
+        <v>0.02376499033607422</v>
       </c>
       <c r="AD2">
         <v>46258.4</v>
@@ -787,10 +787,10 @@
         <v>0.07464350546634681</v>
       </c>
       <c r="X3">
-        <v>0.1091118662209753</v>
+        <v>0.1090822989552619</v>
       </c>
       <c r="Y3">
-        <v>-0.03446836075462846</v>
+        <v>-0.03443879348891514</v>
       </c>
       <c r="Z3">
         <v>0.9117031175935671</v>
@@ -799,10 +799,10 @@
         <v>0.09315177902887165</v>
       </c>
       <c r="AB3">
-        <v>0.06939752568770874</v>
+        <v>0.06938678869279742</v>
       </c>
       <c r="AC3">
-        <v>0.02375425334116291</v>
+        <v>0.02376499033607422</v>
       </c>
       <c r="AD3">
         <v>46258.4</v>
@@ -1139,49 +1139,49 @@
         <v>3.19728372811534</v>
       </c>
       <c r="F2">
-        <v>3.04698610729749</v>
+        <v>3.00466091659536</v>
       </c>
       <c r="G2">
         <v>3.21084880168028</v>
       </c>
       <c r="H2">
-        <v>1.76458465409058</v>
+        <v>1.86541806289576</v>
       </c>
       <c r="I2">
         <v>0.6368620955548721</v>
       </c>
       <c r="J2">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="K2">
         <v>26496.2</v>
       </c>
       <c r="L2">
-        <v>45822.9217081883</v>
+        <v>44983.9572885469</v>
       </c>
       <c r="M2">
         <v>64234.2671125575</v>
       </c>
       <c r="N2">
-        <v>62630.2201975834</v>
+        <v>63250.5471201932</v>
       </c>
       <c r="O2">
         <v>46468.3671125575</v>
       </c>
       <c r="P2">
-        <v>25537.5984893951</v>
+        <v>26996.8898316463</v>
       </c>
       <c r="Q2">
-        <v>0.0693975256877087</v>
+        <v>0.06938678869279739</v>
       </c>
       <c r="R2">
-        <v>0.07147908459676069</v>
+        <v>0.0706508217422832</v>
       </c>
       <c r="S2">
         <v>0.0467524624969006</v>
       </c>
       <c r="T2">
-        <v>0.0478774624969006</v>
+        <v>0.0459274624969006</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.109111866220975</v>
+        <v>0.109082298955262</v>
       </c>
       <c r="X2">
-        <v>0.0841876503428392</v>
+        <v>0.08517088987052369</v>
       </c>
       <c r="Y2">
         <v>1.23348979391916</v>
       </c>
       <c r="Z2">
-        <v>0.747897317465934</v>
+        <v>0.767411924575287</v>
       </c>
       <c r="AA2">
         <v>46258.4</v>
@@ -1236,7 +1236,7 @@
         <v>26496.2</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963756</v>
+        <v>0.05130346377183671</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.0731446276414745</v>
+        <v>0.07313185743077678</v>
       </c>
       <c r="C2">
-        <v>70133.61981952583</v>
+        <v>70135.06109867145</v>
       </c>
       <c r="D2">
-        <v>61403.31981952584</v>
+        <v>61404.76109867144</v>
       </c>
       <c r="E2">
         <v>-46468.36711255749</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.0731446276414745</v>
+        <v>0.07313185743077678</v>
       </c>
       <c r="T2">
         <v>0.532748774085323</v>
       </c>
       <c r="U2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V2">
         <v>0.25</v>
       </c>
       <c r="W2">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.07305054069733981</v>
+        <v>0.07302730241216886</v>
       </c>
       <c r="C3">
-        <v>69471.99962315589</v>
+        <v>69481.02301867792</v>
       </c>
       <c r="D3">
-        <v>61471.34529428146</v>
+        <v>61480.36868980349</v>
       </c>
       <c r="E3">
         <v>-45738.72144143192</v>
@@ -1539,37 +1539,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M3">
-        <v>42.05430784614219</v>
+        <v>41.03280390656639</v>
       </c>
       <c r="N3">
-        <v>4925.245692153857</v>
+        <v>4926.267196093433</v>
       </c>
       <c r="O3">
-        <v>1231.311423038464</v>
+        <v>1231.566799023358</v>
       </c>
       <c r="P3">
-        <v>3693.934269115392</v>
+        <v>3694.700397070075</v>
       </c>
       <c r="Q3">
-        <v>13198.93426911539</v>
+        <v>13199.70039707008</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.07335178391148567</v>
+        <v>0.07333891695676753</v>
       </c>
       <c r="T3">
         <v>0.5367847496465754</v>
       </c>
       <c r="U3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V3">
         <v>0.25</v>
       </c>
       <c r="W3">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>118.1163180279442</v>
+        <v>121.0568015607896</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07295645375320513</v>
+        <v>0.07292274739356092</v>
       </c>
       <c r="C4">
-        <v>68810.53031756636</v>
+        <v>68827.17135925309</v>
       </c>
       <c r="D4">
-        <v>61539.52165981751</v>
+        <v>61556.16270150424</v>
       </c>
       <c r="E4">
         <v>-45009.07577030634</v>
@@ -1621,37 +1621,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M4">
-        <v>84.10861569228437</v>
+        <v>82.06560781313277</v>
       </c>
       <c r="N4">
-        <v>4883.191384307715</v>
+        <v>4885.234392186867</v>
       </c>
       <c r="O4">
-        <v>1220.797846076929</v>
+        <v>1221.308598046717</v>
       </c>
       <c r="P4">
-        <v>3662.393538230786</v>
+        <v>3663.92579414015</v>
       </c>
       <c r="Q4">
-        <v>13167.39353823079</v>
+        <v>13168.92579414015</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07356316786047666</v>
+        <v>0.07355020218737031</v>
       </c>
       <c r="T4">
         <v>0.5409030920560167</v>
       </c>
       <c r="U4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V4">
         <v>0.25</v>
       </c>
       <c r="W4">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>59.05815901397209</v>
+        <v>60.5284007803948</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.07286236680907045</v>
+        <v>0.07281819237495298</v>
       </c>
       <c r="C5">
-        <v>68149.21240536252</v>
+        <v>68173.50681071503</v>
       </c>
       <c r="D5">
-        <v>61607.84941873924</v>
+        <v>61632.14382409175</v>
       </c>
       <c r="E5">
         <v>-44279.43009918077</v>
@@ -1703,37 +1703,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M5">
-        <v>126.1629235384266</v>
+        <v>123.0984117196991</v>
       </c>
       <c r="N5">
-        <v>4841.137076461573</v>
+        <v>4844.2015882803</v>
       </c>
       <c r="O5">
-        <v>1210.284269115393</v>
+        <v>1211.050397070075</v>
       </c>
       <c r="P5">
-        <v>3630.85280734618</v>
+        <v>3633.151191210225</v>
       </c>
       <c r="Q5">
-        <v>13135.85280734618</v>
+        <v>13138.15119121023</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07377891024140561</v>
+        <v>0.07376584381448037</v>
       </c>
       <c r="T5">
         <v>0.5451063487419412</v>
       </c>
       <c r="U5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>39.37210600931473</v>
+        <v>40.35226718692987</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.07276827986493578</v>
+        <v>0.07271363735634505</v>
       </c>
       <c r="C6">
-        <v>67488.04639138424</v>
+        <v>67520.03006679435</v>
       </c>
       <c r="D6">
-        <v>61676.32907588653</v>
+        <v>61708.31275129665</v>
       </c>
       <c r="E6">
         <v>-43549.78442805519</v>
@@ -1785,37 +1785,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M6">
-        <v>168.2172313845687</v>
+        <v>164.1312156262655</v>
       </c>
       <c r="N6">
-        <v>4799.082768615431</v>
+        <v>4803.168784373734</v>
       </c>
       <c r="O6">
-        <v>1199.770692153858</v>
+        <v>1200.792196093433</v>
       </c>
       <c r="P6">
-        <v>3599.312076461573</v>
+        <v>3602.3765882803</v>
       </c>
       <c r="Q6">
-        <v>13104.31207646157</v>
+        <v>13107.3765882803</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07399914725527058</v>
+        <v>0.07398597797548856</v>
       </c>
       <c r="T6">
         <v>0.5493971732754893</v>
       </c>
       <c r="U6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.52907950698605</v>
+        <v>30.2642003901974</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.0726741929208011</v>
+        <v>0.07260908233773712</v>
       </c>
       <c r="C7">
-        <v>66827.03278271858</v>
+        <v>66866.74182465539</v>
       </c>
       <c r="D7">
-        <v>61744.96113834646</v>
+        <v>61784.67018028326</v>
       </c>
       <c r="E7">
         <v>-42820.13875692962</v>
@@ -1867,37 +1867,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M7">
-        <v>210.2715392307109</v>
+        <v>205.1640195328319</v>
       </c>
       <c r="N7">
-        <v>4757.028460769288</v>
+        <v>4762.135980467167</v>
       </c>
       <c r="O7">
-        <v>1189.257115192322</v>
+        <v>1190.533995116792</v>
       </c>
       <c r="P7">
-        <v>3567.771345576966</v>
+        <v>3571.601985350376</v>
       </c>
       <c r="Q7">
-        <v>13072.77134557697</v>
+        <v>13076.60198535037</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.0742240208378485</v>
+        <v>0.07421074653988641</v>
       </c>
       <c r="T7">
         <v>0.553778330957112</v>
       </c>
       <c r="U7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.62326360558884</v>
+        <v>24.21136031215793</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.07258010597666642</v>
+        <v>0.07250452731912915</v>
       </c>
       <c r="C8">
-        <v>66166.17208871216</v>
+        <v>66213.64278491742</v>
       </c>
       <c r="D8">
-        <v>61813.7461154656</v>
+        <v>61861.21681167086</v>
       </c>
       <c r="E8">
         <v>-42090.49308580404</v>
@@ -1949,37 +1949,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M8">
-        <v>252.3258470768531</v>
+        <v>246.1968234393983</v>
       </c>
       <c r="N8">
-        <v>4714.974152923146</v>
+        <v>4721.103176560601</v>
       </c>
       <c r="O8">
-        <v>1178.743538230786</v>
+        <v>1180.27579414015</v>
       </c>
       <c r="P8">
-        <v>3536.230614692359</v>
+        <v>3540.827382420451</v>
       </c>
       <c r="Q8">
-        <v>13041.23061469236</v>
+        <v>13045.82738242045</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07445367896473658</v>
+        <v>0.07444029741416504</v>
       </c>
       <c r="T8">
         <v>0.5582527047596203</v>
       </c>
       <c r="U8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V8">
         <v>0.25</v>
       </c>
       <c r="W8">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.68605300465737</v>
+        <v>20.17613359346494</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.07248601903253174</v>
+        <v>0.07239997230052123</v>
       </c>
       <c r="C9">
-        <v>65505.46482098381</v>
+        <v>65560.733651676</v>
       </c>
       <c r="D9">
-        <v>61882.68451886284</v>
+        <v>61937.95334955502</v>
       </c>
       <c r="E9">
         <v>-41360.84741467846</v>
@@ -2031,37 +2031,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M9">
-        <v>294.3801549229953</v>
+        <v>287.2296273459647</v>
       </c>
       <c r="N9">
-        <v>4672.919845077004</v>
+        <v>4680.070372654034</v>
       </c>
       <c r="O9">
-        <v>1168.229961269251</v>
+        <v>1170.017593163509</v>
       </c>
       <c r="P9">
-        <v>3504.689883807753</v>
+        <v>3510.052779490526</v>
       </c>
       <c r="Q9">
-        <v>13009.68988380775</v>
+        <v>13015.05277949052</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07468827597607387</v>
+        <v>0.07467478486638515</v>
       </c>
       <c r="T9">
         <v>0.5628233016546557</v>
       </c>
       <c r="U9">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.87375971827774</v>
+        <v>17.29382879439851</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.07239193208839706</v>
+        <v>0.0722954172819133</v>
       </c>
       <c r="C10">
-        <v>64844.9114934373</v>
+        <v>64908.01513252472</v>
       </c>
       <c r="D10">
-        <v>61951.7768624419</v>
+        <v>62014.88050152932</v>
       </c>
       <c r="E10">
         <v>-40631.20174355289</v>
@@ -2113,37 +2113,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M10">
-        <v>336.4344627691375</v>
+        <v>328.2624312525311</v>
       </c>
       <c r="N10">
-        <v>4630.865537230862</v>
+        <v>4639.037568747468</v>
       </c>
       <c r="O10">
-        <v>1157.716384307716</v>
+        <v>1159.759392186867</v>
       </c>
       <c r="P10">
-        <v>3473.149152923147</v>
+        <v>3479.278176560601</v>
       </c>
       <c r="Q10">
-        <v>12978.14915292315</v>
+        <v>12984.2781765606</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07492797292244023</v>
+        <v>0.07491436987191441</v>
       </c>
       <c r="T10">
         <v>0.5674932593517571</v>
       </c>
       <c r="U10">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V10">
         <v>0.25</v>
       </c>
       <c r="W10">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.76453975349303</v>
+        <v>15.1321001950987</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.07229784514426237</v>
+        <v>0.07219086226330536</v>
       </c>
       <c r="C11">
-        <v>64184.51262227403</v>
+        <v>64255.48793857689</v>
       </c>
       <c r="D11">
-        <v>62021.0236624042</v>
+        <v>62091.99897870707</v>
       </c>
       <c r="E11">
         <v>-39901.55607242732</v>
@@ -2195,37 +2195,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M11">
-        <v>378.4887706152796</v>
+        <v>369.2952351590974</v>
       </c>
       <c r="N11">
-        <v>4588.81122938472</v>
+        <v>4598.004764840902</v>
       </c>
       <c r="O11">
-        <v>1147.20280734618</v>
+        <v>1149.501191210225</v>
       </c>
       <c r="P11">
-        <v>3441.60842203854</v>
+        <v>3448.503573630676</v>
       </c>
       <c r="Q11">
-        <v>12946.60842203854</v>
+        <v>12953.50357363068</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07517293793356189</v>
+        <v>0.07515922048196078</v>
       </c>
       <c r="T11">
         <v>0.5722658534817617</v>
       </c>
       <c r="U11">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>13.12403533643825</v>
+        <v>13.45075572897663</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.0722037582001277</v>
+        <v>0.07208630724469743</v>
       </c>
       <c r="C12">
-        <v>63524.26872600592</v>
+        <v>63603.15278448737</v>
       </c>
       <c r="D12">
-        <v>62090.42543726167</v>
+        <v>62169.30949574312</v>
       </c>
       <c r="E12">
         <v>-39171.91040130174</v>
@@ -2277,37 +2277,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M12">
-        <v>420.5430784614218</v>
+        <v>410.3280390656638</v>
       </c>
       <c r="N12">
-        <v>4546.756921538577</v>
+        <v>4556.971960934336</v>
       </c>
       <c r="O12">
-        <v>1136.689230384644</v>
+        <v>1139.242990233584</v>
       </c>
       <c r="P12">
-        <v>3410.067691153933</v>
+        <v>3417.728970700752</v>
       </c>
       <c r="Q12">
-        <v>12915.06769115393</v>
+        <v>12922.72897070075</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.07542334661159737</v>
+        <v>0.07540951221667486</v>
       </c>
       <c r="T12">
         <v>0.5771445052590998</v>
       </c>
       <c r="U12">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.81163180279442</v>
+        <v>12.10568015607896</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.07210967125599302</v>
+        <v>0.07198175222608949</v>
       </c>
       <c r="C13">
-        <v>62864.18032546841</v>
+        <v>62951.0103884748</v>
       </c>
       <c r="D13">
-        <v>62159.98270784974</v>
+        <v>62246.81277085612</v>
       </c>
       <c r="E13">
         <v>-38442.26473017617</v>
@@ -2359,37 +2359,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M13">
-        <v>462.597386307564</v>
+        <v>451.3608429722302</v>
       </c>
       <c r="N13">
-        <v>4504.702613692435</v>
+        <v>4515.939157027769</v>
       </c>
       <c r="O13">
-        <v>1126.175653423109</v>
+        <v>1128.984789256942</v>
       </c>
       <c r="P13">
-        <v>3378.526960269326</v>
+        <v>3386.954367770827</v>
       </c>
       <c r="Q13">
-        <v>12883.52696026933</v>
+        <v>12891.95436777083</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07567938245093703</v>
+        <v>0.07566542848475329</v>
       </c>
       <c r="T13">
         <v>0.5821327896606479</v>
       </c>
       <c r="U13">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.73784709344947</v>
+        <v>11.0051637782536</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.07201558431185834</v>
+        <v>0.07187719720748155</v>
       </c>
       <c r="C14">
-        <v>62204.24794383342</v>
+        <v>62299.06147234367</v>
       </c>
       <c r="D14">
-        <v>62229.69599734031</v>
+        <v>62324.50952585057</v>
       </c>
       <c r="E14">
         <v>-37712.61905905059</v>
@@ -2441,37 +2441,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M14">
-        <v>504.6516941537062</v>
+        <v>492.3936468787966</v>
       </c>
       <c r="N14">
-        <v>4462.648305846293</v>
+        <v>4474.906353121202</v>
       </c>
       <c r="O14">
-        <v>1115.662076461573</v>
+        <v>1118.726588280301</v>
       </c>
       <c r="P14">
-        <v>3346.98622938472</v>
+        <v>3356.179764840902</v>
       </c>
       <c r="Q14">
-        <v>12851.98622938472</v>
+        <v>12861.1797648409</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.0759412372866253</v>
+        <v>0.07592716103165169</v>
       </c>
       <c r="T14">
         <v>0.587234444162231</v>
       </c>
       <c r="U14">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.843026502328682</v>
+        <v>10.08806679673247</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.07192149736772366</v>
+        <v>0.07177264218887362</v>
       </c>
       <c r="C15">
-        <v>61544.47210662242</v>
+        <v>61647.30676150685</v>
       </c>
       <c r="D15">
-        <v>62299.56583125489</v>
+        <v>62402.40048613933</v>
       </c>
       <c r="E15">
         <v>-36982.97338792502</v>
@@ -2523,37 +2523,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M15">
-        <v>546.7060019998484</v>
+        <v>533.4264507853629</v>
       </c>
       <c r="N15">
-        <v>4420.593998000151</v>
+        <v>4433.873549214636</v>
       </c>
       <c r="O15">
-        <v>1105.148499500038</v>
+        <v>1108.468387303659</v>
       </c>
       <c r="P15">
-        <v>3315.445498500113</v>
+        <v>3325.405161910977</v>
       </c>
       <c r="Q15">
-        <v>12820.44549850011</v>
+        <v>12830.40516191098</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07620911177370872</v>
+        <v>0.07619491041870867</v>
       </c>
       <c r="T15">
         <v>0.5924533780776436</v>
       </c>
       <c r="U15">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.04322746249690057</v>
+        <v>0.04217746249690058</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.085870617534171</v>
+        <v>9.312061658522278</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.07194291042358898</v>
+        <v>0.07182558717026569</v>
       </c>
       <c r="C16">
-        <v>60798.91111541314</v>
+        <v>60878.19404269052</v>
       </c>
       <c r="D16">
-        <v>62283.6505111712</v>
+        <v>62362.93343844858</v>
       </c>
       <c r="E16">
         <v>-36253.32771679944</v>
@@ -2605,37 +2605,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M16">
-        <v>599.9968531813245</v>
+        <v>589.7818137855664</v>
       </c>
       <c r="N16">
-        <v>4367.303146818675</v>
+        <v>4377.518186214433</v>
       </c>
       <c r="O16">
-        <v>1091.825786704669</v>
+        <v>1094.379546553608</v>
       </c>
       <c r="P16">
-        <v>3275.477360114006</v>
+        <v>3283.138639660825</v>
       </c>
       <c r="Q16">
-        <v>12780.47736011401</v>
+        <v>12788.13863966082</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07648321590002663</v>
+        <v>0.07646888653569721</v>
       </c>
       <c r="T16">
         <v>0.5977936825492287</v>
       </c>
       <c r="U16">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.278876753539965</v>
+        <v>8.422267156928672</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.07185707347945429</v>
+        <v>0.07173228215165774</v>
       </c>
       <c r="C17">
-        <v>60133.11310448957</v>
+        <v>60218.13477839353</v>
       </c>
       <c r="D17">
-        <v>62347.4981713732</v>
+        <v>62432.51984527717</v>
       </c>
       <c r="E17">
         <v>-35523.68204567386</v>
@@ -2687,37 +2687,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M17">
-        <v>642.8537712657047</v>
+        <v>631.9090861988211</v>
       </c>
       <c r="N17">
-        <v>4324.446228734295</v>
+        <v>4335.390913801179</v>
       </c>
       <c r="O17">
-        <v>1081.111557183574</v>
+        <v>1083.847728450295</v>
       </c>
       <c r="P17">
-        <v>3243.334671550721</v>
+        <v>3251.543185350884</v>
       </c>
       <c r="Q17">
-        <v>12748.33467155072</v>
+        <v>12756.54318535088</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07676376953519906</v>
+        <v>0.07674930914955606</v>
       </c>
       <c r="T17">
         <v>0.6032596412436745</v>
       </c>
       <c r="U17">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.726951636637303</v>
+        <v>7.860782679800097</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.07177123653531961</v>
+        <v>0.07163897713304981</v>
       </c>
       <c r="C18">
-        <v>59467.44612978039</v>
+        <v>59558.23098071523</v>
       </c>
       <c r="D18">
-        <v>62411.4768677896</v>
+        <v>62502.26171872443</v>
       </c>
       <c r="E18">
         <v>-34794.03637454829</v>
@@ -2769,37 +2769,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M18">
-        <v>685.7106893500851</v>
+        <v>674.0363586120759</v>
       </c>
       <c r="N18">
-        <v>4281.589310649914</v>
+        <v>4293.263641387924</v>
       </c>
       <c r="O18">
-        <v>1070.397327662479</v>
+        <v>1073.315910346981</v>
       </c>
       <c r="P18">
-        <v>3211.191982987436</v>
+        <v>3219.947731040943</v>
       </c>
       <c r="Q18">
-        <v>12716.19198298744</v>
+        <v>12724.94773104094</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.077051003018828</v>
+        <v>0.07703640849231633</v>
       </c>
       <c r="T18">
         <v>0.6088557418117976</v>
       </c>
       <c r="U18">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.244017159347471</v>
+        <v>7.369483762312591</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.07168539959118493</v>
+        <v>0.07154567211444186</v>
       </c>
       <c r="C19">
-        <v>58801.91059509355</v>
+        <v>58898.48317124242</v>
       </c>
       <c r="D19">
-        <v>62475.58700422833</v>
+        <v>62572.15958037719</v>
       </c>
       <c r="E19">
         <v>-34064.39070342272</v>
@@ -2851,37 +2851,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M19">
-        <v>728.5676074344653</v>
+        <v>716.1636310253306</v>
       </c>
       <c r="N19">
-        <v>4238.732392565534</v>
+        <v>4251.136368974669</v>
       </c>
       <c r="O19">
-        <v>1059.683098141383</v>
+        <v>1062.784092243667</v>
       </c>
       <c r="P19">
-        <v>3179.049294424151</v>
+        <v>3188.352276731001</v>
       </c>
       <c r="Q19">
-        <v>12684.04929442415</v>
+        <v>12693.352276731</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07734515779121909</v>
+        <v>0.07733042589152865</v>
       </c>
       <c r="T19">
         <v>0.6145866881767431</v>
       </c>
       <c r="U19">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.04405246249690057</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.817898502915266</v>
+        <v>6.935984717470673</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.07189656264705026</v>
+        <v>0.07168186709583393</v>
       </c>
       <c r="C20">
-        <v>57914.78681261468</v>
+        <v>58066.8617188387</v>
       </c>
       <c r="D20">
-        <v>62318.10889287503</v>
+        <v>62470.18379909905</v>
       </c>
       <c r="E20">
         <v>-33334.74503229714</v>
@@ -2933,37 +2933,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M20">
-        <v>800.3184940954184</v>
+        <v>780.6180609750279</v>
       </c>
       <c r="N20">
-        <v>4166.981505904581</v>
+        <v>4186.681939024971</v>
       </c>
       <c r="O20">
-        <v>1041.745376476145</v>
+        <v>1046.670484756243</v>
       </c>
       <c r="P20">
-        <v>3125.236129428436</v>
+        <v>3140.011454268728</v>
       </c>
       <c r="Q20">
-        <v>12630.23612942844</v>
+        <v>12645.01145426873</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07764648707025384</v>
+        <v>0.07763161444681931</v>
       </c>
       <c r="T20">
         <v>0.6204574137213212</v>
       </c>
       <c r="U20">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.206654021677238</v>
+        <v>6.363291151367434</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.07182722570291558</v>
+        <v>0.07160131207722602</v>
       </c>
       <c r="C21">
-        <v>57236.76262459038</v>
+        <v>57397.49129650288</v>
       </c>
       <c r="D21">
-        <v>62369.7303759763</v>
+        <v>62530.4590478888</v>
       </c>
       <c r="E21">
         <v>-32605.09936117157</v>
@@ -3015,37 +3015,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M21">
-        <v>844.7806326562751</v>
+        <v>823.9857310291961</v>
       </c>
       <c r="N21">
-        <v>4122.519367343724</v>
+        <v>4143.314268970803</v>
       </c>
       <c r="O21">
-        <v>1030.629841835931</v>
+        <v>1035.828567242701</v>
       </c>
       <c r="P21">
-        <v>3091.889525507793</v>
+        <v>3107.485701728102</v>
       </c>
       <c r="Q21">
-        <v>12596.88952550779</v>
+        <v>12612.4857017281</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07795525657840058</v>
+        <v>0.0779402397565616</v>
       </c>
       <c r="T21">
         <v>0.6264730954521854</v>
       </c>
       <c r="U21">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V21">
         <v>0.25</v>
       </c>
       <c r="W21">
-        <v>0.04570246249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.87998802053633</v>
+        <v>6.028381090769148</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.07198288875878088</v>
+        <v>0.07152075705861807</v>
       </c>
       <c r="C22">
-        <v>56391.34481994144</v>
+        <v>56728.23730137234</v>
       </c>
       <c r="D22">
-        <v>62253.95824245294</v>
+        <v>62590.85072388384</v>
       </c>
       <c r="E22">
         <v>-31875.45369004599</v>
@@ -3097,45 +3097,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M22">
-        <v>911.1321413508989</v>
+        <v>867.3534010833644</v>
       </c>
       <c r="N22">
-        <v>4056.1678586491</v>
+        <v>4099.946598916635</v>
       </c>
       <c r="O22">
-        <v>1014.041964662275</v>
+        <v>1024.986649729159</v>
       </c>
       <c r="P22">
-        <v>3042.125893986825</v>
+        <v>3074.959949187476</v>
       </c>
       <c r="Q22">
-        <v>12547.12589398683</v>
+        <v>12579.95994918748</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07827174532425096</v>
+        <v>0.07825658069904744</v>
       </c>
       <c r="T22">
         <v>0.632639169226321</v>
       </c>
       <c r="U22">
-        <v>0.0624366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.04682746249690058</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>5.451788796118183</v>
+        <v>5.726962036230691</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.07192480181464622</v>
+        <v>0.07156620204001013</v>
       </c>
       <c r="C23">
-        <v>55704.8501664886</v>
+        <v>55964.50743177069</v>
       </c>
       <c r="D23">
-        <v>62297.10926012568</v>
+        <v>62556.76652540777</v>
       </c>
       <c r="E23">
         <v>-31145.80801892042</v>
@@ -3179,37 +3179,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M23">
-        <v>956.6887484184438</v>
+        <v>922.9791184124422</v>
       </c>
       <c r="N23">
-        <v>4010.611251581556</v>
+        <v>4044.320881587557</v>
       </c>
       <c r="O23">
-        <v>1002.652812895389</v>
+        <v>1011.080220396889</v>
       </c>
       <c r="P23">
-        <v>3007.958438686167</v>
+        <v>3033.240661190668</v>
       </c>
       <c r="Q23">
-        <v>12512.95843868617</v>
+        <v>12538.24066119067</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07859624644341404</v>
+        <v>0.07858093027298861</v>
       </c>
       <c r="T23">
         <v>0.638961346133979</v>
       </c>
       <c r="U23">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.192179805826842</v>
+        <v>5.38181189683244</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.07186671487051154</v>
+        <v>0.07149164702140219</v>
       </c>
       <c r="C24">
-        <v>55018.41537434957</v>
+        <v>55290.79830555906</v>
       </c>
       <c r="D24">
-        <v>62340.32013911221</v>
+        <v>62612.70307032171</v>
       </c>
       <c r="E24">
         <v>-30416.16234779485</v>
@@ -3261,37 +3261,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M24">
-        <v>1002.245355485989</v>
+        <v>966.9305050035109</v>
       </c>
       <c r="N24">
-        <v>3965.054644514011</v>
+        <v>4000.369494996488</v>
       </c>
       <c r="O24">
-        <v>991.2636611285027</v>
+        <v>1000.092373749122</v>
       </c>
       <c r="P24">
-        <v>2973.790983385508</v>
+        <v>3000.277121247366</v>
       </c>
       <c r="Q24">
-        <v>12478.79098338551</v>
+        <v>12505.27712124737</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07892906810409411</v>
+        <v>0.07891359650267188</v>
       </c>
       <c r="T24">
         <v>0.6454456301418335</v>
       </c>
       <c r="U24">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.956171632834712</v>
+        <v>5.137184083340057</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.07180862792637685</v>
+        <v>0.07141709200279425</v>
       </c>
       <c r="C25">
-        <v>54332.04056817482</v>
+        <v>54617.18930272365</v>
       </c>
       <c r="D25">
-        <v>62383.59100406305</v>
+        <v>62668.73973861188</v>
       </c>
       <c r="E25">
         <v>-29686.51667666927</v>
@@ -3343,37 +3343,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M25">
-        <v>1047.801962553534</v>
+        <v>1010.88189159458</v>
       </c>
       <c r="N25">
-        <v>3919.498037446466</v>
+        <v>3956.41810840542</v>
       </c>
       <c r="O25">
-        <v>979.8745093616164</v>
+        <v>989.104527101355</v>
       </c>
       <c r="P25">
-        <v>2939.62352808485</v>
+        <v>2967.313581304065</v>
       </c>
       <c r="Q25">
-        <v>12444.62352808485</v>
+        <v>12472.31358130406</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.0792705344832334</v>
+        <v>0.07925490341364561</v>
       </c>
       <c r="T25">
         <v>0.652098337110931</v>
       </c>
       <c r="U25">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.740685909667985</v>
+        <v>4.913828253629619</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.07175054098224218</v>
+        <v>0.07134253698418633</v>
       </c>
       <c r="C26">
-        <v>53645.72587296121</v>
+        <v>53943.68069232834</v>
       </c>
       <c r="D26">
-        <v>62426.921979975</v>
+        <v>62724.87679934214</v>
       </c>
       <c r="E26">
         <v>-28956.87100554369</v>
@@ -3425,37 +3425,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M26">
-        <v>1093.358569621079</v>
+        <v>1054.833278185648</v>
       </c>
       <c r="N26">
-        <v>3873.941430378921</v>
+        <v>3912.466721814351</v>
       </c>
       <c r="O26">
-        <v>968.4853575947302</v>
+        <v>978.1166804535877</v>
       </c>
       <c r="P26">
-        <v>2905.456072784191</v>
+        <v>2934.350041360763</v>
       </c>
       <c r="Q26">
-        <v>12410.45607278419</v>
+        <v>12439.35004136076</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.07962098681971846</v>
+        <v>0.07960519208543446</v>
       </c>
       <c r="T26">
         <v>0.6589261153160574</v>
       </c>
       <c r="U26">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.543157330098486</v>
+        <v>4.709085409728385</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.07169245403810749</v>
+        <v>0.07126798196557838</v>
       </c>
       <c r="C27">
-        <v>52959.47141405307</v>
+        <v>53270.27274440204</v>
       </c>
       <c r="D27">
-        <v>62470.31319219244</v>
+        <v>62781.11452254141</v>
       </c>
       <c r="E27">
         <v>-28227.22533441812</v>
@@ -3507,37 +3507,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M27">
-        <v>1138.915176688624</v>
+        <v>1098.784664776717</v>
       </c>
       <c r="N27">
-        <v>3828.384823311376</v>
+        <v>3868.515335223282</v>
       </c>
       <c r="O27">
-        <v>957.096205827844</v>
+        <v>967.1288338058206</v>
       </c>
       <c r="P27">
-        <v>2871.288617483532</v>
+        <v>2901.386501417462</v>
       </c>
       <c r="Q27">
-        <v>12376.28861748353</v>
+        <v>12406.38650141746</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07998078455184313</v>
+        <v>0.07996482178847097</v>
       </c>
       <c r="T27">
         <v>0.6659359676066536</v>
       </c>
       <c r="U27">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.04682746249690058</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.361431036894547</v>
+        <v>4.52072199333925</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.07190736709397282</v>
+        <v>0.07119342694697044</v>
       </c>
       <c r="C28">
-        <v>52069.58520705858</v>
+        <v>52596.96572994285</v>
       </c>
       <c r="D28">
-        <v>62310.07265632352</v>
+        <v>62837.4531792078</v>
       </c>
       <c r="E28">
         <v>-27497.57966329254</v>
@@ -3589,45 +3589,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M28">
-        <v>1211.030886185139</v>
+        <v>1142.736051367786</v>
       </c>
       <c r="N28">
-        <v>3756.26911381486</v>
+        <v>3824.563948632213</v>
       </c>
       <c r="O28">
-        <v>939.0672784537151</v>
+        <v>956.1409871580533</v>
       </c>
       <c r="P28">
-        <v>2817.201835361145</v>
+        <v>2868.42296147416</v>
       </c>
       <c r="Q28">
-        <v>12322.20183536115</v>
+        <v>12373.42296147416</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.08035030654699819</v>
+        <v>0.08033417121321121</v>
       </c>
       <c r="T28">
         <v>0.6731352753645635</v>
       </c>
       <c r="U28">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.04787746249690057</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.10171206751585</v>
+        <v>4.34684807051851</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.07185978014983813</v>
+        <v>0.07132137192836252</v>
       </c>
       <c r="C29">
-        <v>51375.34976333319</v>
+        <v>51770.6984844703</v>
       </c>
       <c r="D29">
-        <v>62345.48288372372</v>
+        <v>62740.83160486082</v>
       </c>
       <c r="E29">
         <v>-26767.93399216697</v>
@@ -3671,37 +3671,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M29">
-        <v>1257.60899719226</v>
+        <v>1206.387871079245</v>
       </c>
       <c r="N29">
-        <v>3709.691002807739</v>
+        <v>3760.912128920754</v>
       </c>
       <c r="O29">
-        <v>927.4227507019348</v>
+        <v>940.2280322301885</v>
       </c>
       <c r="P29">
-        <v>2782.268252105804</v>
+        <v>2820.684096690566</v>
       </c>
       <c r="Q29">
-        <v>12287.26825210581</v>
+        <v>12325.68409669057</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.08072995243243147</v>
+        <v>0.0807136398002731</v>
       </c>
       <c r="T29">
         <v>0.6805318244309092</v>
       </c>
       <c r="U29">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.949796805756002</v>
+        <v>4.117498293112156</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.07181219320570345</v>
+        <v>0.07125431690975458</v>
       </c>
       <c r="C30">
-        <v>50681.15458908999</v>
+        <v>51091.65437993137</v>
       </c>
       <c r="D30">
-        <v>62380.93338060609</v>
+        <v>62791.43317144748</v>
       </c>
       <c r="E30">
         <v>-26038.28832104139</v>
@@ -3753,37 +3753,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M30">
-        <v>1304.187108199381</v>
+        <v>1251.068903341439</v>
       </c>
       <c r="N30">
-        <v>3663.112891800618</v>
+        <v>3716.23109665856</v>
       </c>
       <c r="O30">
-        <v>915.7782229501545</v>
+        <v>929.05777416464</v>
       </c>
       <c r="P30">
-        <v>2747.334668850463</v>
+        <v>2787.17332249392</v>
       </c>
       <c r="Q30">
-        <v>12252.33466885046</v>
+        <v>12292.17332249392</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.08112014403690457</v>
+        <v>0.08110364918142002</v>
       </c>
       <c r="T30">
         <v>0.6881338331935422</v>
       </c>
       <c r="U30">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.808732634121859</v>
+        <v>3.970444782643865</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.07176460626156876</v>
+        <v>0.07118726189114663</v>
       </c>
       <c r="C31">
-        <v>49986.99975306141</v>
+        <v>50412.69196335372</v>
       </c>
       <c r="D31">
-        <v>62416.42421570307</v>
+        <v>62842.11642599538</v>
       </c>
       <c r="E31">
         <v>-25308.64264991582</v>
@@ -3835,37 +3835,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M31">
-        <v>1350.765219206502</v>
+        <v>1295.749935603633</v>
       </c>
       <c r="N31">
-        <v>3616.534780793498</v>
+        <v>3671.550064396366</v>
       </c>
       <c r="O31">
-        <v>904.1336951983744</v>
+        <v>917.8875160990915</v>
       </c>
       <c r="P31">
-        <v>2712.401085595123</v>
+        <v>2753.662548297274</v>
       </c>
       <c r="Q31">
-        <v>12217.40108559512</v>
+        <v>12258.66254829727</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.08152132695417971</v>
+        <v>0.08150464474231756</v>
       </c>
       <c r="T31">
         <v>0.6959499830480803</v>
       </c>
       <c r="U31">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.677397026048693</v>
+        <v>3.833532893587181</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.07171701931743409</v>
+        <v>0.07112020687253869</v>
       </c>
       <c r="C32">
-        <v>49292.88532413633</v>
+        <v>49733.81143270488</v>
       </c>
       <c r="D32">
-        <v>62451.95545790358</v>
+        <v>62892.88156647213</v>
       </c>
       <c r="E32">
         <v>-24578.99697879024</v>
@@ -3917,37 +3917,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M32">
-        <v>1397.343330213622</v>
+        <v>1340.430967865828</v>
       </c>
       <c r="N32">
-        <v>3569.956669786377</v>
+        <v>3626.869032134172</v>
       </c>
       <c r="O32">
-        <v>892.4891674465941</v>
+        <v>906.717258033543</v>
       </c>
       <c r="P32">
-        <v>2677.467502339782</v>
+        <v>2720.151774100629</v>
       </c>
       <c r="Q32">
-        <v>12182.46750233978</v>
+        <v>12225.15177410063</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.08193397224051988</v>
+        <v>0.08191709731924075</v>
       </c>
       <c r="T32">
         <v>0.703989451469891</v>
       </c>
       <c r="U32">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.554817125180402</v>
+        <v>3.705748463800941</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.0716694323732994</v>
+        <v>0.07105315185393075</v>
       </c>
       <c r="C33">
-        <v>48598.81137136069</v>
+        <v>49055.01298659268</v>
       </c>
       <c r="D33">
-        <v>62487.52717625351</v>
+        <v>62943.7287914855</v>
       </c>
       <c r="E33">
         <v>-23849.35130766467</v>
@@ -3999,37 +3999,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M33">
-        <v>1443.921441220743</v>
+        <v>1385.112000128022</v>
       </c>
       <c r="N33">
-        <v>3523.378558779256</v>
+        <v>3582.187999871978</v>
       </c>
       <c r="O33">
-        <v>880.8446396948141</v>
+        <v>895.5469999679945</v>
       </c>
       <c r="P33">
-        <v>2642.533919084442</v>
+        <v>2686.640999903983</v>
       </c>
       <c r="Q33">
-        <v>12147.53391908444</v>
+        <v>12191.64099990398</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.08235857825979742</v>
+        <v>0.08234150504332113</v>
       </c>
       <c r="T33">
         <v>0.7122619479618991</v>
       </c>
       <c r="U33">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.440145605013293</v>
+        <v>3.586208190775105</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.07162184542916472</v>
+        <v>0.07098609683532282</v>
       </c>
       <c r="C34">
-        <v>47904.77796393773</v>
+        <v>48376.2968242677</v>
       </c>
       <c r="D34">
-        <v>62523.13943995612</v>
+        <v>62994.6583002861</v>
       </c>
       <c r="E34">
         <v>-23119.70563653909</v>
@@ -4081,37 +4081,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M34">
-        <v>1490.499552227864</v>
+        <v>1429.793032390216</v>
       </c>
       <c r="N34">
-        <v>3476.800447772135</v>
+        <v>3537.506967609783</v>
       </c>
       <c r="O34">
-        <v>869.2001119430338</v>
+        <v>884.3767419024457</v>
       </c>
       <c r="P34">
-        <v>2607.600335829101</v>
+        <v>2653.130225707337</v>
       </c>
       <c r="Q34">
-        <v>12112.6003358291</v>
+        <v>12158.13022570734</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.08279567269140668</v>
+        <v>0.08277839534752154</v>
       </c>
       <c r="T34">
         <v>0.7207777531742605</v>
       </c>
       <c r="U34">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.332641054856627</v>
+        <v>3.474139184813382</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.07157425848503003</v>
+        <v>0.07091904181671489</v>
       </c>
       <c r="C35">
-        <v>47210.78517122861</v>
+        <v>47697.66314562596</v>
       </c>
       <c r="D35">
-        <v>62558.79231837258</v>
+        <v>63045.67029276994</v>
       </c>
       <c r="E35">
         <v>-22390.05996541352</v>
@@ -4163,37 +4163,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M35">
-        <v>1537.077663234985</v>
+        <v>1474.47406465241</v>
       </c>
       <c r="N35">
-        <v>3430.222336765014</v>
+        <v>3492.825935347589</v>
       </c>
       <c r="O35">
-        <v>857.5555841912536</v>
+        <v>873.2064838368972</v>
       </c>
       <c r="P35">
-        <v>2572.666752573761</v>
+        <v>2619.619451510692</v>
       </c>
       <c r="Q35">
-        <v>12077.66675257376</v>
+        <v>12124.61945151069</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.08324581471798934</v>
+        <v>0.08322832715333986</v>
       </c>
       <c r="T35">
         <v>0.7295477615272893</v>
       </c>
       <c r="U35">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.231651931982184</v>
+        <v>3.368862239819037</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.07152667154089537</v>
+        <v>0.07085198679810695</v>
       </c>
       <c r="C36">
-        <v>46516.83306275272</v>
+        <v>47019.11215121148</v>
       </c>
       <c r="D36">
-        <v>62594.48588102227</v>
+        <v>63096.76496948102</v>
       </c>
       <c r="E36">
         <v>-21660.41429428794</v>
@@ -4245,37 +4245,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M36">
-        <v>1583.655774242106</v>
+        <v>1519.155096914605</v>
       </c>
       <c r="N36">
-        <v>3383.644225757894</v>
+        <v>3448.144903085395</v>
       </c>
       <c r="O36">
-        <v>845.9110564394734</v>
+        <v>862.0362257713487</v>
       </c>
       <c r="P36">
-        <v>2537.733169318421</v>
+        <v>2586.108677314046</v>
       </c>
       <c r="Q36">
-        <v>12042.73316931842</v>
+        <v>12091.10867731405</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.0837095974120442</v>
+        <v>0.08369189325630419</v>
       </c>
       <c r="T36">
         <v>0.7385835277091978</v>
       </c>
       <c r="U36">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.136603345747414</v>
+        <v>3.269778056294948</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.07147908459676068</v>
+        <v>0.07078493177949902</v>
       </c>
       <c r="C37">
-        <v>45822.9217081883</v>
+        <v>46340.64404221886</v>
       </c>
       <c r="D37">
-        <v>62630.22019758342</v>
+        <v>63147.94253161398</v>
       </c>
       <c r="E37">
         <v>-20930.76862316237</v>
@@ -4327,37 +4327,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M37">
-        <v>1630.233885249226</v>
+        <v>1563.836129176799</v>
       </c>
       <c r="N37">
-        <v>3337.066114750773</v>
+        <v>3403.463870823201</v>
       </c>
       <c r="O37">
-        <v>834.2665286876932</v>
+        <v>850.8659677058001</v>
       </c>
       <c r="P37">
-        <v>2502.799586063079</v>
+        <v>2552.5979031174</v>
       </c>
       <c r="Q37">
-        <v>12007.79958606308</v>
+        <v>12057.5979031174</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.0841876503428392</v>
+        <v>0.08416972293166741</v>
       </c>
       <c r="T37">
         <v>0.7478973174659342</v>
       </c>
       <c r="U37">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V37">
         <v>0.25</v>
       </c>
       <c r="W37">
-        <v>0.04787746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.046986107297487</v>
+        <v>3.176355826115092</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.072133497652626</v>
+        <v>0.07071787676089109</v>
       </c>
       <c r="C38">
-        <v>44605.40926646114</v>
+        <v>45662.25902049606</v>
       </c>
       <c r="D38">
-        <v>62142.35342698183</v>
+        <v>63199.20318101675</v>
       </c>
       <c r="E38">
         <v>-20201.1229520368</v>
@@ -4409,45 +4409,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M38">
-        <v>1745.106831073701</v>
+        <v>1608.517161438993</v>
       </c>
       <c r="N38">
-        <v>3222.193168926299</v>
+        <v>3358.782838561006</v>
       </c>
       <c r="O38">
-        <v>805.5482922315747</v>
+        <v>839.6957096402516</v>
       </c>
       <c r="P38">
-        <v>2416.644876694724</v>
+        <v>2519.087128920755</v>
       </c>
       <c r="Q38">
-        <v>11921.64487669473</v>
+        <v>12024.08712892076</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08468064242772155</v>
+        <v>0.08466248478438575</v>
       </c>
       <c r="T38">
         <v>0.7575021631525686</v>
       </c>
       <c r="U38">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.84641599674663</v>
+        <v>3.088123719834118</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.07210541070849133</v>
+        <v>0.07065082174228315</v>
       </c>
       <c r="C39">
-        <v>43896.54633282771</v>
+        <v>44983.95728854694</v>
       </c>
       <c r="D39">
-        <v>62163.13616447398</v>
+        <v>63250.54712019322</v>
       </c>
       <c r="E39">
         <v>-19471.47728091122</v>
@@ -4491,45 +4491,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M39">
-        <v>1793.582020825748</v>
+        <v>1653.198193701187</v>
       </c>
       <c r="N39">
-        <v>3173.717979174252</v>
+        <v>3314.101806298812</v>
       </c>
       <c r="O39">
-        <v>793.429494793563</v>
+        <v>828.5254515747031</v>
       </c>
       <c r="P39">
-        <v>2380.288484380689</v>
+        <v>2485.576354724109</v>
       </c>
       <c r="Q39">
-        <v>11885.28848438069</v>
+        <v>11990.57635472411</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08518928505498113</v>
+        <v>0.08517088987052371</v>
       </c>
       <c r="T39">
         <v>0.7674119245752866</v>
       </c>
       <c r="U39">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.04982746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.769485834672397</v>
+        <v>3.004660916595358</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.07207732376435663</v>
+        <v>0.07129626672367521</v>
       </c>
       <c r="C40">
-        <v>43187.69730490122</v>
+        <v>43763.53162790969</v>
       </c>
       <c r="D40">
-        <v>62183.93280767306</v>
+        <v>62759.76713068153</v>
       </c>
       <c r="E40">
         <v>-18741.83160978564</v>
@@ -4573,37 +4573,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M40">
-        <v>1842.057210577795</v>
+        <v>1767.195564720311</v>
       </c>
       <c r="N40">
-        <v>3125.242789422204</v>
+        <v>3200.104435279688</v>
       </c>
       <c r="O40">
-        <v>781.310697355551</v>
+        <v>800.026108819922</v>
       </c>
       <c r="P40">
-        <v>2343.932092066653</v>
+        <v>2400.078326459766</v>
       </c>
       <c r="Q40">
-        <v>11848.93209206665</v>
+        <v>11905.07832645977</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08571433550892649</v>
+        <v>0.08569569512073064</v>
       </c>
       <c r="T40">
         <v>0.7776413557213182</v>
       </c>
       <c r="U40">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V40">
         <v>0.25</v>
       </c>
       <c r="W40">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.696604628496807</v>
+        <v>2.810837747199846</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.07204923682022196</v>
+        <v>0.07124796170506728</v>
       </c>
       <c r="C41">
-        <v>42478.86219664273</v>
+        <v>43070.35204511377</v>
       </c>
       <c r="D41">
-        <v>62204.74337054015</v>
+        <v>62796.23321901119</v>
       </c>
       <c r="E41">
         <v>-18012.18593866007</v>
@@ -4655,37 +4655,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M41">
-        <v>1890.532400329842</v>
+        <v>1813.700711160319</v>
       </c>
       <c r="N41">
-        <v>3076.767599670157</v>
+        <v>3153.59928883968</v>
       </c>
       <c r="O41">
-        <v>769.1918999175393</v>
+        <v>788.39982220992</v>
       </c>
       <c r="P41">
-        <v>2307.575699752618</v>
+        <v>2365.19946662976</v>
       </c>
       <c r="Q41">
-        <v>11812.57569975262</v>
+        <v>11870.19946662976</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08625660073185368</v>
+        <v>0.08623770710045255</v>
       </c>
       <c r="T41">
         <v>0.7882061780524655</v>
       </c>
       <c r="U41">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.627460920073812</v>
+        <v>2.738764984451132</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.07202114987608726</v>
+        <v>0.07119965668645933</v>
       </c>
       <c r="C42">
-        <v>41770.04102203211</v>
+        <v>42377.21486364484</v>
       </c>
       <c r="D42">
-        <v>62225.5678670551</v>
+        <v>62832.74170866783</v>
       </c>
       <c r="E42">
         <v>-17282.5402675345</v>
@@ -4737,37 +4737,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M42">
-        <v>1939.007590081889</v>
+        <v>1860.205857600327</v>
       </c>
       <c r="N42">
-        <v>3028.29240991811</v>
+        <v>3107.094142399672</v>
       </c>
       <c r="O42">
-        <v>757.0731024795275</v>
+        <v>776.773535599918</v>
       </c>
       <c r="P42">
-        <v>2271.219307438582</v>
+        <v>2330.320606799754</v>
       </c>
       <c r="Q42">
-        <v>11776.21930743858</v>
+        <v>11835.32060679975</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08681694146221175</v>
+        <v>0.08679778614616518</v>
       </c>
       <c r="T42">
         <v>0.7991231611279844</v>
       </c>
       <c r="U42">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.04982746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.561774397071967</v>
+        <v>2.670295859839854</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.0728233129319526</v>
+        <v>0.07115135166785139</v>
       </c>
       <c r="C43">
-        <v>40451.08316539065</v>
+        <v>41684.12015749978</v>
       </c>
       <c r="D43">
-        <v>61636.25568153922</v>
+        <v>62869.29267364836</v>
       </c>
       <c r="E43">
         <v>-16552.89459640892</v>
@@ -4819,45 +4819,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M43">
-        <v>2068.254555627538</v>
+        <v>1906.711004040336</v>
       </c>
       <c r="N43">
-        <v>2899.045444372461</v>
+        <v>3060.588995959663</v>
       </c>
       <c r="O43">
-        <v>724.7613610931153</v>
+        <v>765.1472489899159</v>
       </c>
       <c r="P43">
-        <v>2174.284083279346</v>
+        <v>2295.441746969747</v>
       </c>
       <c r="Q43">
-        <v>11679.28408327935</v>
+        <v>11800.44174696975</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08739627679359893</v>
+        <v>0.08737685092224096</v>
       </c>
       <c r="T43">
         <v>0.8104102114264023</v>
       </c>
       <c r="U43">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V43">
         <v>0.25</v>
       </c>
       <c r="W43">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.401686961831857</v>
+        <v>2.605166692526686</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.07281547598781793</v>
+        <v>0.07110304664924347</v>
       </c>
       <c r="C44">
-        <v>39727.14093693385</v>
+        <v>40991.06800084776</v>
       </c>
       <c r="D44">
-        <v>61641.95912420799</v>
+        <v>62905.88618812191</v>
       </c>
       <c r="E44">
         <v>-15823.24892528335</v>
@@ -4901,45 +4901,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M44">
-        <v>2118.699788691624</v>
+        <v>1953.216150480344</v>
       </c>
       <c r="N44">
-        <v>2848.600211308375</v>
+        <v>3014.083849519656</v>
       </c>
       <c r="O44">
-        <v>712.1500528270938</v>
+        <v>753.520962379914</v>
       </c>
       <c r="P44">
-        <v>2136.450158481282</v>
+        <v>2260.562887139742</v>
       </c>
       <c r="Q44">
-        <v>11641.45015848128</v>
+        <v>11765.56288713974</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.08799558920537875</v>
+        <v>0.08797588344921591</v>
       </c>
       <c r="T44">
         <v>0.8220864703558001</v>
       </c>
       <c r="U44">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.05185246249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.344503938931099</v>
+        <v>2.543138914133195</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.07280763904368323</v>
+        <v>0.07218349163063553</v>
       </c>
       <c r="C45">
-        <v>39003.19976409824</v>
+        <v>39452.97884475197</v>
       </c>
       <c r="D45">
-        <v>61647.66362249796</v>
+        <v>62097.44270315168</v>
       </c>
       <c r="E45">
         <v>-15093.60325415777</v>
@@ -4983,37 +4983,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M45">
-        <v>2169.14502175571</v>
+        <v>2109.532970424751</v>
       </c>
       <c r="N45">
-        <v>2798.154978244289</v>
+        <v>2857.767029575248</v>
       </c>
       <c r="O45">
-        <v>699.5387445610722</v>
+        <v>714.4417573938121</v>
       </c>
       <c r="P45">
-        <v>2098.616233683217</v>
+        <v>2143.325272181436</v>
       </c>
       <c r="Q45">
-        <v>11603.61623368322</v>
+        <v>11648.32527218144</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08861593012283507</v>
+        <v>0.08859593466134785</v>
       </c>
       <c r="T45">
         <v>0.8341724225809661</v>
       </c>
       <c r="U45">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V45">
         <v>0.25</v>
       </c>
       <c r="W45">
-        <v>0.05185246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.289980591514096</v>
+        <v>2.354691806025597</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.07435080209954857</v>
+        <v>0.0721614366120276</v>
       </c>
       <c r="C46">
-        <v>37170.28855240915</v>
+        <v>38739.62804045354</v>
       </c>
       <c r="D46">
-        <v>60544.39808193444</v>
+        <v>62113.73756997883</v>
       </c>
       <c r="E46">
         <v>-14363.9575830322</v>
@@ -5065,45 +5065,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M46">
-        <v>2370.480979608566</v>
+        <v>2158.591876713699</v>
       </c>
       <c r="N46">
-        <v>2596.819020391433</v>
+        <v>2808.7081232863</v>
       </c>
       <c r="O46">
-        <v>649.2047550978583</v>
+        <v>702.177030821575</v>
       </c>
       <c r="P46">
-        <v>1947.614265293575</v>
+        <v>2106.531092464725</v>
       </c>
       <c r="Q46">
-        <v>11452.61426529357</v>
+        <v>11611.53109246473</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.0892584260730577</v>
+        <v>0.0892381305596274</v>
       </c>
       <c r="T46">
         <v>0.8466900159570312</v>
       </c>
       <c r="U46">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.05537746249690058</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.095481905457112</v>
+        <v>2.301176083161379</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.07437821515541387</v>
+        <v>0.07213938159341965</v>
       </c>
       <c r="C47">
-        <v>36421.40111279676</v>
+        <v>38026.28579020719</v>
       </c>
       <c r="D47">
-        <v>60525.15631344763</v>
+        <v>62130.04099085807</v>
       </c>
       <c r="E47">
         <v>-13634.31191190662</v>
@@ -5147,45 +5147,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M47">
-        <v>2424.355547326943</v>
+        <v>2207.650783002647</v>
       </c>
       <c r="N47">
-        <v>2542.944452673056</v>
+        <v>2759.649216997353</v>
       </c>
       <c r="O47">
-        <v>635.7361131682641</v>
+        <v>689.9123042493381</v>
       </c>
       <c r="P47">
-        <v>1907.208339504792</v>
+        <v>2069.736912748014</v>
       </c>
       <c r="Q47">
-        <v>11412.20833950479</v>
+        <v>11574.73691274801</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.0899242855123793</v>
+        <v>0.08990367903602617</v>
       </c>
       <c r="T47">
         <v>0.8596627945467711</v>
       </c>
       <c r="U47">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.05537746249690058</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.048915640891398</v>
+        <v>2.250038836868903</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.0744056282112792</v>
+        <v>0.07308332657481172</v>
       </c>
       <c r="C48">
-        <v>35672.52589984892</v>
+        <v>36606.4315401439</v>
       </c>
       <c r="D48">
-        <v>60505.92677162537</v>
+        <v>61439.83241192035</v>
       </c>
       <c r="E48">
         <v>-12904.66624078104</v>
@@ -5229,37 +5229,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M48">
-        <v>2478.23011504532</v>
+        <v>2350.688051732569</v>
       </c>
       <c r="N48">
-        <v>2489.06988495468</v>
+        <v>2616.611948267431</v>
       </c>
       <c r="O48">
-        <v>622.2674712386699</v>
+        <v>654.1529870668577</v>
       </c>
       <c r="P48">
-        <v>1866.80241371601</v>
+        <v>1962.458961200573</v>
       </c>
       <c r="Q48">
-        <v>11371.80241371601</v>
+        <v>11467.45896120057</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.09061480641241654</v>
+        <v>0.09059387745599529</v>
       </c>
       <c r="T48">
         <v>0.8731160464176125</v>
       </c>
       <c r="U48">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.05537746249690058</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.004373996524194</v>
+        <v>2.113125982981393</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.07936804126714452</v>
+        <v>0.07308227155620378</v>
       </c>
       <c r="C49">
-        <v>31652.23891820665</v>
+        <v>35877.54873379942</v>
       </c>
       <c r="D49">
-        <v>57215.28546110867</v>
+        <v>61440.59527670144</v>
       </c>
       <c r="E49">
         <v>-12175.02056965547</v>
@@ -5311,45 +5311,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M49">
-        <v>3012.211534364324</v>
+        <v>2401.789965900668</v>
       </c>
       <c r="N49">
-        <v>1955.088465635676</v>
+        <v>2565.510034099332</v>
       </c>
       <c r="O49">
-        <v>488.7721164089189</v>
+        <v>641.3775085248329</v>
       </c>
       <c r="P49">
-        <v>1466.316349226757</v>
+        <v>1924.132525574499</v>
       </c>
       <c r="Q49">
-        <v>10971.31634922676</v>
+        <v>11429.1325255745</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.09133138470490801</v>
+        <v>0.09131012109935946</v>
       </c>
       <c r="T49">
         <v>0.8870769681703726</v>
       </c>
       <c r="U49">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.06587746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.649054172766875</v>
+        <v>2.068165855683917</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.07950045432300984</v>
+        <v>0.07308121653759585</v>
       </c>
       <c r="C50">
-        <v>30839.68403014378</v>
+        <v>35148.66594639932</v>
       </c>
       <c r="D50">
-        <v>57132.37624417138</v>
+        <v>61441.35816042691</v>
       </c>
       <c r="E50">
         <v>-11445.3748985299</v>
@@ -5393,45 +5393,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M50">
-        <v>3076.301141478458</v>
+        <v>2452.891880068767</v>
       </c>
       <c r="N50">
-        <v>1890.998858521541</v>
+        <v>2514.408119931232</v>
       </c>
       <c r="O50">
-        <v>472.7497146303854</v>
+        <v>628.6020299828081</v>
       </c>
       <c r="P50">
-        <v>1418.249143891156</v>
+        <v>1885.806089948424</v>
       </c>
       <c r="Q50">
-        <v>10923.24914389116</v>
+        <v>11390.80608994842</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.09207552370095685</v>
+        <v>0.09205391257516071</v>
       </c>
       <c r="T50">
         <v>0.901574848452085</v>
       </c>
       <c r="U50">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.06587746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.614698877500899</v>
+        <v>2.025079067023835</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.07963286737887515</v>
+        <v>0.07594666151898792</v>
       </c>
       <c r="C51">
-        <v>30027.36907767721</v>
+        <v>32414.58870448064</v>
       </c>
       <c r="D51">
-        <v>57049.70696283038</v>
+        <v>59436.92658963381</v>
       </c>
       <c r="E51">
         <v>-10715.72922740432</v>
@@ -5475,45 +5475,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M51">
-        <v>3140.390748592592</v>
+        <v>2782.864369741062</v>
       </c>
       <c r="N51">
-        <v>1826.909251407407</v>
+        <v>2184.435630258938</v>
       </c>
       <c r="O51">
-        <v>456.7273128518517</v>
+        <v>546.1089075647344</v>
       </c>
       <c r="P51">
-        <v>1370.181938555555</v>
+        <v>1638.326722694203</v>
       </c>
       <c r="Q51">
-        <v>10875.18193855556</v>
+        <v>11143.3267226942</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.09284884461841936</v>
+        <v>0.09282687234413065</v>
       </c>
       <c r="T51">
         <v>0.9166412730585703</v>
       </c>
       <c r="U51">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.06587746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.581745839184554</v>
+        <v>1.784959430294547</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.07976528043474047</v>
+        <v>0.07746660650037998</v>
       </c>
       <c r="C52">
-        <v>29215.29302076736</v>
+        <v>30673.89572359161</v>
       </c>
       <c r="D52">
-        <v>56967.2765770461</v>
+        <v>58425.87927987036</v>
       </c>
       <c r="E52">
         <v>-9986.083556278747</v>
@@ -5557,37 +5557,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M52">
-        <v>3204.480355706727</v>
+        <v>2981.938426013427</v>
       </c>
       <c r="N52">
-        <v>1762.819644293272</v>
+        <v>1985.361573986572</v>
       </c>
       <c r="O52">
-        <v>440.704911073318</v>
+        <v>496.3403934966431</v>
       </c>
       <c r="P52">
-        <v>1322.114733219954</v>
+        <v>1489.021180489929</v>
       </c>
       <c r="Q52">
-        <v>10827.11473321995</v>
+        <v>10994.02118048993</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.09365309837258037</v>
+        <v>0.09363075050385938</v>
       </c>
       <c r="T52">
         <v>0.9323103546493152</v>
       </c>
       <c r="U52">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.550110922400863</v>
+        <v>1.665795630341306</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.0798976934906058</v>
+        <v>0.07755330148177204</v>
       </c>
       <c r="C53">
-        <v>28403.454825377</v>
+        <v>29887.61760733896</v>
       </c>
       <c r="D53">
-        <v>56885.08405278131</v>
+        <v>58369.24683474327</v>
       </c>
       <c r="E53">
         <v>-9256.437885153173</v>
@@ -5639,37 +5639,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M53">
-        <v>3268.569962820861</v>
+        <v>3041.577194533695</v>
       </c>
       <c r="N53">
-        <v>1698.730037179138</v>
+        <v>1925.722805466304</v>
       </c>
       <c r="O53">
-        <v>424.6825092947845</v>
+        <v>481.430701366576</v>
       </c>
       <c r="P53">
-        <v>1274.047527884353</v>
+        <v>1444.292104099728</v>
       </c>
       <c r="Q53">
-        <v>10779.04752788435</v>
+        <v>10949.29210409973</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.0944901788105847</v>
+        <v>0.09446744001704643</v>
       </c>
       <c r="T53">
         <v>0.9486189905907026</v>
       </c>
       <c r="U53">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V53">
         <v>0.25</v>
       </c>
       <c r="W53">
-        <v>0.06587746249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.519716590589081</v>
+        <v>1.633132970922849</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08638710654647111</v>
+        <v>0.07763999646316411</v>
       </c>
       <c r="C54">
-        <v>23917.09653210891</v>
+        <v>29101.44917289531</v>
       </c>
       <c r="D54">
-        <v>53128.37143063881</v>
+        <v>58312.7240714252</v>
       </c>
       <c r="E54">
         <v>-8526.792214027599</v>
@@ -5721,45 +5721,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M54">
-        <v>3951.107240781033</v>
+        <v>3101.215963053964</v>
       </c>
       <c r="N54">
-        <v>1016.192759218966</v>
+        <v>1866.084036946036</v>
       </c>
       <c r="O54">
-        <v>254.0481898047415</v>
+        <v>466.5210092365089</v>
       </c>
       <c r="P54">
-        <v>762.1445694142244</v>
+        <v>1399.563027709527</v>
       </c>
       <c r="Q54">
-        <v>10267.14456941422</v>
+        <v>10904.56302770953</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.09536213760017254</v>
+        <v>0.09533899159328293</v>
       </c>
       <c r="T54">
         <v>0.9656071530296478</v>
       </c>
       <c r="U54">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V54">
         <v>0.25</v>
       </c>
       <c r="W54">
-        <v>0.07810246249690057</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>1.257191895155468</v>
+        <v>1.601726567635872</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1009733825021736</v>
+        <v>0.07772669144455618</v>
       </c>
       <c r="C55">
-        <v>16320.45040146522</v>
+        <v>28315.3901019327</v>
       </c>
       <c r="D55">
-        <v>46261.37097112069</v>
+        <v>58256.31067158818</v>
       </c>
       <c r="E55">
         <v>-7797.146542902017</v>
@@ -5803,45 +5803,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M55">
-        <v>5291.63898496225</v>
+        <v>3160.854731574233</v>
       </c>
       <c r="N55">
-        <v>-324.3389849622508</v>
+        <v>1806.445268425766</v>
       </c>
       <c r="O55">
-        <v>-81.08474624056271</v>
+        <v>451.6113171064416</v>
       </c>
       <c r="P55">
-        <v>-243.2542387216881</v>
+        <v>1354.833951319325</v>
       </c>
       <c r="Q55">
-        <v>9261.745761278311</v>
+        <v>10859.83395131932</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.09674369793712127</v>
+        <v>0.09624763047063589</v>
       </c>
       <c r="T55">
-        <v>0.9925237592999776</v>
+        <v>0.98331821599791</v>
       </c>
       <c r="U55">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V55">
-        <v>0.2346768181897917</v>
+        <v>0.25</v>
       </c>
       <c r="W55">
-        <v>0.1047242348523144</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>0.9387072727591668</v>
+        <v>1.571505311642742</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.101883748668799</v>
+        <v>0.07781338642594823</v>
       </c>
       <c r="C56">
-        <v>15220.60051816049</v>
+        <v>27529.44007735385</v>
       </c>
       <c r="D56">
-        <v>45891.16675894154</v>
+        <v>58200.0063181349</v>
       </c>
       <c r="E56">
         <v>-7067.500871776443</v>
@@ -5885,45 +5885,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M56">
-        <v>5391.481229961538</v>
+        <v>3220.493500094502</v>
       </c>
       <c r="N56">
-        <v>-424.1812299615385</v>
+        <v>1746.806499905498</v>
       </c>
       <c r="O56">
-        <v>-106.0453074903846</v>
+        <v>436.7016249763744</v>
       </c>
       <c r="P56">
-        <v>-318.1359224711539</v>
+        <v>1310.104874929123</v>
       </c>
       <c r="Q56">
-        <v>9186.864077528846</v>
+        <v>10815.10487492912</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09785116963140651</v>
+        <v>0.09719577538613461</v>
       </c>
       <c r="T56">
-        <v>1.014100362763021</v>
+        <v>1.001799325182184</v>
       </c>
       <c r="U56">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V56">
-        <v>0.230330951186277</v>
+        <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.1053189085895407</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.9213238047451081</v>
+        <v>1.542403361427135</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1027941148354243</v>
+        <v>0.07790008140734028</v>
       </c>
       <c r="C57">
-        <v>14126.62867599748</v>
+        <v>26743.5987832861</v>
       </c>
       <c r="D57">
-        <v>45526.84058790409</v>
+        <v>58143.81069519272</v>
       </c>
       <c r="E57">
         <v>-6337.855200650869</v>
@@ -5967,45 +5967,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M57">
-        <v>5491.323474960825</v>
+        <v>3280.13226861477</v>
       </c>
       <c r="N57">
-        <v>-524.0234749608262</v>
+        <v>1687.16773138523</v>
       </c>
       <c r="O57">
-        <v>-131.0058687402066</v>
+        <v>421.7919328463074</v>
       </c>
       <c r="P57">
-        <v>-393.0176062206197</v>
+        <v>1265.375798538922</v>
       </c>
       <c r="Q57">
-        <v>9111.982393779381</v>
+        <v>10770.37579853892</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.09900786228988223</v>
+        <v>0.09818606007565552</v>
       </c>
       <c r="T57">
-        <v>1.036635926379977</v>
+        <v>1.021101816996869</v>
       </c>
       <c r="U57">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V57">
-        <v>0.2261431157101629</v>
+        <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.1058919578272315</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.9045724628406516</v>
+        <v>1.514359663946642</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1037044810020496</v>
+        <v>0.08395077638873236</v>
       </c>
       <c r="C58">
-        <v>13038.3959817927</v>
+        <v>22343.06270374682</v>
       </c>
       <c r="D58">
-        <v>45168.25356482489</v>
+        <v>54472.92028677902</v>
       </c>
       <c r="E58">
         <v>-5608.209529525295</v>
@@ -6049,45 +6049,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M58">
-        <v>5591.165719960112</v>
+        <v>3919.985274814096</v>
       </c>
       <c r="N58">
-        <v>-623.865719960113</v>
+        <v>1047.314725185904</v>
       </c>
       <c r="O58">
-        <v>-155.9664299900282</v>
+        <v>261.8286812964759</v>
       </c>
       <c r="P58">
-        <v>-467.8992899700847</v>
+        <v>785.4860438894277</v>
       </c>
       <c r="Q58">
-        <v>9037.100710029916</v>
+        <v>10290.48604388943</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1002171318873795</v>
+        <v>0.09922135770560916</v>
       </c>
       <c r="T58">
-        <v>1.060195833797703</v>
+        <v>1.041281694803131</v>
       </c>
       <c r="U58">
-        <v>0.1368366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V58">
-        <v>0.2221048457867672</v>
+        <v>0.25</v>
       </c>
       <c r="W58">
-        <v>0.106444541020719</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.8884193831470687</v>
+        <v>1.267173127387723</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.104614847168675</v>
+        <v>0.09725690970714293</v>
       </c>
       <c r="C59">
-        <v>11955.76788407161</v>
+        <v>14972.43215276071</v>
       </c>
       <c r="D59">
-        <v>44815.27113822938</v>
+        <v>47831.93540691848</v>
       </c>
       <c r="E59">
         <v>-4878.563858399721</v>
@@ -6131,37 +6131,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M59">
-        <v>5691.0079649594</v>
+        <v>5179.453384933259</v>
       </c>
       <c r="N59">
-        <v>-723.7079649594007</v>
+        <v>-212.15338493326</v>
       </c>
       <c r="O59">
-        <v>-180.9269912398502</v>
+        <v>-53.038346233315</v>
       </c>
       <c r="P59">
-        <v>-542.7809737195505</v>
+        <v>-159.115038699945</v>
       </c>
       <c r="Q59">
-        <v>8962.219026280449</v>
+        <v>9345.884961300055</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1014826465824349</v>
+        <v>0.1006758152765464</v>
       </c>
       <c r="T59">
-        <v>1.084851550862766</v>
+        <v>1.069631780041151</v>
       </c>
       <c r="U59">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V59">
-        <v>0.2182082695448941</v>
+        <v>0.2397598564382102</v>
       </c>
       <c r="W59">
-        <v>0.1069777353302245</v>
+        <v>0.09467773533022451</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8728330781795763</v>
+        <v>0.9590394257528406</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1055252133353003</v>
+        <v>0.09804427587376828</v>
       </c>
       <c r="C60">
-        <v>10878.61400473549</v>
+        <v>13900.19788121417</v>
       </c>
       <c r="D60">
-        <v>44467.76293001883</v>
+        <v>47489.3468064975</v>
       </c>
       <c r="E60">
         <v>-4148.918187274154</v>
@@ -6213,37 +6213,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M60">
-        <v>5790.850209958687</v>
+        <v>5270.320988177702</v>
       </c>
       <c r="N60">
-        <v>-823.5502099586874</v>
+        <v>-303.0209881777027</v>
       </c>
       <c r="O60">
-        <v>-205.8875524896719</v>
+        <v>-75.75524704442569</v>
       </c>
       <c r="P60">
-        <v>-617.6626574690156</v>
+        <v>-227.2657411332771</v>
       </c>
       <c r="Q60">
-        <v>8887.337342530984</v>
+        <v>9277.734258866723</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1028084238820167</v>
+        <v>0.1019823823069404</v>
       </c>
       <c r="T60">
-        <v>1.110681349692832</v>
+        <v>1.095099203375465</v>
       </c>
       <c r="U60">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V60">
-        <v>0.2144460580010166</v>
+        <v>0.2356260658099651</v>
       </c>
       <c r="W60">
-        <v>0.1074925436290574</v>
+        <v>0.09519254362905744</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8577842320040665</v>
+        <v>0.9425042632398606</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1064355795019256</v>
+        <v>0.09883164204039362</v>
       </c>
       <c r="C61">
-        <v>9806.807978499695</v>
+        <v>12832.83618294392</v>
       </c>
       <c r="D61">
-        <v>44125.60257490862</v>
+        <v>47151.63077935285</v>
       </c>
       <c r="E61">
         <v>-3419.272516148572</v>
@@ -6295,37 +6295,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M61">
-        <v>5890.692454957975</v>
+        <v>5361.188591422146</v>
       </c>
       <c r="N61">
-        <v>-923.392454957976</v>
+        <v>-393.8885914221464</v>
       </c>
       <c r="O61">
-        <v>-230.848113739494</v>
+        <v>-98.4721478555366</v>
       </c>
       <c r="P61">
-        <v>-692.544341218482</v>
+        <v>-295.4164435666098</v>
       </c>
       <c r="Q61">
-        <v>8812.455658781519</v>
+        <v>9209.58355643339</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1041988732449927</v>
+        <v>0.1033526843144267</v>
       </c>
       <c r="T61">
-        <v>1.13777113870973</v>
+        <v>1.121808940043159</v>
       </c>
       <c r="U61">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V61">
-        <v>0.2108113790518468</v>
+        <v>0.2316324036775929</v>
       </c>
       <c r="W61">
-        <v>0.1079899007991164</v>
+        <v>0.09568990079911636</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8432455162073873</v>
+        <v>0.9265296147103714</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.107345945668551</v>
+        <v>0.09961900820701897</v>
       </c>
       <c r="C62">
-        <v>8740.227299688137</v>
+        <v>11770.24383943784</v>
       </c>
       <c r="D62">
-        <v>43788.66756722263</v>
+        <v>46818.68410697234</v>
       </c>
       <c r="E62">
         <v>-2689.626845022998</v>
@@ -6377,37 +6377,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M62">
-        <v>5990.534699957263</v>
+        <v>5452.056194666588</v>
       </c>
       <c r="N62">
-        <v>-1023.234699957264</v>
+        <v>-484.7561946665892</v>
       </c>
       <c r="O62">
-        <v>-255.8086749893159</v>
+        <v>-121.1890486666473</v>
       </c>
       <c r="P62">
-        <v>-767.4260249679478</v>
+        <v>-363.5671459999419</v>
       </c>
       <c r="Q62">
-        <v>8737.573975032052</v>
+        <v>9141.432854000059</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1056588450761175</v>
+        <v>0.1047915014222874</v>
       </c>
       <c r="T62">
-        <v>1.166215417177473</v>
+        <v>1.149854163544238</v>
       </c>
       <c r="U62">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V62">
-        <v>0.2072978560676494</v>
+        <v>0.2277718636162996</v>
       </c>
       <c r="W62">
-        <v>0.10847067939684</v>
+        <v>0.09617067939684</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8291914242705976</v>
+        <v>0.9110874544651986</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1082563118351763</v>
+        <v>0.1004063743736443</v>
       </c>
       <c r="C63">
-        <v>7678.753175993625</v>
+        <v>10712.32052712454</v>
       </c>
       <c r="D63">
-        <v>43456.83911465369</v>
+        <v>46490.40646578461</v>
       </c>
       <c r="E63">
         <v>-1959.981173897424</v>
@@ -6459,37 +6459,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M63">
-        <v>6090.376944956551</v>
+        <v>5542.923797911032</v>
       </c>
       <c r="N63">
-        <v>-1123.076944956551</v>
+        <v>-575.6237979110329</v>
       </c>
       <c r="O63">
-        <v>-280.7692362391379</v>
+        <v>-143.9059494777582</v>
       </c>
       <c r="P63">
-        <v>-842.3077087174136</v>
+        <v>-431.7178484332746</v>
       </c>
       <c r="Q63">
-        <v>8662.692291282587</v>
+        <v>9073.282151566726</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1071936872575564</v>
+        <v>0.1063041040228589</v>
       </c>
       <c r="T63">
-        <v>1.196118376592281</v>
+        <v>1.179337603635116</v>
       </c>
       <c r="U63">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V63">
-        <v>0.2038995305583436</v>
+        <v>0.2240378986389832</v>
       </c>
       <c r="W63">
-        <v>0.1089356947618514</v>
+        <v>0.09663569476185137</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8155981222333746</v>
+        <v>0.896151594555933</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1091666780018017</v>
+        <v>0.1011937405402696</v>
       </c>
       <c r="C64">
-        <v>6622.270388837336</v>
+        <v>9658.968716588148</v>
       </c>
       <c r="D64">
-        <v>43130.00199862298</v>
+        <v>46166.70032637379</v>
       </c>
       <c r="E64">
         <v>-1230.33550277185</v>
@@ -6541,37 +6541,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M64">
-        <v>6190.219189955838</v>
+        <v>5633.791401155475</v>
       </c>
       <c r="N64">
-        <v>-1222.919189955839</v>
+        <v>-666.4914011554756</v>
       </c>
       <c r="O64">
-        <v>-305.7297974889598</v>
+        <v>-166.6228502888689</v>
       </c>
       <c r="P64">
-        <v>-917.1893924668793</v>
+        <v>-499.8685508666067</v>
       </c>
       <c r="Q64">
-        <v>8587.81060753312</v>
+        <v>9005.131449133394</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1088093106064394</v>
+        <v>0.1078963172866183</v>
       </c>
       <c r="T64">
-        <v>1.227595175976288</v>
+        <v>1.210372803730777</v>
       </c>
       <c r="U64">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V64">
-        <v>0.2006108284525639</v>
+        <v>0.2204243841448061</v>
       </c>
       <c r="W64">
-        <v>0.1093857096312172</v>
+        <v>0.09708570963121722</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8024433138102556</v>
+        <v>0.8816975365792245</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1648662761241698</v>
+        <v>0.101981106706895</v>
       </c>
       <c r="C65">
-        <v>-7699.523988673725</v>
+        <v>8610.093575964362</v>
       </c>
       <c r="D65">
-        <v>29537.85329223749</v>
+        <v>45847.47085687557</v>
       </c>
       <c r="E65">
         <v>-500.6898316462757</v>
@@ -6623,45 +6623,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M65">
-        <v>10192.71723610449</v>
+        <v>5724.659004399918</v>
       </c>
       <c r="N65">
-        <v>-5225.417236104489</v>
+        <v>-757.3590043999184</v>
       </c>
       <c r="O65">
-        <v>-1306.354309026122</v>
+        <v>-189.3397510999796</v>
       </c>
       <c r="P65">
-        <v>-3919.062927078367</v>
+        <v>-568.0192532999388</v>
       </c>
       <c r="Q65">
-        <v>5585.937072921633</v>
+        <v>8936.980746700061</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1140318107734858</v>
+        <v>0.1095745961322026</v>
       </c>
       <c r="T65">
-        <v>1.329343885014636</v>
+        <v>1.243085582209987</v>
       </c>
       <c r="U65">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V65">
-        <v>0.121834538448808</v>
+        <v>0.2169255843964759</v>
       </c>
       <c r="W65">
-        <v>0.194721438314254</v>
+        <v>0.09752143831425399</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.4873381537952318</v>
+        <v>0.8677023375859034</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1666256422907951</v>
+        <v>0.1027684728735203</v>
       </c>
       <c r="C66">
-        <v>-8720.301696982919</v>
+        <v>7565.602878316895</v>
       </c>
       <c r="D66">
-        <v>29246.72125505388</v>
+        <v>45532.62583035369</v>
       </c>
       <c r="E66">
         <v>228.9558394793057</v>
@@ -6705,45 +6705,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M66">
-        <v>10354.50639858234</v>
+        <v>5815.526607644362</v>
       </c>
       <c r="N66">
-        <v>-5387.206398582339</v>
+        <v>-848.226607644363</v>
       </c>
       <c r="O66">
-        <v>-1346.801599645585</v>
+        <v>-212.0566519110907</v>
       </c>
       <c r="P66">
-        <v>-4040.404798936754</v>
+        <v>-636.1699557332722</v>
       </c>
       <c r="Q66">
-        <v>5464.595201063246</v>
+        <v>8868.830044266728</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1159271388505271</v>
+        <v>0.1113461126914305</v>
       </c>
       <c r="T66">
-        <v>1.36627010404282</v>
+        <v>1.277615737271375</v>
       </c>
       <c r="U66">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V66">
-        <v>0.1199308737855453</v>
+        <v>0.2135361221402809</v>
       </c>
       <c r="W66">
-        <v>0.1951435504759459</v>
+        <v>0.09794355047594588</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.4797234951421813</v>
+        <v>0.8541444885611235</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1683850084574205</v>
+        <v>0.1035558390401457</v>
       </c>
       <c r="C67">
-        <v>-9735.396485666199</v>
+        <v>6525.406912804458</v>
       </c>
       <c r="D67">
-        <v>28961.27213749618</v>
+        <v>45222.07553596683</v>
       </c>
       <c r="E67">
         <v>958.6015106048799</v>
@@ -6787,45 +6787,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M67">
-        <v>10516.29556106019</v>
+        <v>5906.394210888805</v>
       </c>
       <c r="N67">
-        <v>-5548.995561060188</v>
+        <v>-939.0942108888057</v>
       </c>
       <c r="O67">
-        <v>-1387.248890265047</v>
+        <v>-234.7735527222014</v>
       </c>
       <c r="P67">
-        <v>-4161.746670795141</v>
+        <v>-704.3206581666043</v>
       </c>
       <c r="Q67">
-        <v>5343.253329204859</v>
+        <v>8800.679341833396</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1179307713891136</v>
+        <v>0.1132188587683285</v>
       </c>
       <c r="T67">
-        <v>1.405306392729758</v>
+        <v>1.314119044050558</v>
       </c>
       <c r="U67">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V67">
-        <v>0.1180857834196138</v>
+        <v>0.2102509510304304</v>
       </c>
       <c r="W67">
-        <v>0.1955526745711242</v>
+        <v>0.09835267457112415</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.4723431336784554</v>
+        <v>0.8410038041217216</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1701443746240458</v>
+        <v>0.104343205206771</v>
       </c>
       <c r="C68">
-        <v>-10744.97314292287</v>
+        <v>5489.418399458133</v>
       </c>
       <c r="D68">
-        <v>28681.34115136508</v>
+        <v>44915.73269374607</v>
       </c>
       <c r="E68">
         <v>1688.247181730454</v>
@@ -6869,45 +6869,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M68">
-        <v>10678.08472353804</v>
+        <v>5997.261814133248</v>
       </c>
       <c r="N68">
-        <v>-5710.784723538038</v>
+        <v>-1029.961814133248</v>
       </c>
       <c r="O68">
-        <v>-1427.696180884509</v>
+        <v>-257.4904535333121</v>
       </c>
       <c r="P68">
-        <v>-4283.088542653528</v>
+        <v>-772.4713605999364</v>
       </c>
       <c r="Q68">
-        <v>5221.911457346472</v>
+        <v>8732.528639400063</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.120052264665264</v>
+        <v>0.1152017663791617</v>
       </c>
       <c r="T68">
-        <v>1.446638933692398</v>
+        <v>1.352769604169692</v>
       </c>
       <c r="U68">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V68">
-        <v>0.116296604882953</v>
+        <v>0.2070653305602724</v>
       </c>
       <c r="W68">
-        <v>0.1959494009664486</v>
+        <v>0.09874940096644856</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.4651864195318122</v>
+        <v>0.8282613222410895</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1719037407906711</v>
+        <v>0.1051305713733963</v>
       </c>
       <c r="C69">
-        <v>-11749.19014677096</v>
+        <v>4457.552407399526</v>
       </c>
       <c r="D69">
-        <v>28406.76981864256</v>
+        <v>44613.51237281304</v>
       </c>
       <c r="E69">
         <v>2417.892852856028</v>
@@ -6951,45 +6951,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M69">
-        <v>10839.87388601588</v>
+        <v>6088.129417377691</v>
       </c>
       <c r="N69">
-        <v>-5872.573886015885</v>
+        <v>-1120.829417377691</v>
       </c>
       <c r="O69">
-        <v>-1468.143471503971</v>
+        <v>-280.2073543444228</v>
       </c>
       <c r="P69">
-        <v>-4404.430414511914</v>
+        <v>-840.6220630332684</v>
       </c>
       <c r="Q69">
-        <v>5100.569585488086</v>
+        <v>8664.377936966732</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1223023332914841</v>
+        <v>0.1173048502088332</v>
       </c>
       <c r="T69">
-        <v>1.490476477137622</v>
+        <v>1.393762622477864</v>
       </c>
       <c r="U69">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V69">
-        <v>0.1145608346608194</v>
+        <v>0.2039748032384773</v>
       </c>
       <c r="W69">
-        <v>0.196334284782808</v>
+        <v>0.09913428478280803</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.4582433386432777</v>
+        <v>0.8158992129539091</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1736631069572965</v>
+        <v>0.1059179375400217</v>
       </c>
       <c r="C70">
-        <v>-12748.19996422528</v>
+        <v>3429.726276338384</v>
       </c>
       <c r="D70">
-        <v>28137.40567231381</v>
+        <v>44315.33191287747</v>
       </c>
       <c r="E70">
         <v>3147.538523981602</v>
@@ -7033,45 +7033,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M70">
-        <v>11001.66304849373</v>
+        <v>6178.997020622134</v>
       </c>
       <c r="N70">
-        <v>-6034.363048493735</v>
+        <v>-1211.697020622135</v>
       </c>
       <c r="O70">
-        <v>-1508.590762123434</v>
+        <v>-302.9242551555337</v>
       </c>
       <c r="P70">
-        <v>-4525.772286370301</v>
+        <v>-908.7727654666012</v>
       </c>
       <c r="Q70">
-        <v>4979.227713629699</v>
+        <v>8596.227234533399</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.124693031206843</v>
+        <v>0.1195393767778593</v>
       </c>
       <c r="T70">
-        <v>1.537053867048173</v>
+        <v>1.437317704430298</v>
       </c>
       <c r="U70">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V70">
-        <v>0.1128761165040427</v>
+        <v>0.2009751737790879</v>
       </c>
       <c r="W70">
-        <v>0.1967078484869217</v>
+        <v>0.09950784848692165</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.4515044660161707</v>
+        <v>0.8039006951163516</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1754224731239218</v>
+        <v>0.1649084693197916</v>
       </c>
       <c r="C71">
-        <v>-13742.14933361392</v>
+        <v>-12086.40139016427</v>
       </c>
       <c r="D71">
-        <v>27873.10197405075</v>
+        <v>29528.8499175004</v>
       </c>
       <c r="E71">
         <v>3877.184195107176</v>
@@ -7115,37 +7115,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M71">
-        <v>11163.45221097158</v>
+        <v>10408.26894135661</v>
       </c>
       <c r="N71">
-        <v>-6196.152210971584</v>
+        <v>-5440.968941356614</v>
       </c>
       <c r="O71">
-        <v>-1549.038052742896</v>
+        <v>-1360.242235339153</v>
       </c>
       <c r="P71">
-        <v>-4647.114158228688</v>
+        <v>-4080.72670601746</v>
       </c>
       <c r="Q71">
-        <v>4857.885841771312</v>
+        <v>5424.27329398254</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1272379676973863</v>
+        <v>0.1267089231679339</v>
       </c>
       <c r="T71">
-        <v>1.586636249856178</v>
+        <v>1.577065508242531</v>
       </c>
       <c r="U71">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.1112402307576073</v>
+        <v>0.1193113866481375</v>
       </c>
       <c r="W71">
-        <v>0.1970705842575827</v>
+        <v>0.1820705842575827</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.444960923030429</v>
+        <v>0.47724554659255</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1771818392905471</v>
+        <v>0.1665178354864169</v>
       </c>
       <c r="C72">
-        <v>-14731.1795311313</v>
+        <v>-13082.42266904424</v>
       </c>
       <c r="D72">
-        <v>27613.71744765895</v>
+        <v>29262.47430974601</v>
       </c>
       <c r="E72">
         <v>4606.829866232758</v>
@@ -7197,37 +7197,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M72">
-        <v>11325.24137344943</v>
+        <v>10559.11341876758</v>
       </c>
       <c r="N72">
-        <v>-6357.941373449434</v>
+        <v>-5591.813418767581</v>
       </c>
       <c r="O72">
-        <v>-1589.485343362358</v>
+        <v>-1397.953354691895</v>
       </c>
       <c r="P72">
-        <v>-4768.456030087075</v>
+        <v>-4193.860064075685</v>
       </c>
       <c r="Q72">
-        <v>4736.543969912925</v>
+        <v>5311.139935924315</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1299525666206325</v>
+        <v>0.1294058872735317</v>
       </c>
       <c r="T72">
-        <v>1.639524124851384</v>
+        <v>1.629634358517282</v>
       </c>
       <c r="U72">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.1096510846039271</v>
+        <v>0.1176069382674498</v>
       </c>
       <c r="W72">
-        <v>0.197422956149082</v>
+        <v>0.182422956149082</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4386043384157086</v>
+        <v>0.4704277530697993</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1789412054571725</v>
+        <v>0.1681272016530423</v>
       </c>
       <c r="C73">
-        <v>-15715.42662264556</v>
+        <v>-14073.68103956183</v>
       </c>
       <c r="D73">
-        <v>27359.11602727026</v>
+        <v>29000.86161035399</v>
       </c>
       <c r="E73">
         <v>5336.475537358325</v>
@@ -7279,37 +7279,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M73">
-        <v>11487.03053592728</v>
+        <v>10709.95789617854</v>
       </c>
       <c r="N73">
-        <v>-6519.730535927281</v>
+        <v>-5742.657896178544</v>
       </c>
       <c r="O73">
-        <v>-1629.93263398182</v>
+        <v>-1435.664474044636</v>
       </c>
       <c r="P73">
-        <v>-4889.797901945461</v>
+        <v>-4306.993422133908</v>
       </c>
       <c r="Q73">
-        <v>4615.202098054539</v>
+        <v>5198.006577866092</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1328543792627233</v>
+        <v>0.1322888489036535</v>
       </c>
       <c r="T73">
-        <v>1.696059439501432</v>
+        <v>1.685828646742015</v>
       </c>
       <c r="U73">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.1081067031306324</v>
+        <v>0.1159505025172041</v>
       </c>
       <c r="W73">
-        <v>0.1977654020718067</v>
+        <v>0.1827654020718067</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4324268125225297</v>
+        <v>0.4638020100688163</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1807005716237979</v>
+        <v>0.1697365678196676</v>
       </c>
       <c r="C74">
-        <v>-16695.02170170288</v>
+        <v>-15060.30311399603</v>
       </c>
       <c r="D74">
-        <v>27109.16661933851</v>
+        <v>28743.88520704536</v>
       </c>
       <c r="E74">
         <v>6066.121208483899</v>
@@ -7361,37 +7361,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M74">
-        <v>11648.81969840513</v>
+        <v>10860.80237358951</v>
       </c>
       <c r="N74">
-        <v>-6681.519698405131</v>
+        <v>-5893.502373589508</v>
       </c>
       <c r="O74">
-        <v>-1670.379924601283</v>
+        <v>-1473.375593397377</v>
       </c>
       <c r="P74">
-        <v>-5011.139773803849</v>
+        <v>-4420.126780192131</v>
       </c>
       <c r="Q74">
-        <v>4493.860226196151</v>
+        <v>5084.873219807869</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.135963464236392</v>
+        <v>0.1353777363644983</v>
       </c>
       <c r="T74">
-        <v>1.756632990912197</v>
+        <v>1.746036812697087</v>
       </c>
       <c r="U74">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.106605221142707</v>
+        <v>0.1143400788711318</v>
       </c>
       <c r="W74">
-        <v>0.198098335607789</v>
+        <v>0.183098335607789</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4264208845708278</v>
+        <v>0.4573603154845273</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1824599377904232</v>
+        <v>0.1713459339862929</v>
       </c>
       <c r="C75">
-        <v>-17670.09111460378</v>
+        <v>-16042.41105639993</v>
       </c>
       <c r="D75">
-        <v>26863.74287756318</v>
+        <v>28491.42293576703</v>
       </c>
       <c r="E75">
         <v>6795.766879609473</v>
@@ -7443,37 +7443,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M75">
-        <v>11810.60886088298</v>
+        <v>11011.64685100047</v>
       </c>
       <c r="N75">
-        <v>-6843.30886088298</v>
+        <v>-6044.346851000475</v>
       </c>
       <c r="O75">
-        <v>-1710.827215220745</v>
+        <v>-1511.086712750119</v>
       </c>
       <c r="P75">
-        <v>-5132.481645662236</v>
+        <v>-4533.260138250356</v>
       </c>
       <c r="Q75">
-        <v>4372.518354337764</v>
+        <v>4971.739861749644</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1393028518007028</v>
+        <v>0.1386954303039241</v>
       </c>
       <c r="T75">
-        <v>1.821693472057093</v>
+        <v>1.810704842796979</v>
       </c>
       <c r="U75">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.1051448756476014</v>
+        <v>0.1127737764208423</v>
       </c>
       <c r="W75">
-        <v>0.1984221476770321</v>
+        <v>0.1834221476770321</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4205795025904056</v>
+        <v>0.4510951056833693</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1842193039570486</v>
+        <v>0.1729553001529183</v>
       </c>
       <c r="C76">
-        <v>-18640.75667336306</v>
+        <v>-17020.12277624741</v>
       </c>
       <c r="D76">
-        <v>26622.72298992948</v>
+        <v>28243.35688704513</v>
       </c>
       <c r="E76">
         <v>7525.412550735047</v>
@@ -7525,37 +7525,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M76">
-        <v>11972.39802336083</v>
+        <v>11162.49132841144</v>
       </c>
       <c r="N76">
-        <v>-7005.098023360828</v>
+        <v>-6195.19132841144</v>
       </c>
       <c r="O76">
-        <v>-1751.274505840207</v>
+        <v>-1548.79783210286</v>
       </c>
       <c r="P76">
-        <v>-5253.823517520621</v>
+        <v>-4646.393496308579</v>
       </c>
       <c r="Q76">
-        <v>4251.176482479379</v>
+        <v>4858.606503691421</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1428991153314991</v>
+        <v>0.1422683314694597</v>
       </c>
       <c r="T76">
-        <v>1.891758605597751</v>
+        <v>1.880347336750709</v>
       </c>
       <c r="U76">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.1037239989496608</v>
+        <v>0.1112498064692093</v>
       </c>
       <c r="W76">
-        <v>0.1987372080687281</v>
+        <v>0.1837372080687281</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4148959957986433</v>
+        <v>0.4449992258768373</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1859786701236739</v>
+        <v>0.1745646663195436</v>
       </c>
       <c r="C77">
-        <v>-19607.13585730784</v>
+        <v>-17993.55211205098</v>
       </c>
       <c r="D77">
-        <v>26385.98947711028</v>
+        <v>27999.57322236714</v>
       </c>
       <c r="E77">
         <v>8255.058221860629</v>
@@ -7607,37 +7607,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M77">
-        <v>12134.18718583868</v>
+        <v>11313.33580582241</v>
       </c>
       <c r="N77">
-        <v>-7166.887185838679</v>
+        <v>-6346.035805822406</v>
       </c>
       <c r="O77">
-        <v>-1791.72179645967</v>
+        <v>-1586.508951455602</v>
       </c>
       <c r="P77">
-        <v>-5375.16538937901</v>
+        <v>-4759.526854366804</v>
       </c>
       <c r="Q77">
-        <v>4129.83461062099</v>
+        <v>4745.473145633196</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.146783079944759</v>
+        <v>0.1461270647282381</v>
       </c>
       <c r="T77">
-        <v>1.967428949821661</v>
+        <v>1.955561230220738</v>
       </c>
       <c r="U77">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.1023410122969987</v>
+        <v>0.1097664757162865</v>
       </c>
       <c r="W77">
-        <v>0.1990438668499788</v>
+        <v>0.1840438668499788</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4093640491879946</v>
+        <v>0.439065902865146</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1877380362902992</v>
+        <v>0.1761740324861689</v>
       </c>
       <c r="C78">
-        <v>-20569.34200401443</v>
+        <v>-18962.80900555163</v>
       </c>
       <c r="D78">
-        <v>26153.42900152927</v>
+        <v>27759.96199999207</v>
       </c>
       <c r="E78">
         <v>8984.703892986203</v>
@@ -7689,37 +7689,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M78">
-        <v>12295.97634831653</v>
+        <v>11464.18028323337</v>
       </c>
       <c r="N78">
-        <v>-7328.676348316527</v>
+        <v>-6496.880283233371</v>
       </c>
       <c r="O78">
-        <v>-1832.169087079132</v>
+        <v>-1624.220070808343</v>
       </c>
       <c r="P78">
-        <v>-5496.507261237395</v>
+        <v>-4872.660212425028</v>
       </c>
       <c r="Q78">
-        <v>4008.492738762605</v>
+        <v>4632.339787574972</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1509907082757907</v>
+        <v>0.1503073590919146</v>
       </c>
       <c r="T78">
-        <v>2.04940515606423</v>
+        <v>2.037042948146602</v>
       </c>
       <c r="U78">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.1009944200299329</v>
+        <v>0.1083221799831775</v>
       </c>
       <c r="W78">
-        <v>0.1993424556633019</v>
+        <v>0.1843424556633019</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4039776801197316</v>
+        <v>0.4332887199327099</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1894974024569246</v>
+        <v>0.1777833986527943</v>
       </c>
       <c r="C79">
-        <v>-21527.48449023624</v>
+        <v>-19927.99966704048</v>
       </c>
       <c r="D79">
-        <v>25924.93218643303</v>
+        <v>27524.41700962879</v>
       </c>
       <c r="E79">
         <v>9714.349564111777</v>
@@ -7771,37 +7771,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M79">
-        <v>12457.76551079438</v>
+        <v>11615.02476064434</v>
       </c>
       <c r="N79">
-        <v>-7490.465510794376</v>
+        <v>-6647.724760644336</v>
       </c>
       <c r="O79">
-        <v>-1872.616377698594</v>
+        <v>-1661.931190161084</v>
       </c>
       <c r="P79">
-        <v>-5617.849133095782</v>
+        <v>-4985.793570483253</v>
       </c>
       <c r="Q79">
-        <v>3887.150866904218</v>
+        <v>4519.206429516747</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1555642173312598</v>
+        <v>0.1548511573133022</v>
       </c>
       <c r="T79">
-        <v>2.138509728067023</v>
+        <v>2.125610032848628</v>
       </c>
       <c r="U79">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.09968280418538832</v>
+        <v>0.1069153984249544</v>
       </c>
       <c r="W79">
-        <v>0.1996332889230322</v>
+        <v>0.1846332889230322</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3987312167415533</v>
+        <v>0.4276615936998176</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1912567686235499</v>
+        <v>0.1793927648194197</v>
       </c>
       <c r="C80">
-        <v>-22481.6689034294</v>
+        <v>-20889.22673233481</v>
       </c>
       <c r="D80">
-        <v>25700.39344436544</v>
+        <v>27292.83561546003</v>
       </c>
       <c r="E80">
         <v>10443.99523523735</v>
@@ -7853,37 +7853,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M80">
-        <v>12619.55467327223</v>
+        <v>11765.8692380553</v>
       </c>
       <c r="N80">
-        <v>-7652.254673272226</v>
+        <v>-6798.569238055303</v>
       </c>
       <c r="O80">
-        <v>-1913.063668318056</v>
+        <v>-1699.642309513826</v>
       </c>
       <c r="P80">
-        <v>-5739.191004954169</v>
+        <v>-5098.926928541478</v>
       </c>
       <c r="Q80">
-        <v>3765.808995045831</v>
+        <v>4406.073071458522</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1605534999372262</v>
+        <v>0.1598080281002705</v>
       </c>
       <c r="T80">
-        <v>2.235714715706433</v>
+        <v>2.222228670705384</v>
       </c>
       <c r="U80">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.09840481951634487</v>
+        <v>0.105544688188737</v>
       </c>
       <c r="W80">
-        <v>0.1999166649196925</v>
+        <v>0.1849166649196925</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3936192780653796</v>
+        <v>0.4221787527549481</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1930161347901752</v>
+        <v>0.181002130986045</v>
       </c>
       <c r="C81">
-        <v>-23431.9972044414</v>
+        <v>-21846.58941189566</v>
       </c>
       <c r="D81">
-        <v>25479.71081447902</v>
+        <v>27065.11860702475</v>
       </c>
       <c r="E81">
         <v>11173.64090636293</v>
@@ -7935,37 +7935,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M81">
-        <v>12781.34383575007</v>
+        <v>11916.71371546627</v>
       </c>
       <c r="N81">
-        <v>-7814.043835750073</v>
+        <v>-6949.413715466268</v>
       </c>
       <c r="O81">
-        <v>-1953.510958937518</v>
+        <v>-1737.353428866567</v>
       </c>
       <c r="P81">
-        <v>-5860.532876812555</v>
+        <v>-5212.060286599701</v>
       </c>
       <c r="Q81">
-        <v>3644.467123187445</v>
+        <v>4292.939713400299</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1660179523151893</v>
+        <v>0.165236981819331</v>
       </c>
       <c r="T81">
-        <v>2.342177321216263</v>
+        <v>2.328049083596117</v>
       </c>
       <c r="U81">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.09715918888955571</v>
+        <v>0.1042086794774872</v>
       </c>
       <c r="W81">
-        <v>0.2001928668404879</v>
+        <v>0.1851928668404879</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3886367555582229</v>
+        <v>0.4168347179099489</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1947755009568006</v>
+        <v>0.1826114971526703</v>
       </c>
       <c r="C82">
-        <v>-24378.56788188915</v>
+        <v>-22800.18363254223</v>
       </c>
       <c r="D82">
-        <v>25262.78580815684</v>
+        <v>26841.17005750376</v>
       </c>
       <c r="E82">
         <v>11903.2865774885</v>
@@ -8017,37 +8017,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M82">
-        <v>12943.13299822792</v>
+        <v>12067.55819287723</v>
       </c>
       <c r="N82">
-        <v>-7975.832998227923</v>
+        <v>-7100.258192877232</v>
       </c>
       <c r="O82">
-        <v>-1993.958249556981</v>
+        <v>-1775.064548219308</v>
       </c>
       <c r="P82">
-        <v>-5981.874748670942</v>
+        <v>-5325.193644657924</v>
       </c>
       <c r="Q82">
-        <v>3523.125251329058</v>
+        <v>4179.806355342076</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1720288499309488</v>
+        <v>0.1712088309102976</v>
       </c>
       <c r="T82">
-        <v>2.459286187277077</v>
+        <v>2.444451537775923</v>
       </c>
       <c r="U82">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.09594469902843626</v>
+        <v>0.1029060709840186</v>
       </c>
       <c r="W82">
-        <v>0.2004621637132635</v>
+        <v>0.1854621637132635</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.383778796113745</v>
+        <v>0.4116242839360744</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1965348671234259</v>
+        <v>0.1842208633192957</v>
       </c>
       <c r="C83">
-        <v>-25321.47609871787</v>
+        <v>-23750.10217218843</v>
       </c>
       <c r="D83">
-        <v>25049.52326245371</v>
+        <v>26620.89718898314</v>
       </c>
       <c r="E83">
         <v>12632.93224861408</v>
@@ -8099,37 +8099,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M83">
-        <v>13104.92216070577</v>
+        <v>12218.4026702882</v>
       </c>
       <c r="N83">
-        <v>-8137.622160705774</v>
+        <v>-7251.102670288199</v>
       </c>
       <c r="O83">
-        <v>-2034.405540176444</v>
+        <v>-1812.77566757205</v>
       </c>
       <c r="P83">
-        <v>-6103.216620529331</v>
+        <v>-5438.327002716149</v>
       </c>
       <c r="Q83">
-        <v>3401.783379470669</v>
+        <v>4066.672997283851</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1786724736115251</v>
+        <v>0.1778092956950501</v>
       </c>
       <c r="T83">
-        <v>2.588722302396923</v>
+        <v>2.573106881869392</v>
       </c>
       <c r="U83">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.09476019657129506</v>
+        <v>0.1016356256632283</v>
       </c>
       <c r="W83">
-        <v>0.2007248112805385</v>
+        <v>0.1857248112805385</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3790407862851802</v>
+        <v>0.406542502652913</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1982942332900512</v>
+        <v>0.185830229485921</v>
       </c>
       <c r="C84">
-        <v>-26260.81383139862</v>
+        <v>-24696.4347879991</v>
       </c>
       <c r="D84">
-        <v>24839.83120089853</v>
+        <v>26404.21024429805</v>
       </c>
       <c r="E84">
         <v>13362.57791973966</v>
@@ -8181,37 +8181,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M84">
-        <v>13266.71132318362</v>
+        <v>12369.24714769916</v>
       </c>
       <c r="N84">
-        <v>-8299.411323183622</v>
+        <v>-7401.947147699164</v>
       </c>
       <c r="O84">
-        <v>-2074.852830795905</v>
+        <v>-1850.486786924791</v>
       </c>
       <c r="P84">
-        <v>-6224.558492387716</v>
+        <v>-5551.460360774373</v>
       </c>
       <c r="Q84">
-        <v>3280.441507612284</v>
+        <v>3953.539639225627</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1860542777010543</v>
+        <v>0.1851431454558863</v>
       </c>
       <c r="T84">
-        <v>2.732540208085641</v>
+        <v>2.71605726419547</v>
       </c>
       <c r="U84">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.09360458441798659</v>
+        <v>0.1003961668136767</v>
       </c>
       <c r="W84">
-        <v>0.2009810528095872</v>
+        <v>0.1859810528095872</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3744183376719463</v>
+        <v>0.4015846672547068</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2000535994566766</v>
+        <v>0.1874395956525464</v>
       </c>
       <c r="C85">
-        <v>-27196.67000219275</v>
+        <v>-25639.26833833775</v>
       </c>
       <c r="D85">
-        <v>24633.62070122998</v>
+        <v>26191.02236508497</v>
       </c>
       <c r="E85">
         <v>14092.22359086523</v>
@@ -8263,37 +8263,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M85">
-        <v>13428.50048566147</v>
+        <v>12520.09162511013</v>
       </c>
       <c r="N85">
-        <v>-8461.200485661471</v>
+        <v>-7552.791625110131</v>
       </c>
       <c r="O85">
-        <v>-2115.300121415368</v>
+        <v>-1888.197906277533</v>
       </c>
       <c r="P85">
-        <v>-6345.900364246103</v>
+        <v>-5664.593718832598</v>
       </c>
       <c r="Q85">
-        <v>3159.099635753897</v>
+        <v>3840.406281167402</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.1943045293305281</v>
+        <v>0.1933398010709384</v>
       </c>
       <c r="T85">
-        <v>2.893277867384797</v>
+        <v>2.87582533855991</v>
       </c>
       <c r="U85">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.09247681834066145</v>
+        <v>0.09918657444242757</v>
       </c>
       <c r="W85">
-        <v>0.2012311198439601</v>
+        <v>0.18623111984396</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3699072733626458</v>
+        <v>0.3967462977697103</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2018129656233019</v>
+        <v>0.1890489618191717</v>
       </c>
       <c r="C86">
-        <v>-28129.13060488217</v>
+        <v>-26578.68689885415</v>
       </c>
       <c r="D86">
-        <v>24430.80576966612</v>
+        <v>25981.24947569414</v>
       </c>
       <c r="E86">
         <v>14821.8692619908</v>
@@ -8345,37 +8345,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M86">
-        <v>13590.28964813932</v>
+        <v>12670.93610252109</v>
       </c>
       <c r="N86">
-        <v>-8622.989648139319</v>
+        <v>-7703.636102521094</v>
       </c>
       <c r="O86">
-        <v>-2155.74741203483</v>
+        <v>-1925.909025630273</v>
       </c>
       <c r="P86">
-        <v>-6467.242236104489</v>
+        <v>-5777.72707689082</v>
       </c>
       <c r="Q86">
-        <v>3037.757763895511</v>
+        <v>3727.27292310918</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.203586062413686</v>
+        <v>0.2025610386378719</v>
       </c>
       <c r="T86">
-        <v>3.074107734096344</v>
+        <v>3.055564422219902</v>
       </c>
       <c r="U86">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.09137590383660596</v>
+        <v>0.09800578188954154</v>
       </c>
       <c r="W86">
-        <v>0.201475232901324</v>
+        <v>0.186475232901324</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3655036153464238</v>
+        <v>0.3920231275581662</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2035723317899273</v>
+        <v>0.190658327985797</v>
       </c>
       <c r="C87">
-        <v>-29058.2788243397</v>
+        <v>-27514.77187303732</v>
       </c>
       <c r="D87">
-        <v>24231.30322133416</v>
+        <v>25774.81017263655</v>
       </c>
       <c r="E87">
         <v>15551.51493311637</v>
@@ -8427,37 +8427,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M87">
-        <v>13752.07881061717</v>
+        <v>12821.78057993206</v>
       </c>
       <c r="N87">
-        <v>-8784.778810617167</v>
+        <v>-7854.480579932058</v>
       </c>
       <c r="O87">
-        <v>-2196.194702654292</v>
+        <v>-1963.620144983015</v>
       </c>
       <c r="P87">
-        <v>-6588.584107962875</v>
+        <v>-5890.860434949043</v>
       </c>
       <c r="Q87">
-        <v>2916.415892037125</v>
+        <v>3614.139565050957</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.214105133241265</v>
+        <v>0.2130117745470634</v>
       </c>
       <c r="T87">
-        <v>3.279048249702768</v>
+        <v>3.259268717034562</v>
       </c>
       <c r="U87">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.09030089320323413</v>
+        <v>0.09685277269084105</v>
       </c>
       <c r="W87">
-        <v>0.2017136021220442</v>
+        <v>0.1867136021220441</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3612035728129366</v>
+        <v>0.3874110907633642</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2053316979565526</v>
+        <v>0.1922676941524224</v>
       </c>
       <c r="C88">
-        <v>-29984.19515028805</v>
+        <v>-28447.60209753968</v>
       </c>
       <c r="D88">
-        <v>24035.03256651139</v>
+        <v>25571.62561925976</v>
       </c>
       <c r="E88">
         <v>16281.16060424194</v>
@@ -8509,37 +8509,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M88">
-        <v>13913.86797309502</v>
+        <v>12972.62505734302</v>
       </c>
       <c r="N88">
-        <v>-8946.567973095016</v>
+        <v>-8005.325057343023</v>
       </c>
       <c r="O88">
-        <v>-2236.641993273754</v>
+        <v>-2001.331264335756</v>
       </c>
       <c r="P88">
-        <v>-6709.925979821262</v>
+        <v>-6003.993793007267</v>
       </c>
       <c r="Q88">
-        <v>2795.074020178738</v>
+        <v>3501.006206992733</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.226126928472784</v>
+        <v>0.2249554727289965</v>
       </c>
       <c r="T88">
-        <v>3.513265981824394</v>
+        <v>3.492073625394174</v>
       </c>
       <c r="U88">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.08925088281715002</v>
+        <v>0.09572657765955221</v>
       </c>
       <c r="W88">
-        <v>0.201946427872515</v>
+        <v>0.1869464278725149</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3570035312686001</v>
+        <v>0.3829063106382089</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.207091064123178</v>
+        <v>0.1938770603190477</v>
       </c>
       <c r="C89">
-        <v>-30906.95748557489</v>
+        <v>-29377.25394255846</v>
       </c>
       <c r="D89">
-        <v>23841.91590235013</v>
+        <v>25371.61944536655</v>
       </c>
       <c r="E89">
         <v>17010.80627536753</v>
@@ -8591,37 +8591,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M89">
-        <v>14075.65713557287</v>
+        <v>13123.46953475399</v>
       </c>
       <c r="N89">
-        <v>-9108.357135572867</v>
+        <v>-8156.16953475399</v>
       </c>
       <c r="O89">
-        <v>-2277.089283893217</v>
+        <v>-2039.042383688497</v>
       </c>
       <c r="P89">
-        <v>-6831.26785167965</v>
+        <v>-6117.127151065492</v>
       </c>
       <c r="Q89">
-        <v>2673.73214832035</v>
+        <v>3387.872848934508</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.2399982306629981</v>
+        <v>0.2387366629389193</v>
       </c>
       <c r="T89">
-        <v>3.783517211195501</v>
+        <v>3.760694673501418</v>
       </c>
       <c r="U89">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.08822501060086092</v>
+        <v>0.09462627216921252</v>
       </c>
       <c r="W89">
-        <v>0.202173901306883</v>
+        <v>0.187173901306883</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3529000424034436</v>
+        <v>0.3785050886768501</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2088504302898033</v>
+        <v>0.195486426485673</v>
       </c>
       <c r="C90">
-        <v>-31826.64124926949</v>
+        <v>-30303.80140754292</v>
       </c>
       <c r="D90">
-        <v>23651.8778097811</v>
+        <v>25174.71765150768</v>
       </c>
       <c r="E90">
         <v>17740.4519464931</v>
@@ -8673,37 +8673,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M90">
-        <v>14237.44629805071</v>
+        <v>13274.31401216496</v>
       </c>
       <c r="N90">
-        <v>-9270.146298050715</v>
+        <v>-8307.014012164957</v>
       </c>
       <c r="O90">
-        <v>-2317.536574512679</v>
+        <v>-2076.753503041239</v>
       </c>
       <c r="P90">
-        <v>-6952.609723538037</v>
+        <v>-6230.260509123717</v>
       </c>
       <c r="Q90">
-        <v>2552.390276461963</v>
+        <v>3274.739490876283</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2561814165515813</v>
+        <v>0.2548147181838293</v>
       </c>
       <c r="T90">
-        <v>4.09881031212846</v>
+        <v>4.074085896293204</v>
       </c>
       <c r="U90">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.08722245366221479</v>
+        <v>0.09355097362183509</v>
       </c>
       <c r="W90">
-        <v>0.2023962048904699</v>
+        <v>0.1873962048904699</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3488898146488592</v>
+        <v>0.3742038944873404</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2106097964564287</v>
+        <v>0.1970957926522984</v>
       </c>
       <c r="C91">
-        <v>-32743.31947486804</v>
+        <v>-31227.31621247932</v>
       </c>
       <c r="D91">
-        <v>23464.84525530813</v>
+        <v>24980.84851769684</v>
       </c>
       <c r="E91">
         <v>18470.09761761867</v>
@@ -8755,37 +8755,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M91">
-        <v>14399.23546052856</v>
+        <v>13425.15848957592</v>
       </c>
       <c r="N91">
-        <v>-9431.935460528564</v>
+        <v>-8457.858489575921</v>
       </c>
       <c r="O91">
-        <v>-2357.983865132141</v>
+        <v>-2114.46462239398</v>
       </c>
       <c r="P91">
-        <v>-7073.951595396424</v>
+        <v>-6343.393867181941</v>
       </c>
       <c r="Q91">
-        <v>2431.048404603576</v>
+        <v>3161.606132818059</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2753069998744524</v>
+        <v>0.2738160562005411</v>
       </c>
       <c r="T91">
-        <v>4.471429431412866</v>
+        <v>4.444457341410769</v>
       </c>
       <c r="U91">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.08624242609297642</v>
+        <v>0.09249983908675831</v>
       </c>
       <c r="W91">
-        <v>0.2026135128879089</v>
+        <v>0.1876135128879089</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3449697043719057</v>
+        <v>0.3699993563470332</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.212369162623054</v>
+        <v>0.1987051588189237</v>
       </c>
       <c r="C92">
-        <v>-33657.0629038758</v>
+        <v>-32147.86788499037</v>
       </c>
       <c r="D92">
-        <v>23280.74749742595</v>
+        <v>24789.94251631138</v>
       </c>
       <c r="E92">
         <v>19199.74328874426</v>
@@ -8837,37 +8837,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M92">
-        <v>14561.02462300641</v>
+        <v>13576.00296698689</v>
       </c>
       <c r="N92">
-        <v>-9593.724623006416</v>
+        <v>-8608.702966986888</v>
       </c>
       <c r="O92">
-        <v>-2398.431155751604</v>
+        <v>-2152.175741746722</v>
       </c>
       <c r="P92">
-        <v>-7195.293467254812</v>
+        <v>-6456.527225240166</v>
       </c>
       <c r="Q92">
-        <v>2309.706532745188</v>
+        <v>3048.472774759834</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.2982576998618977</v>
+        <v>0.2966176618205952</v>
       </c>
       <c r="T92">
-        <v>4.918572374554153</v>
+        <v>4.888903075551846</v>
       </c>
       <c r="U92">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.08528417691416555</v>
+        <v>0.09147206309690542</v>
       </c>
       <c r="W92">
-        <v>0.202825991818738</v>
+        <v>0.187825991818738</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3411367076566622</v>
+        <v>0.3658882523876217</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2141285287896793</v>
+        <v>0.2003145249855491</v>
       </c>
       <c r="C93">
-        <v>-34567.94007501837</v>
+        <v>-33065.52384347105</v>
       </c>
       <c r="D93">
-        <v>23099.51599740895</v>
+        <v>24601.93222895628</v>
       </c>
       <c r="E93">
         <v>19929.38895986983</v>
@@ -8919,37 +8919,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M93">
-        <v>14722.81378548426</v>
+        <v>13726.84744439785</v>
       </c>
       <c r="N93">
-        <v>-9755.513785484263</v>
+        <v>-8759.547444397853</v>
       </c>
       <c r="O93">
-        <v>-2438.878446371066</v>
+        <v>-2189.886861099463</v>
       </c>
       <c r="P93">
-        <v>-7316.635339113198</v>
+        <v>-6569.66058329839</v>
       </c>
       <c r="Q93">
-        <v>2188.364660886802</v>
+        <v>2935.33941670161</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.3263085554021085</v>
+        <v>0.3244862909117724</v>
       </c>
       <c r="T93">
-        <v>5.465080416171282</v>
+        <v>5.432114528390939</v>
       </c>
       <c r="U93">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.08434698815686703</v>
+        <v>0.09046687559034602</v>
       </c>
       <c r="W93">
-        <v>0.2030338008829556</v>
+        <v>0.1880338008829556</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3373879526274681</v>
+        <v>0.3618675023613841</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2158878949563047</v>
+        <v>0.2019238911521744</v>
       </c>
       <c r="C94">
-        <v>-35476.01740931837</v>
+        <v>-33980.34947646994</v>
       </c>
       <c r="D94">
-        <v>22921.08433423452</v>
+        <v>24416.75226708296</v>
       </c>
       <c r="E94">
         <v>20659.0346309954</v>
@@ -9001,37 +9001,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M94">
-        <v>14884.60294796211</v>
+        <v>13877.69192180882</v>
       </c>
       <c r="N94">
-        <v>-9917.302947962113</v>
+        <v>-8910.391921808818</v>
       </c>
       <c r="O94">
-        <v>-2479.325736990528</v>
+        <v>-2227.597980452204</v>
       </c>
       <c r="P94">
-        <v>-7437.977210971585</v>
+        <v>-6682.793941356613</v>
       </c>
       <c r="Q94">
-        <v>2067.022789028415</v>
+        <v>2822.206058643387</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.3613721248273722</v>
+        <v>0.3593220772757441</v>
       </c>
       <c r="T94">
-        <v>6.148215468192694</v>
+        <v>6.11112884443981</v>
       </c>
       <c r="U94">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.08343017306820544</v>
+        <v>0.08948353998610314</v>
       </c>
       <c r="W94">
-        <v>0.2032370923588206</v>
+        <v>0.1882370923588206</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3337206922728218</v>
+        <v>0.3579341599444126</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.21764726112293</v>
+        <v>0.2035332573187998</v>
       </c>
       <c r="C95">
-        <v>-36381.35929125914</v>
+        <v>-34892.40821851234</v>
       </c>
       <c r="D95">
-        <v>22745.38812341933</v>
+        <v>24234.33919616613</v>
       </c>
       <c r="E95">
         <v>21388.68030212098</v>
@@ -9083,37 +9083,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M95">
-        <v>15046.39211043996</v>
+        <v>14028.53639921978</v>
       </c>
       <c r="N95">
-        <v>-10079.09211043996</v>
+        <v>-9061.236399219784</v>
       </c>
       <c r="O95">
-        <v>-2519.773027609991</v>
+        <v>-2265.309099804946</v>
       </c>
       <c r="P95">
-        <v>-7559.319082829972</v>
+        <v>-6795.927299414838</v>
       </c>
       <c r="Q95">
-        <v>1945.680917170028</v>
+        <v>2709.072700585162</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.4064538569455682</v>
+        <v>0.4041109454579934</v>
       </c>
       <c r="T95">
-        <v>7.026531963648793</v>
+        <v>6.984147250788355</v>
       </c>
       <c r="U95">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.08253307443306344</v>
+        <v>0.08852135138410203</v>
       </c>
       <c r="W95">
-        <v>0.2034360119749895</v>
+        <v>0.1884360119749895</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3301322977322537</v>
+        <v>0.3540854055364081</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2194066272895553</v>
+        <v>0.2051426234854251</v>
       </c>
       <c r="C96">
-        <v>-37284.02814624408</v>
+        <v>-35801.76162254963</v>
       </c>
       <c r="D96">
-        <v>22572.36493955997</v>
+        <v>24054.63146325441</v>
       </c>
       <c r="E96">
         <v>22118.32597324655</v>
@@ -9165,37 +9165,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M96">
-        <v>15208.18127291781</v>
+        <v>14179.38087663075</v>
       </c>
       <c r="N96">
-        <v>-10240.88127291781</v>
+        <v>-9212.080876630749</v>
       </c>
       <c r="O96">
-        <v>-2560.220318229452</v>
+        <v>-2303.020219157687</v>
       </c>
       <c r="P96">
-        <v>-7680.660954688357</v>
+        <v>-6909.060657473062</v>
       </c>
       <c r="Q96">
-        <v>1824.339045311643</v>
+        <v>2595.939342526938</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.466562833103163</v>
+        <v>0.463829436367659</v>
       </c>
       <c r="T96">
-        <v>8.197620624256928</v>
+        <v>8.148171792586416</v>
       </c>
       <c r="U96">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.08165506300292448</v>
+        <v>0.08757963488001584</v>
       </c>
       <c r="W96">
-        <v>0.2036306992588996</v>
+        <v>0.1886306992588996</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3266202520116979</v>
+        <v>0.3503185395200633</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2211659934561807</v>
+        <v>0.2067519896520504</v>
       </c>
       <c r="C97">
-        <v>-38184.08451454733</v>
+        <v>-36708.46942920914</v>
       </c>
       <c r="D97">
-        <v>22401.95424238229</v>
+        <v>23877.56932772047</v>
       </c>
       <c r="E97">
         <v>22847.97164437213</v>
@@ -9247,37 +9247,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M97">
-        <v>15369.97043539566</v>
+        <v>14330.22535404171</v>
       </c>
       <c r="N97">
-        <v>-10402.67043539566</v>
+        <v>-9362.925354041714</v>
       </c>
       <c r="O97">
-        <v>-2600.667608848915</v>
+        <v>-2340.731338510428</v>
       </c>
       <c r="P97">
-        <v>-7802.002826546744</v>
+        <v>-7022.194015531286</v>
       </c>
       <c r="Q97">
-        <v>1702.997173453256</v>
+        <v>2482.805984468714</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.5507153997237959</v>
+        <v>0.5474353236411909</v>
       </c>
       <c r="T97">
-        <v>9.837144749108319</v>
+        <v>9.777806151103702</v>
       </c>
       <c r="U97">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.08079553602394632</v>
+        <v>0.08665774398654198</v>
       </c>
       <c r="W97">
-        <v>0.2038212878631484</v>
+        <v>0.1888212878631483</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3231821440957853</v>
+        <v>0.346630975946168</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.222925359622806</v>
+        <v>0.2083613558186758</v>
       </c>
       <c r="C98">
-        <v>-39081.58712193974</v>
+        <v>-37612.5896330078</v>
       </c>
       <c r="D98">
-        <v>22234.09730611545</v>
+        <v>23703.0947950474</v>
       </c>
       <c r="E98">
         <v>23577.6173154977</v>
@@ -9329,37 +9329,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M98">
-        <v>15531.75959787351</v>
+        <v>14481.06983145268</v>
       </c>
       <c r="N98">
-        <v>-10564.45959787351</v>
+        <v>-9513.769831452679</v>
       </c>
       <c r="O98">
-        <v>-2641.114899468377</v>
+        <v>-2378.44245786317</v>
       </c>
       <c r="P98">
-        <v>-7923.344698405132</v>
+        <v>-7135.327373589509</v>
       </c>
       <c r="Q98">
-        <v>1581.655301594868</v>
+        <v>2369.672626410491</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.6769442496547434</v>
+        <v>0.6728441545514873</v>
       </c>
       <c r="T98">
-        <v>12.29643093638537</v>
+        <v>12.2222576888796</v>
       </c>
       <c r="U98">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.07995391585703021</v>
+        <v>0.08575505915334884</v>
       </c>
       <c r="W98">
-        <v>0.2040079058714753</v>
+        <v>0.1890079058714753</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3198156634281208</v>
+        <v>0.3430202366133954</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2246847257894314</v>
+        <v>0.2099707219853011</v>
       </c>
       <c r="C99">
-        <v>-39976.59294716327</v>
+        <v>-38514.17854568391</v>
       </c>
       <c r="D99">
-        <v>22068.73715201749</v>
+        <v>23531.15155349686</v>
       </c>
       <c r="E99">
         <v>24307.26298662327</v>
@@ -9411,37 +9411,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M99">
-        <v>15693.54876035136</v>
+        <v>14631.91430886364</v>
       </c>
       <c r="N99">
-        <v>-10726.24876035136</v>
+        <v>-9664.614308863645</v>
       </c>
       <c r="O99">
-        <v>-2681.562190087839</v>
+        <v>-2416.153577215911</v>
       </c>
       <c r="P99">
-        <v>-8044.686570263517</v>
+        <v>-7248.460731647734</v>
       </c>
       <c r="Q99">
-        <v>1460.313429736483</v>
+        <v>2256.539268352266</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.8873256662063246</v>
+        <v>0.8818588727353165</v>
       </c>
       <c r="T99">
-        <v>16.39524124851383</v>
+        <v>16.2963435851728</v>
       </c>
       <c r="U99">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.0791296486832464</v>
+        <v>0.08487098637857204</v>
       </c>
       <c r="W99">
-        <v>0.2041906760858161</v>
+        <v>0.1891906760858161</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3165185947329856</v>
+        <v>0.3394839455142882</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2264440919560567</v>
+        <v>0.2115800881519265</v>
       </c>
       <c r="C100">
-        <v>-40869.15728641672</v>
+        <v>-39413.29085679233</v>
       </c>
       <c r="D100">
-        <v>21905.81848388961</v>
+        <v>23361.68491351401</v>
       </c>
       <c r="E100">
         <v>25036.90865774885</v>
@@ -9493,37 +9493,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M100">
-        <v>15855.33792282921</v>
+        <v>14782.75878627461</v>
       </c>
       <c r="N100">
-        <v>-10888.03792282921</v>
+        <v>-9815.45878627461</v>
       </c>
       <c r="O100">
-        <v>-2722.009480707301</v>
+        <v>-2453.864696568653</v>
       </c>
       <c r="P100">
-        <v>-8166.028442121904</v>
+        <v>-7361.594089705957</v>
       </c>
       <c r="Q100">
-        <v>1338.971557878096</v>
+        <v>2143.405910294043</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.308088499309487</v>
+        <v>1.299888309102975</v>
       </c>
       <c r="T100">
-        <v>24.59286187277074</v>
+        <v>24.4445153777592</v>
       </c>
       <c r="U100">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.0783222032885194</v>
+        <v>0.08400495590532131</v>
       </c>
       <c r="W100">
-        <v>0.2043697162957826</v>
+        <v>0.1893697162957826</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3132888131540775</v>
+        <v>0.3360198236212852</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2282034581226821</v>
+        <v>0.2131894543185518</v>
       </c>
       <c r="C101">
-        <v>-41759.33381500602</v>
+        <v>-40309.97969170005</v>
       </c>
       <c r="D101">
-        <v>21745.28762642589</v>
+        <v>23194.64174973187</v>
       </c>
       <c r="E101">
         <v>25766.55432887442</v>
@@ -9575,37 +9575,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M101">
-        <v>16017.12708530705</v>
+        <v>14933.60326368557</v>
       </c>
       <c r="N101">
-        <v>-11049.82708530706</v>
+        <v>-9966.303263685575</v>
       </c>
       <c r="O101">
-        <v>-2762.456771326764</v>
+        <v>-2491.575815921394</v>
       </c>
       <c r="P101">
-        <v>-8287.370313980291</v>
+        <v>-7474.727447764181</v>
       </c>
       <c r="Q101">
-        <v>1217.629686019709</v>
+        <v>2030.272552235819</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>2.570376998618974</v>
+        <v>2.553976618205949</v>
       </c>
       <c r="T101">
-        <v>49.18572374554148</v>
+        <v>48.8890307555184</v>
       </c>
       <c r="U101">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V101">
-        <v>0.07753106992196869</v>
+        <v>0.08315642099718676</v>
       </c>
       <c r="W101">
-        <v>0.2045451395318104</v>
+        <v>0.1895451395318104</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3101242796878748</v>
+        <v>0.332625683988747</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/france/france_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/france/france_telecom_services.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07313185743077678</v>
+        <v>0.07302730241216886</v>
       </c>
       <c r="C2">
-        <v>70135.06109867145</v>
+        <v>69481.02301867792</v>
       </c>
       <c r="D2">
-        <v>61404.76109867144</v>
+        <v>61480.36868980349</v>
       </c>
       <c r="E2">
-        <v>-46468.36711255749</v>
+        <v>-45738.72144143192</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>729.6456711255749</v>
       </c>
       <c r="G2">
         <v>8730.299999999999</v>
@@ -1457,28 +1457,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>41.03280390656639</v>
       </c>
       <c r="N2">
-        <v>4967.299999999999</v>
+        <v>4926.267196093433</v>
       </c>
       <c r="O2">
-        <v>1241.825</v>
+        <v>1231.566799023358</v>
       </c>
       <c r="P2">
-        <v>3725.474999999999</v>
+        <v>3694.700397070075</v>
       </c>
       <c r="Q2">
-        <v>13230.475</v>
+        <v>13199.70039707008</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07313185743077678</v>
+        <v>0.07333891695676753</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5367847496465754</v>
       </c>
       <c r="U2">
         <v>0.0562366166625341</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>121.0568015607896</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07302730241216886</v>
+        <v>0.07292274739356092</v>
       </c>
       <c r="C3">
-        <v>69481.02301867792</v>
+        <v>68827.17135925309</v>
       </c>
       <c r="D3">
-        <v>61480.36868980349</v>
+        <v>61556.16270150424</v>
       </c>
       <c r="E3">
-        <v>-45738.72144143192</v>
+        <v>-45009.07577030634</v>
       </c>
       <c r="F3">
-        <v>729.6456711255749</v>
+        <v>1459.29134225115</v>
       </c>
       <c r="G3">
         <v>8730.299999999999</v>
@@ -1539,28 +1539,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M3">
-        <v>41.03280390656639</v>
+        <v>82.06560781313277</v>
       </c>
       <c r="N3">
-        <v>4926.267196093433</v>
+        <v>4885.234392186867</v>
       </c>
       <c r="O3">
-        <v>1231.566799023358</v>
+        <v>1221.308598046717</v>
       </c>
       <c r="P3">
-        <v>3694.700397070075</v>
+        <v>3663.92579414015</v>
       </c>
       <c r="Q3">
-        <v>13199.70039707008</v>
+        <v>13168.92579414015</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07333891695676753</v>
+        <v>0.07355020218737031</v>
       </c>
       <c r="T3">
-        <v>0.5367847496465754</v>
+        <v>0.5409030920560167</v>
       </c>
       <c r="U3">
         <v>0.0562366166625341</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>121.0568015607896</v>
+        <v>60.5284007803948</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07292274739356092</v>
+        <v>0.07281819237495298</v>
       </c>
       <c r="C4">
-        <v>68827.17135925309</v>
+        <v>68173.50681071503</v>
       </c>
       <c r="D4">
-        <v>61556.16270150424</v>
+        <v>61632.14382409175</v>
       </c>
       <c r="E4">
-        <v>-45009.07577030634</v>
+        <v>-44279.43009918077</v>
       </c>
       <c r="F4">
-        <v>1459.29134225115</v>
+        <v>2188.937013376725</v>
       </c>
       <c r="G4">
         <v>8730.299999999999</v>
@@ -1621,28 +1621,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M4">
-        <v>82.06560781313277</v>
+        <v>123.0984117196991</v>
       </c>
       <c r="N4">
-        <v>4885.234392186867</v>
+        <v>4844.2015882803</v>
       </c>
       <c r="O4">
-        <v>1221.308598046717</v>
+        <v>1211.050397070075</v>
       </c>
       <c r="P4">
-        <v>3663.92579414015</v>
+        <v>3633.151191210225</v>
       </c>
       <c r="Q4">
-        <v>13168.92579414015</v>
+        <v>13138.15119121023</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07355020218737031</v>
+        <v>0.07376584381448037</v>
       </c>
       <c r="T4">
-        <v>0.5409030920560167</v>
+        <v>0.5451063487419412</v>
       </c>
       <c r="U4">
         <v>0.0562366166625341</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>60.5284007803948</v>
+        <v>40.35226718692987</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07281819237495298</v>
+        <v>0.07271363735634505</v>
       </c>
       <c r="C5">
-        <v>68173.50681071503</v>
+        <v>67520.03006679435</v>
       </c>
       <c r="D5">
-        <v>61632.14382409175</v>
+        <v>61708.31275129665</v>
       </c>
       <c r="E5">
-        <v>-44279.43009918077</v>
+        <v>-43549.78442805519</v>
       </c>
       <c r="F5">
-        <v>2188.937013376725</v>
+        <v>2918.5826845023</v>
       </c>
       <c r="G5">
         <v>8730.299999999999</v>
@@ -1703,28 +1703,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M5">
-        <v>123.0984117196991</v>
+        <v>164.1312156262655</v>
       </c>
       <c r="N5">
-        <v>4844.2015882803</v>
+        <v>4803.168784373734</v>
       </c>
       <c r="O5">
-        <v>1211.050397070075</v>
+        <v>1200.792196093433</v>
       </c>
       <c r="P5">
-        <v>3633.151191210225</v>
+        <v>3602.3765882803</v>
       </c>
       <c r="Q5">
-        <v>13138.15119121023</v>
+        <v>13107.3765882803</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07376584381448037</v>
+        <v>0.07398597797548856</v>
       </c>
       <c r="T5">
-        <v>0.5451063487419412</v>
+        <v>0.5493971732754893</v>
       </c>
       <c r="U5">
         <v>0.0562366166625341</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>40.35226718692987</v>
+        <v>30.2642003901974</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07271363735634505</v>
+        <v>0.07260908233773712</v>
       </c>
       <c r="C6">
-        <v>67520.03006679435</v>
+        <v>66866.74182465539</v>
       </c>
       <c r="D6">
-        <v>61708.31275129665</v>
+        <v>61784.67018028326</v>
       </c>
       <c r="E6">
-        <v>-43549.78442805519</v>
+        <v>-42820.13875692962</v>
       </c>
       <c r="F6">
-        <v>2918.5826845023</v>
+        <v>3648.228355627874</v>
       </c>
       <c r="G6">
         <v>8730.299999999999</v>
@@ -1785,28 +1785,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M6">
-        <v>164.1312156262655</v>
+        <v>205.1640195328319</v>
       </c>
       <c r="N6">
-        <v>4803.168784373734</v>
+        <v>4762.135980467167</v>
       </c>
       <c r="O6">
-        <v>1200.792196093433</v>
+        <v>1190.533995116792</v>
       </c>
       <c r="P6">
-        <v>3602.3765882803</v>
+        <v>3571.601985350376</v>
       </c>
       <c r="Q6">
-        <v>13107.3765882803</v>
+        <v>13076.60198535037</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07398597797548856</v>
+        <v>0.07421074653988641</v>
       </c>
       <c r="T6">
-        <v>0.5493971732754893</v>
+        <v>0.553778330957112</v>
       </c>
       <c r="U6">
         <v>0.0562366166625341</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>30.2642003901974</v>
+        <v>24.21136031215793</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07260908233773712</v>
+        <v>0.07250452731912917</v>
       </c>
       <c r="C7">
-        <v>66866.74182465539</v>
+        <v>66213.64278491741</v>
       </c>
       <c r="D7">
-        <v>61784.67018028326</v>
+        <v>61861.21681167086</v>
       </c>
       <c r="E7">
-        <v>-42820.13875692962</v>
+        <v>-42090.49308580404</v>
       </c>
       <c r="F7">
-        <v>3648.228355627874</v>
+        <v>4377.874026753449</v>
       </c>
       <c r="G7">
         <v>8730.299999999999</v>
@@ -1867,28 +1867,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M7">
-        <v>205.1640195328319</v>
+        <v>246.1968234393983</v>
       </c>
       <c r="N7">
-        <v>4762.135980467167</v>
+        <v>4721.103176560601</v>
       </c>
       <c r="O7">
-        <v>1190.533995116792</v>
+        <v>1180.27579414015</v>
       </c>
       <c r="P7">
-        <v>3571.601985350376</v>
+        <v>3540.827382420451</v>
       </c>
       <c r="Q7">
-        <v>13076.60198535037</v>
+        <v>13045.82738242045</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07421074653988641</v>
+        <v>0.07444029741416504</v>
       </c>
       <c r="T7">
-        <v>0.553778330957112</v>
+        <v>0.5582527047596203</v>
       </c>
       <c r="U7">
         <v>0.0562366166625341</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.21136031215793</v>
+        <v>20.17613359346494</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07250452731912915</v>
+        <v>0.07239997230052123</v>
       </c>
       <c r="C8">
-        <v>66213.64278491742</v>
+        <v>65560.733651676</v>
       </c>
       <c r="D8">
-        <v>61861.21681167086</v>
+        <v>61937.95334955502</v>
       </c>
       <c r="E8">
-        <v>-42090.49308580404</v>
+        <v>-41360.84741467846</v>
       </c>
       <c r="F8">
-        <v>4377.874026753449</v>
+        <v>5107.519697879024</v>
       </c>
       <c r="G8">
         <v>8730.299999999999</v>
@@ -1949,28 +1949,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M8">
-        <v>246.1968234393983</v>
+        <v>287.2296273459646</v>
       </c>
       <c r="N8">
-        <v>4721.103176560601</v>
+        <v>4680.070372654035</v>
       </c>
       <c r="O8">
-        <v>1180.27579414015</v>
+        <v>1170.017593163509</v>
       </c>
       <c r="P8">
-        <v>3540.827382420451</v>
+        <v>3510.052779490527</v>
       </c>
       <c r="Q8">
-        <v>13045.82738242045</v>
+        <v>13015.05277949053</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07444029741416504</v>
+        <v>0.07467478486638515</v>
       </c>
       <c r="T8">
-        <v>0.5582527047596203</v>
+        <v>0.5628233016546557</v>
       </c>
       <c r="U8">
         <v>0.0562366166625341</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.17613359346494</v>
+        <v>17.29382879439852</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07239997230052123</v>
+        <v>0.0722954172819133</v>
       </c>
       <c r="C9">
-        <v>65560.733651676</v>
+        <v>64908.01513252472</v>
       </c>
       <c r="D9">
-        <v>61937.95334955502</v>
+        <v>62014.88050152932</v>
       </c>
       <c r="E9">
-        <v>-41360.84741467846</v>
+        <v>-40631.20174355289</v>
       </c>
       <c r="F9">
-        <v>5107.519697879025</v>
+        <v>5837.1653690046</v>
       </c>
       <c r="G9">
         <v>8730.299999999999</v>
@@ -2031,28 +2031,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M9">
-        <v>287.2296273459647</v>
+        <v>328.2624312525311</v>
       </c>
       <c r="N9">
-        <v>4680.070372654034</v>
+        <v>4639.037568747468</v>
       </c>
       <c r="O9">
-        <v>1170.017593163509</v>
+        <v>1159.759392186867</v>
       </c>
       <c r="P9">
-        <v>3510.052779490526</v>
+        <v>3479.278176560601</v>
       </c>
       <c r="Q9">
-        <v>13015.05277949052</v>
+        <v>12984.2781765606</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07467478486638515</v>
+        <v>0.07491436987191441</v>
       </c>
       <c r="T9">
-        <v>0.5628233016546557</v>
+        <v>0.5674932593517571</v>
       </c>
       <c r="U9">
         <v>0.0562366166625341</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.29382879439851</v>
+        <v>15.1321001950987</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0722954172819133</v>
+        <v>0.07219086226330536</v>
       </c>
       <c r="C10">
-        <v>64908.01513252472</v>
+        <v>64255.48793857689</v>
       </c>
       <c r="D10">
-        <v>62014.88050152932</v>
+        <v>62091.99897870707</v>
       </c>
       <c r="E10">
-        <v>-40631.20174355289</v>
+        <v>-39901.55607242732</v>
       </c>
       <c r="F10">
-        <v>5837.1653690046</v>
+        <v>6566.811040130174</v>
       </c>
       <c r="G10">
         <v>8730.299999999999</v>
@@ -2113,28 +2113,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M10">
-        <v>328.2624312525311</v>
+        <v>369.2952351590974</v>
       </c>
       <c r="N10">
-        <v>4639.037568747468</v>
+        <v>4598.004764840902</v>
       </c>
       <c r="O10">
-        <v>1159.759392186867</v>
+        <v>1149.501191210225</v>
       </c>
       <c r="P10">
-        <v>3479.278176560601</v>
+        <v>3448.503573630676</v>
       </c>
       <c r="Q10">
-        <v>12984.2781765606</v>
+        <v>12953.50357363068</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07491436987191441</v>
+        <v>0.07515922048196078</v>
       </c>
       <c r="T10">
-        <v>0.5674932593517571</v>
+        <v>0.5722658534817617</v>
       </c>
       <c r="U10">
         <v>0.0562366166625341</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.1321001950987</v>
+        <v>13.45075572897663</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07219086226330536</v>
+        <v>0.07208630724469743</v>
       </c>
       <c r="C11">
-        <v>64255.48793857689</v>
+        <v>63603.15278448737</v>
       </c>
       <c r="D11">
-        <v>62091.99897870707</v>
+        <v>62169.30949574312</v>
       </c>
       <c r="E11">
-        <v>-39901.55607242732</v>
+        <v>-39171.91040130174</v>
       </c>
       <c r="F11">
-        <v>6566.811040130174</v>
+        <v>7296.456711255748</v>
       </c>
       <c r="G11">
         <v>8730.299999999999</v>
@@ -2195,28 +2195,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M11">
-        <v>369.2952351590974</v>
+        <v>410.3280390656637</v>
       </c>
       <c r="N11">
-        <v>4598.004764840902</v>
+        <v>4556.971960934336</v>
       </c>
       <c r="O11">
-        <v>1149.501191210225</v>
+        <v>1139.242990233584</v>
       </c>
       <c r="P11">
-        <v>3448.503573630676</v>
+        <v>3417.728970700752</v>
       </c>
       <c r="Q11">
-        <v>12953.50357363068</v>
+        <v>12922.72897070075</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07515922048196078</v>
+        <v>0.07540951221667486</v>
       </c>
       <c r="T11">
-        <v>0.5722658534817617</v>
+        <v>0.5771445052590998</v>
       </c>
       <c r="U11">
         <v>0.0562366166625341</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>13.45075572897663</v>
+        <v>12.10568015607896</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07208630724469743</v>
+        <v>0.07198175222608949</v>
       </c>
       <c r="C12">
-        <v>63603.15278448737</v>
+        <v>62951.0103884748</v>
       </c>
       <c r="D12">
-        <v>62169.30949574312</v>
+        <v>62246.81277085612</v>
       </c>
       <c r="E12">
-        <v>-39171.91040130174</v>
+        <v>-38442.26473017617</v>
       </c>
       <c r="F12">
-        <v>7296.456711255749</v>
+        <v>8026.102382381324</v>
       </c>
       <c r="G12">
         <v>8730.299999999999</v>
@@ -2277,28 +2277,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M12">
-        <v>410.3280390656638</v>
+        <v>451.3608429722302</v>
       </c>
       <c r="N12">
-        <v>4556.971960934336</v>
+        <v>4515.939157027769</v>
       </c>
       <c r="O12">
-        <v>1139.242990233584</v>
+        <v>1128.984789256942</v>
       </c>
       <c r="P12">
-        <v>3417.728970700752</v>
+        <v>3386.954367770827</v>
       </c>
       <c r="Q12">
-        <v>12922.72897070075</v>
+        <v>12891.95436777083</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07540951221667486</v>
+        <v>0.07566542848475329</v>
       </c>
       <c r="T12">
-        <v>0.5771445052590998</v>
+        <v>0.5821327896606479</v>
       </c>
       <c r="U12">
         <v>0.0562366166625341</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>12.10568015607896</v>
+        <v>11.0051637782536</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07198175222608949</v>
+        <v>0.07187719720748155</v>
       </c>
       <c r="C13">
-        <v>62951.0103884748</v>
+        <v>62299.06147234367</v>
       </c>
       <c r="D13">
-        <v>62246.81277085612</v>
+        <v>62324.50952585057</v>
       </c>
       <c r="E13">
-        <v>-38442.26473017617</v>
+        <v>-37712.61905905059</v>
       </c>
       <c r="F13">
-        <v>8026.102382381324</v>
+        <v>8755.748053506899</v>
       </c>
       <c r="G13">
         <v>8730.299999999999</v>
@@ -2359,28 +2359,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M13">
-        <v>451.3608429722302</v>
+        <v>492.3936468787966</v>
       </c>
       <c r="N13">
-        <v>4515.939157027769</v>
+        <v>4474.906353121202</v>
       </c>
       <c r="O13">
-        <v>1128.984789256942</v>
+        <v>1118.726588280301</v>
       </c>
       <c r="P13">
-        <v>3386.954367770827</v>
+        <v>3356.179764840902</v>
       </c>
       <c r="Q13">
-        <v>12891.95436777083</v>
+        <v>12861.1797648409</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07566542848475329</v>
+        <v>0.07592716103165169</v>
       </c>
       <c r="T13">
-        <v>0.5821327896606479</v>
+        <v>0.587234444162231</v>
       </c>
       <c r="U13">
         <v>0.0562366166625341</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.0051637782536</v>
+        <v>10.08806679673247</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07187719720748155</v>
+        <v>0.07177264218887362</v>
       </c>
       <c r="C14">
-        <v>62299.06147234367</v>
+        <v>61647.30676150685</v>
       </c>
       <c r="D14">
-        <v>62324.50952585057</v>
+        <v>62402.40048613933</v>
       </c>
       <c r="E14">
-        <v>-37712.61905905059</v>
+        <v>-36982.97338792502</v>
       </c>
       <c r="F14">
-        <v>8755.748053506899</v>
+        <v>9485.393724632473</v>
       </c>
       <c r="G14">
         <v>8730.299999999999</v>
@@ -2441,28 +2441,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M14">
-        <v>492.3936468787966</v>
+        <v>533.4264507853629</v>
       </c>
       <c r="N14">
-        <v>4474.906353121202</v>
+        <v>4433.873549214636</v>
       </c>
       <c r="O14">
-        <v>1118.726588280301</v>
+        <v>1108.468387303659</v>
       </c>
       <c r="P14">
-        <v>3356.179764840902</v>
+        <v>3325.405161910977</v>
       </c>
       <c r="Q14">
-        <v>12861.1797648409</v>
+        <v>12830.40516191098</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07592716103165169</v>
+        <v>0.07619491041870867</v>
       </c>
       <c r="T14">
-        <v>0.587234444162231</v>
+        <v>0.5924533780776436</v>
       </c>
       <c r="U14">
         <v>0.0562366166625341</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.08806679673247</v>
+        <v>9.312061658522278</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07177264218887362</v>
+        <v>0.07182558717026569</v>
       </c>
       <c r="C15">
-        <v>61647.30676150685</v>
+        <v>60878.19404269052</v>
       </c>
       <c r="D15">
-        <v>62402.40048613933</v>
+        <v>62362.93343844858</v>
       </c>
       <c r="E15">
-        <v>-36982.97338792502</v>
+        <v>-36253.32771679944</v>
       </c>
       <c r="F15">
-        <v>9485.393724632473</v>
+        <v>10215.03939575805</v>
       </c>
       <c r="G15">
         <v>8730.299999999999</v>
@@ -2523,45 +2523,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M15">
-        <v>533.4264507853629</v>
+        <v>589.7818137855664</v>
       </c>
       <c r="N15">
-        <v>4433.873549214636</v>
+        <v>4377.518186214433</v>
       </c>
       <c r="O15">
-        <v>1108.468387303659</v>
+        <v>1094.379546553608</v>
       </c>
       <c r="P15">
-        <v>3325.405161910977</v>
+        <v>3283.138639660825</v>
       </c>
       <c r="Q15">
-        <v>12830.40516191098</v>
+        <v>12788.13863966082</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07619491041870867</v>
+        <v>0.07646888653569721</v>
       </c>
       <c r="T15">
-        <v>0.5924533780776436</v>
+        <v>0.5977936825492287</v>
       </c>
       <c r="U15">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.04217746249690058</v>
+        <v>0.04330246249690057</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>9.312061658522278</v>
+        <v>8.422267156928672</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07182558717026569</v>
+        <v>0.07173228215165774</v>
       </c>
       <c r="C16">
-        <v>60878.19404269052</v>
+        <v>60218.13477839353</v>
       </c>
       <c r="D16">
-        <v>62362.93343844858</v>
+        <v>62432.51984527717</v>
       </c>
       <c r="E16">
-        <v>-36253.32771679944</v>
+        <v>-35523.68204567386</v>
       </c>
       <c r="F16">
-        <v>10215.03939575805</v>
+        <v>10944.68506688363</v>
       </c>
       <c r="G16">
         <v>8730.299999999999</v>
@@ -2605,28 +2605,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M16">
-        <v>589.7818137855664</v>
+        <v>631.9090861988212</v>
       </c>
       <c r="N16">
-        <v>4377.518186214433</v>
+        <v>4335.390913801178</v>
       </c>
       <c r="O16">
-        <v>1094.379546553608</v>
+        <v>1083.847728450294</v>
       </c>
       <c r="P16">
-        <v>3283.138639660825</v>
+        <v>3251.543185350884</v>
       </c>
       <c r="Q16">
-        <v>12788.13863966082</v>
+        <v>12756.54318535088</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07646888653569721</v>
+        <v>0.07674930914955606</v>
       </c>
       <c r="T16">
-        <v>0.5977936825492287</v>
+        <v>0.6032596412436745</v>
       </c>
       <c r="U16">
         <v>0.05773661666253409</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.422267156928672</v>
+        <v>7.860782679800095</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07173228215165774</v>
+        <v>0.07163897713304981</v>
       </c>
       <c r="C17">
-        <v>60218.13477839353</v>
+        <v>59558.23098071523</v>
       </c>
       <c r="D17">
-        <v>62432.51984527717</v>
+        <v>62502.26171872443</v>
       </c>
       <c r="E17">
-        <v>-35523.68204567386</v>
+        <v>-34794.03637454829</v>
       </c>
       <c r="F17">
-        <v>10944.68506688362</v>
+        <v>11674.3307380092</v>
       </c>
       <c r="G17">
         <v>8730.299999999999</v>
@@ -2687,28 +2687,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M17">
-        <v>631.9090861988211</v>
+        <v>674.0363586120759</v>
       </c>
       <c r="N17">
-        <v>4335.390913801179</v>
+        <v>4293.263641387924</v>
       </c>
       <c r="O17">
-        <v>1083.847728450295</v>
+        <v>1073.315910346981</v>
       </c>
       <c r="P17">
-        <v>3251.543185350884</v>
+        <v>3219.947731040943</v>
       </c>
       <c r="Q17">
-        <v>12756.54318535088</v>
+        <v>12724.94773104094</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07674930914955606</v>
+        <v>0.07703640849231633</v>
       </c>
       <c r="T17">
-        <v>0.6032596412436745</v>
+        <v>0.6088557418117976</v>
       </c>
       <c r="U17">
         <v>0.05773661666253409</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.860782679800097</v>
+        <v>7.369483762312591</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07163897713304981</v>
+        <v>0.07154567211444186</v>
       </c>
       <c r="C18">
-        <v>59558.23098071523</v>
+        <v>58898.48317124242</v>
       </c>
       <c r="D18">
-        <v>62502.26171872443</v>
+        <v>62572.15958037719</v>
       </c>
       <c r="E18">
-        <v>-34794.03637454829</v>
+        <v>-34064.39070342272</v>
       </c>
       <c r="F18">
-        <v>11674.3307380092</v>
+        <v>12403.97640913477</v>
       </c>
       <c r="G18">
         <v>8730.299999999999</v>
@@ -2769,28 +2769,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M18">
-        <v>674.0363586120759</v>
+        <v>716.1636310253306</v>
       </c>
       <c r="N18">
-        <v>4293.263641387924</v>
+        <v>4251.136368974669</v>
       </c>
       <c r="O18">
-        <v>1073.315910346981</v>
+        <v>1062.784092243667</v>
       </c>
       <c r="P18">
-        <v>3219.947731040943</v>
+        <v>3188.352276731001</v>
       </c>
       <c r="Q18">
-        <v>12724.94773104094</v>
+        <v>12693.352276731</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07703640849231633</v>
+        <v>0.07733042589152865</v>
       </c>
       <c r="T18">
-        <v>0.6088557418117976</v>
+        <v>0.6145866881767431</v>
       </c>
       <c r="U18">
         <v>0.05773661666253409</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.369483762312591</v>
+        <v>6.935984717470673</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07154567211444186</v>
+        <v>0.07168186709583393</v>
       </c>
       <c r="C19">
-        <v>58898.48317124242</v>
+        <v>58066.8617188387</v>
       </c>
       <c r="D19">
-        <v>62572.15958037719</v>
+        <v>62470.18379909905</v>
       </c>
       <c r="E19">
-        <v>-34064.39070342272</v>
+        <v>-33334.74503229714</v>
       </c>
       <c r="F19">
-        <v>12403.97640913477</v>
+        <v>13133.62208026035</v>
       </c>
       <c r="G19">
         <v>8730.299999999999</v>
@@ -2851,45 +2851,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M19">
-        <v>716.1636310253306</v>
+        <v>780.618060975028</v>
       </c>
       <c r="N19">
-        <v>4251.136368974669</v>
+        <v>4186.681939024971</v>
       </c>
       <c r="O19">
-        <v>1062.784092243667</v>
+        <v>1046.670484756243</v>
       </c>
       <c r="P19">
-        <v>3188.352276731001</v>
+        <v>3140.011454268728</v>
       </c>
       <c r="Q19">
-        <v>12693.352276731</v>
+        <v>12645.01145426873</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07733042589152865</v>
+        <v>0.07763161444681931</v>
       </c>
       <c r="T19">
-        <v>0.6145866881767431</v>
+        <v>0.6204574137213212</v>
       </c>
       <c r="U19">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.04330246249690057</v>
+        <v>0.04457746249690057</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.935984717470673</v>
+        <v>6.363291151367434</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07168186709583393</v>
+        <v>0.07160131207722602</v>
       </c>
       <c r="C20">
-        <v>58066.8617188387</v>
+        <v>57397.49129650288</v>
       </c>
       <c r="D20">
-        <v>62470.18379909905</v>
+        <v>62530.4590478888</v>
       </c>
       <c r="E20">
-        <v>-33334.74503229714</v>
+        <v>-32605.09936117157</v>
       </c>
       <c r="F20">
-        <v>13133.62208026035</v>
+        <v>13863.26775138592</v>
       </c>
       <c r="G20">
         <v>8730.299999999999</v>
@@ -2933,28 +2933,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M20">
-        <v>780.6180609750279</v>
+        <v>823.9857310291961</v>
       </c>
       <c r="N20">
-        <v>4186.681939024971</v>
+        <v>4143.314268970803</v>
       </c>
       <c r="O20">
-        <v>1046.670484756243</v>
+        <v>1035.828567242701</v>
       </c>
       <c r="P20">
-        <v>3140.011454268728</v>
+        <v>3107.485701728102</v>
       </c>
       <c r="Q20">
-        <v>12645.01145426873</v>
+        <v>12612.4857017281</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07763161444681931</v>
+        <v>0.0779402397565616</v>
       </c>
       <c r="T20">
-        <v>0.6204574137213212</v>
+        <v>0.6264730954521854</v>
       </c>
       <c r="U20">
         <v>0.05943661666253409</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.363291151367434</v>
+        <v>6.028381090769148</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07160131207722602</v>
+        <v>0.07152075705861807</v>
       </c>
       <c r="C21">
-        <v>57397.49129650288</v>
+        <v>56728.23730137234</v>
       </c>
       <c r="D21">
-        <v>62530.4590478888</v>
+        <v>62590.85072388384</v>
       </c>
       <c r="E21">
-        <v>-32605.09936117157</v>
+        <v>-31875.45369004599</v>
       </c>
       <c r="F21">
-        <v>13863.26775138592</v>
+        <v>14592.9134225115</v>
       </c>
       <c r="G21">
         <v>8730.299999999999</v>
@@ -3015,28 +3015,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M21">
-        <v>823.9857310291961</v>
+        <v>867.3534010833644</v>
       </c>
       <c r="N21">
-        <v>4143.314268970803</v>
+        <v>4099.946598916635</v>
       </c>
       <c r="O21">
-        <v>1035.828567242701</v>
+        <v>1024.986649729159</v>
       </c>
       <c r="P21">
-        <v>3107.485701728102</v>
+        <v>3074.959949187476</v>
       </c>
       <c r="Q21">
-        <v>12612.4857017281</v>
+        <v>12579.95994918748</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0779402397565616</v>
+        <v>0.07825658069904744</v>
       </c>
       <c r="T21">
-        <v>0.6264730954521854</v>
+        <v>0.632639169226321</v>
       </c>
       <c r="U21">
         <v>0.05943661666253409</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.028381090769148</v>
+        <v>5.726962036230691</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07152075705861807</v>
+        <v>0.07156620204001013</v>
       </c>
       <c r="C22">
-        <v>56728.23730137234</v>
+        <v>55964.50743177069</v>
       </c>
       <c r="D22">
-        <v>62590.85072388384</v>
+        <v>62556.76652540777</v>
       </c>
       <c r="E22">
-        <v>-31875.45369004599</v>
+        <v>-31145.80801892042</v>
       </c>
       <c r="F22">
-        <v>14592.9134225115</v>
+        <v>15322.55909363707</v>
       </c>
       <c r="G22">
         <v>8730.299999999999</v>
@@ -3097,45 +3097,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M22">
-        <v>867.3534010833644</v>
+        <v>922.9791184124423</v>
       </c>
       <c r="N22">
-        <v>4099.946598916635</v>
+        <v>4044.320881587557</v>
       </c>
       <c r="O22">
-        <v>1024.986649729159</v>
+        <v>1011.080220396889</v>
       </c>
       <c r="P22">
-        <v>3074.959949187476</v>
+        <v>3033.240661190668</v>
       </c>
       <c r="Q22">
-        <v>12579.95994918748</v>
+        <v>12538.24066119067</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07825658069904744</v>
+        <v>0.07858093027298861</v>
       </c>
       <c r="T22">
-        <v>0.632639169226321</v>
+        <v>0.638961346133979</v>
       </c>
       <c r="U22">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.04457746249690057</v>
+        <v>0.04517746249690057</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>5.726962036230691</v>
+        <v>5.38181189683244</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07156620204001013</v>
+        <v>0.07149164702140219</v>
       </c>
       <c r="C23">
-        <v>55964.50743177069</v>
+        <v>55290.79830555906</v>
       </c>
       <c r="D23">
-        <v>62556.76652540777</v>
+        <v>62612.70307032171</v>
       </c>
       <c r="E23">
-        <v>-31145.80801892042</v>
+        <v>-30416.16234779485</v>
       </c>
       <c r="F23">
-        <v>15322.55909363707</v>
+        <v>16052.20476476265</v>
       </c>
       <c r="G23">
         <v>8730.299999999999</v>
@@ -3179,28 +3179,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M23">
-        <v>922.9791184124422</v>
+        <v>966.9305050035109</v>
       </c>
       <c r="N23">
-        <v>4044.320881587557</v>
+        <v>4000.369494996488</v>
       </c>
       <c r="O23">
-        <v>1011.080220396889</v>
+        <v>1000.092373749122</v>
       </c>
       <c r="P23">
-        <v>3033.240661190668</v>
+        <v>3000.277121247366</v>
       </c>
       <c r="Q23">
-        <v>12538.24066119067</v>
+        <v>12505.27712124737</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07858093027298861</v>
+        <v>0.07891359650267188</v>
       </c>
       <c r="T23">
-        <v>0.638961346133979</v>
+        <v>0.6454456301418335</v>
       </c>
       <c r="U23">
         <v>0.0602366166625341</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.38181189683244</v>
+        <v>5.137184083340057</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07149164702140219</v>
+        <v>0.07141709200279425</v>
       </c>
       <c r="C24">
-        <v>55290.79830555906</v>
+        <v>54617.18930272365</v>
       </c>
       <c r="D24">
-        <v>62612.70307032171</v>
+        <v>62668.73973861188</v>
       </c>
       <c r="E24">
-        <v>-30416.16234779485</v>
+        <v>-29686.51667666927</v>
       </c>
       <c r="F24">
-        <v>16052.20476476265</v>
+        <v>16781.85043588822</v>
       </c>
       <c r="G24">
         <v>8730.299999999999</v>
@@ -3261,28 +3261,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M24">
-        <v>966.9305050035109</v>
+        <v>1010.88189159458</v>
       </c>
       <c r="N24">
-        <v>4000.369494996488</v>
+        <v>3956.41810840542</v>
       </c>
       <c r="O24">
-        <v>1000.092373749122</v>
+        <v>989.104527101355</v>
       </c>
       <c r="P24">
-        <v>3000.277121247366</v>
+        <v>2967.313581304065</v>
       </c>
       <c r="Q24">
-        <v>12505.27712124737</v>
+        <v>12472.31358130406</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07891359650267188</v>
+        <v>0.07925490341364561</v>
       </c>
       <c r="T24">
-        <v>0.6454456301418335</v>
+        <v>0.652098337110931</v>
       </c>
       <c r="U24">
         <v>0.0602366166625341</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.137184083340057</v>
+        <v>4.913828253629619</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07141709200279425</v>
+        <v>0.07134253698418633</v>
       </c>
       <c r="C25">
-        <v>54617.18930272365</v>
+        <v>53943.68069232834</v>
       </c>
       <c r="D25">
-        <v>62668.73973861188</v>
+        <v>62724.87679934214</v>
       </c>
       <c r="E25">
-        <v>-29686.51667666927</v>
+        <v>-28956.87100554369</v>
       </c>
       <c r="F25">
-        <v>16781.85043588822</v>
+        <v>17511.4961070138</v>
       </c>
       <c r="G25">
         <v>8730.299999999999</v>
@@ -3343,28 +3343,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M25">
-        <v>1010.88189159458</v>
+        <v>1054.833278185648</v>
       </c>
       <c r="N25">
-        <v>3956.41810840542</v>
+        <v>3912.466721814351</v>
       </c>
       <c r="O25">
-        <v>989.104527101355</v>
+        <v>978.1166804535877</v>
       </c>
       <c r="P25">
-        <v>2967.313581304065</v>
+        <v>2934.350041360763</v>
       </c>
       <c r="Q25">
-        <v>12472.31358130406</v>
+        <v>12439.35004136076</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07925490341364561</v>
+        <v>0.07960519208543446</v>
       </c>
       <c r="T25">
-        <v>0.652098337110931</v>
+        <v>0.6589261153160574</v>
       </c>
       <c r="U25">
         <v>0.0602366166625341</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.913828253629619</v>
+        <v>4.709085409728385</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07134253698418633</v>
+        <v>0.07126798196557838</v>
       </c>
       <c r="C26">
-        <v>53943.68069232834</v>
+        <v>53270.27274440204</v>
       </c>
       <c r="D26">
-        <v>62724.87679934214</v>
+        <v>62781.11452254141</v>
       </c>
       <c r="E26">
-        <v>-28956.87100554369</v>
+        <v>-28227.22533441812</v>
       </c>
       <c r="F26">
-        <v>17511.4961070138</v>
+        <v>18241.14177813937</v>
       </c>
       <c r="G26">
         <v>8730.299999999999</v>
@@ -3425,28 +3425,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M26">
-        <v>1054.833278185648</v>
+        <v>1098.784664776717</v>
       </c>
       <c r="N26">
-        <v>3912.466721814351</v>
+        <v>3868.515335223282</v>
       </c>
       <c r="O26">
-        <v>978.1166804535877</v>
+        <v>967.1288338058206</v>
       </c>
       <c r="P26">
-        <v>2934.350041360763</v>
+        <v>2901.386501417462</v>
       </c>
       <c r="Q26">
-        <v>12439.35004136076</v>
+        <v>12406.38650141746</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07960519208543446</v>
+        <v>0.07996482178847097</v>
       </c>
       <c r="T26">
-        <v>0.6589261153160574</v>
+        <v>0.6659359676066536</v>
       </c>
       <c r="U26">
         <v>0.0602366166625341</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.709085409728385</v>
+        <v>4.52072199333925</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07126798196557838</v>
+        <v>0.07119342694697044</v>
       </c>
       <c r="C27">
-        <v>53270.27274440204</v>
+        <v>52596.96572994285</v>
       </c>
       <c r="D27">
-        <v>62781.11452254141</v>
+        <v>62837.4531792078</v>
       </c>
       <c r="E27">
-        <v>-28227.22533441812</v>
+        <v>-27497.57966329254</v>
       </c>
       <c r="F27">
-        <v>18241.14177813937</v>
+        <v>18970.78744926495</v>
       </c>
       <c r="G27">
         <v>8730.299999999999</v>
@@ -3507,28 +3507,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M27">
-        <v>1098.784664776717</v>
+        <v>1142.736051367786</v>
       </c>
       <c r="N27">
-        <v>3868.515335223282</v>
+        <v>3824.563948632213</v>
       </c>
       <c r="O27">
-        <v>967.1288338058206</v>
+        <v>956.1409871580533</v>
       </c>
       <c r="P27">
-        <v>2901.386501417462</v>
+        <v>2868.42296147416</v>
       </c>
       <c r="Q27">
-        <v>12406.38650141746</v>
+        <v>12373.42296147416</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07996482178847097</v>
+        <v>0.08033417121321121</v>
       </c>
       <c r="T27">
-        <v>0.6659359676066536</v>
+        <v>0.6731352753645635</v>
       </c>
       <c r="U27">
         <v>0.0602366166625341</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.52072199333925</v>
+        <v>4.34684807051851</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07119342694697044</v>
+        <v>0.07132137192836252</v>
       </c>
       <c r="C28">
-        <v>52596.96572994285</v>
+        <v>51770.6984844703</v>
       </c>
       <c r="D28">
-        <v>62837.4531792078</v>
+        <v>62740.83160486082</v>
       </c>
       <c r="E28">
-        <v>-27497.57966329254</v>
+        <v>-26767.93399216697</v>
       </c>
       <c r="F28">
-        <v>18970.78744926495</v>
+        <v>19700.43312039052</v>
       </c>
       <c r="G28">
         <v>8730.299999999999</v>
@@ -3589,45 +3589,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M28">
-        <v>1142.736051367786</v>
+        <v>1206.387871079245</v>
       </c>
       <c r="N28">
-        <v>3824.563948632213</v>
+        <v>3760.912128920754</v>
       </c>
       <c r="O28">
-        <v>956.1409871580533</v>
+        <v>940.2280322301885</v>
       </c>
       <c r="P28">
-        <v>2868.42296147416</v>
+        <v>2820.684096690566</v>
       </c>
       <c r="Q28">
-        <v>12373.42296147416</v>
+        <v>12325.68409669057</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08033417121321121</v>
+        <v>0.0807136398002731</v>
       </c>
       <c r="T28">
-        <v>0.6731352753645635</v>
+        <v>0.6805318244309092</v>
       </c>
       <c r="U28">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.04517746249690057</v>
+        <v>0.04592746249690057</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.34684807051851</v>
+        <v>4.117498293112156</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07132137192836252</v>
+        <v>0.07125431690975458</v>
       </c>
       <c r="C29">
-        <v>51770.6984844703</v>
+        <v>51091.65437993137</v>
       </c>
       <c r="D29">
-        <v>62740.83160486082</v>
+        <v>62791.43317144748</v>
       </c>
       <c r="E29">
-        <v>-26767.93399216697</v>
+        <v>-26038.28832104139</v>
       </c>
       <c r="F29">
-        <v>19700.43312039052</v>
+        <v>20430.0787915161</v>
       </c>
       <c r="G29">
         <v>8730.299999999999</v>
@@ -3671,28 +3671,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M29">
-        <v>1206.387871079245</v>
+        <v>1251.068903341439</v>
       </c>
       <c r="N29">
-        <v>3760.912128920754</v>
+        <v>3716.23109665856</v>
       </c>
       <c r="O29">
-        <v>940.2280322301885</v>
+        <v>929.05777416464</v>
       </c>
       <c r="P29">
-        <v>2820.684096690566</v>
+        <v>2787.17332249392</v>
       </c>
       <c r="Q29">
-        <v>12325.68409669057</v>
+        <v>12292.17332249392</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0807136398002731</v>
+        <v>0.08110364918142002</v>
       </c>
       <c r="T29">
-        <v>0.6805318244309092</v>
+        <v>0.6881338331935422</v>
       </c>
       <c r="U29">
         <v>0.0612366166625341</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.117498293112156</v>
+        <v>3.970444782643865</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07125431690975458</v>
+        <v>0.07118726189114663</v>
       </c>
       <c r="C30">
-        <v>51091.65437993137</v>
+        <v>50412.6919633537</v>
       </c>
       <c r="D30">
-        <v>62791.43317144748</v>
+        <v>62842.11642599538</v>
       </c>
       <c r="E30">
-        <v>-26038.28832104139</v>
+        <v>-25308.64264991582</v>
       </c>
       <c r="F30">
-        <v>20430.0787915161</v>
+        <v>21159.72446264168</v>
       </c>
       <c r="G30">
         <v>8730.299999999999</v>
@@ -3753,28 +3753,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M30">
-        <v>1251.068903341439</v>
+        <v>1295.749935603634</v>
       </c>
       <c r="N30">
-        <v>3716.23109665856</v>
+        <v>3671.550064396366</v>
       </c>
       <c r="O30">
-        <v>929.05777416464</v>
+        <v>917.8875160990915</v>
       </c>
       <c r="P30">
-        <v>2787.17332249392</v>
+        <v>2753.662548297274</v>
       </c>
       <c r="Q30">
-        <v>12292.17332249392</v>
+        <v>12258.66254829727</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08110364918142002</v>
+        <v>0.08150464474231756</v>
       </c>
       <c r="T30">
-        <v>0.6881338331935422</v>
+        <v>0.6959499830480803</v>
       </c>
       <c r="U30">
         <v>0.0612366166625341</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.970444782643865</v>
+        <v>3.83353289358718</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07118726189114663</v>
+        <v>0.07112020687253869</v>
       </c>
       <c r="C31">
-        <v>50412.69196335372</v>
+        <v>49733.81143270488</v>
       </c>
       <c r="D31">
-        <v>62842.11642599538</v>
+        <v>62892.88156647213</v>
       </c>
       <c r="E31">
-        <v>-25308.64264991582</v>
+        <v>-24578.99697879024</v>
       </c>
       <c r="F31">
-        <v>21159.72446264167</v>
+        <v>21889.37013376725</v>
       </c>
       <c r="G31">
         <v>8730.299999999999</v>
@@ -3835,28 +3835,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M31">
-        <v>1295.749935603633</v>
+        <v>1340.430967865828</v>
       </c>
       <c r="N31">
-        <v>3671.550064396366</v>
+        <v>3626.869032134172</v>
       </c>
       <c r="O31">
-        <v>917.8875160990915</v>
+        <v>906.717258033543</v>
       </c>
       <c r="P31">
-        <v>2753.662548297274</v>
+        <v>2720.151774100629</v>
       </c>
       <c r="Q31">
-        <v>12258.66254829727</v>
+        <v>12225.15177410063</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08150464474231756</v>
+        <v>0.08191709731924075</v>
       </c>
       <c r="T31">
-        <v>0.6959499830480803</v>
+        <v>0.703989451469891</v>
       </c>
       <c r="U31">
         <v>0.0612366166625341</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.833532893587181</v>
+        <v>3.705748463800941</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07112020687253869</v>
+        <v>0.07105315185393075</v>
       </c>
       <c r="C32">
-        <v>49733.81143270488</v>
+        <v>49055.01298659268</v>
       </c>
       <c r="D32">
-        <v>62892.88156647213</v>
+        <v>62943.7287914855</v>
       </c>
       <c r="E32">
-        <v>-24578.99697879024</v>
+        <v>-23849.35130766467</v>
       </c>
       <c r="F32">
-        <v>21889.37013376725</v>
+        <v>22619.01580489282</v>
       </c>
       <c r="G32">
         <v>8730.299999999999</v>
@@ -3917,28 +3917,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M32">
-        <v>1340.430967865828</v>
+        <v>1385.112000128022</v>
       </c>
       <c r="N32">
-        <v>3626.869032134172</v>
+        <v>3582.187999871978</v>
       </c>
       <c r="O32">
-        <v>906.717258033543</v>
+        <v>895.5469999679945</v>
       </c>
       <c r="P32">
-        <v>2720.151774100629</v>
+        <v>2686.640999903983</v>
       </c>
       <c r="Q32">
-        <v>12225.15177410063</v>
+        <v>12191.64099990398</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08191709731924075</v>
+        <v>0.08234150504332113</v>
       </c>
       <c r="T32">
-        <v>0.703989451469891</v>
+        <v>0.7122619479618991</v>
       </c>
       <c r="U32">
         <v>0.0612366166625341</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.705748463800941</v>
+        <v>3.586208190775105</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07105315185393075</v>
+        <v>0.07098609683532282</v>
       </c>
       <c r="C33">
-        <v>49055.01298659268</v>
+        <v>48376.2968242677</v>
       </c>
       <c r="D33">
-        <v>62943.7287914855</v>
+        <v>62994.6583002861</v>
       </c>
       <c r="E33">
-        <v>-23849.35130766467</v>
+        <v>-23119.70563653909</v>
       </c>
       <c r="F33">
-        <v>22619.01580489282</v>
+        <v>23348.6614760184</v>
       </c>
       <c r="G33">
         <v>8730.299999999999</v>
@@ -3999,28 +3999,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M33">
-        <v>1385.112000128022</v>
+        <v>1429.793032390216</v>
       </c>
       <c r="N33">
-        <v>3582.187999871978</v>
+        <v>3537.506967609783</v>
       </c>
       <c r="O33">
-        <v>895.5469999679945</v>
+        <v>884.3767419024457</v>
       </c>
       <c r="P33">
-        <v>2686.640999903983</v>
+        <v>2653.130225707337</v>
       </c>
       <c r="Q33">
-        <v>12191.64099990398</v>
+        <v>12158.13022570734</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08234150504332113</v>
+        <v>0.08277839534752154</v>
       </c>
       <c r="T33">
-        <v>0.7122619479618991</v>
+        <v>0.7207777531742605</v>
       </c>
       <c r="U33">
         <v>0.0612366166625341</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.586208190775105</v>
+        <v>3.474139184813382</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07098609683532282</v>
+        <v>0.07091904181671489</v>
       </c>
       <c r="C34">
-        <v>48376.2968242677</v>
+        <v>47697.66314562596</v>
       </c>
       <c r="D34">
-        <v>62994.6583002861</v>
+        <v>63045.67029276994</v>
       </c>
       <c r="E34">
-        <v>-23119.70563653909</v>
+        <v>-22390.05996541352</v>
       </c>
       <c r="F34">
-        <v>23348.6614760184</v>
+        <v>24078.30714714397</v>
       </c>
       <c r="G34">
         <v>8730.299999999999</v>
@@ -4081,28 +4081,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M34">
-        <v>1429.793032390216</v>
+        <v>1474.47406465241</v>
       </c>
       <c r="N34">
-        <v>3537.506967609783</v>
+        <v>3492.825935347589</v>
       </c>
       <c r="O34">
-        <v>884.3767419024457</v>
+        <v>873.2064838368972</v>
       </c>
       <c r="P34">
-        <v>2653.130225707337</v>
+        <v>2619.619451510692</v>
       </c>
       <c r="Q34">
-        <v>12158.13022570734</v>
+        <v>12124.61945151069</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08277839534752154</v>
+        <v>0.08322832715333986</v>
       </c>
       <c r="T34">
-        <v>0.7207777531742605</v>
+        <v>0.7295477615272893</v>
       </c>
       <c r="U34">
         <v>0.0612366166625341</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.474139184813382</v>
+        <v>3.368862239819037</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07091904181671489</v>
+        <v>0.07085198679810695</v>
       </c>
       <c r="C35">
-        <v>47697.66314562596</v>
+        <v>47019.11215121148</v>
       </c>
       <c r="D35">
-        <v>63045.67029276994</v>
+        <v>63096.76496948102</v>
       </c>
       <c r="E35">
-        <v>-22390.05996541352</v>
+        <v>-21660.41429428794</v>
       </c>
       <c r="F35">
-        <v>24078.30714714397</v>
+        <v>24807.95281826955</v>
       </c>
       <c r="G35">
         <v>8730.299999999999</v>
@@ -4163,28 +4163,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M35">
-        <v>1474.47406465241</v>
+        <v>1519.155096914605</v>
       </c>
       <c r="N35">
-        <v>3492.825935347589</v>
+        <v>3448.144903085395</v>
       </c>
       <c r="O35">
-        <v>873.2064838368972</v>
+        <v>862.0362257713487</v>
       </c>
       <c r="P35">
-        <v>2619.619451510692</v>
+        <v>2586.108677314046</v>
       </c>
       <c r="Q35">
-        <v>12124.61945151069</v>
+        <v>12091.10867731405</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08322832715333986</v>
+        <v>0.08369189325630419</v>
       </c>
       <c r="T35">
-        <v>0.7295477615272893</v>
+        <v>0.7385835277091978</v>
       </c>
       <c r="U35">
         <v>0.0612366166625341</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.368862239819037</v>
+        <v>3.269778056294948</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07085198679810695</v>
+        <v>0.07078493177949902</v>
       </c>
       <c r="C36">
-        <v>47019.11215121148</v>
+        <v>46340.64404221886</v>
       </c>
       <c r="D36">
-        <v>63096.76496948102</v>
+        <v>63147.94253161398</v>
       </c>
       <c r="E36">
-        <v>-21660.41429428794</v>
+        <v>-20930.76862316237</v>
       </c>
       <c r="F36">
-        <v>24807.95281826955</v>
+        <v>25537.59848939512</v>
       </c>
       <c r="G36">
         <v>8730.299999999999</v>
@@ -4245,28 +4245,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M36">
-        <v>1519.155096914605</v>
+        <v>1563.836129176799</v>
       </c>
       <c r="N36">
-        <v>3448.144903085395</v>
+        <v>3403.463870823201</v>
       </c>
       <c r="O36">
-        <v>862.0362257713487</v>
+        <v>850.8659677058001</v>
       </c>
       <c r="P36">
-        <v>2586.108677314046</v>
+        <v>2552.5979031174</v>
       </c>
       <c r="Q36">
-        <v>12091.10867731405</v>
+        <v>12057.5979031174</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08369189325630419</v>
+        <v>0.08416972293166741</v>
       </c>
       <c r="T36">
-        <v>0.7385835277091978</v>
+        <v>0.7478973174659342</v>
       </c>
       <c r="U36">
         <v>0.0612366166625341</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.269778056294948</v>
+        <v>3.176355826115092</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07078493177949902</v>
+        <v>0.07071787676089109</v>
       </c>
       <c r="C37">
-        <v>46340.64404221886</v>
+        <v>45662.25902049606</v>
       </c>
       <c r="D37">
-        <v>63147.94253161398</v>
+        <v>63199.20318101675</v>
       </c>
       <c r="E37">
-        <v>-20930.76862316237</v>
+        <v>-20201.12295203679</v>
       </c>
       <c r="F37">
-        <v>25537.59848939512</v>
+        <v>26267.2441605207</v>
       </c>
       <c r="G37">
         <v>8730.299999999999</v>
@@ -4327,28 +4327,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M37">
-        <v>1563.836129176799</v>
+        <v>1608.517161438993</v>
       </c>
       <c r="N37">
-        <v>3403.463870823201</v>
+        <v>3358.782838561006</v>
       </c>
       <c r="O37">
-        <v>850.8659677058001</v>
+        <v>839.6957096402515</v>
       </c>
       <c r="P37">
-        <v>2552.5979031174</v>
+        <v>2519.087128920754</v>
       </c>
       <c r="Q37">
-        <v>12057.5979031174</v>
+        <v>12024.08712892075</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08416972293166741</v>
+        <v>0.08466248478438575</v>
       </c>
       <c r="T37">
-        <v>0.7478973174659342</v>
+        <v>0.7575021631525686</v>
       </c>
       <c r="U37">
         <v>0.0612366166625341</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.176355826115092</v>
+        <v>3.088123719834117</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07071787676089109</v>
+        <v>0.07065082174228315</v>
       </c>
       <c r="C38">
-        <v>45662.25902049606</v>
+        <v>44983.95728854694</v>
       </c>
       <c r="D38">
-        <v>63199.20318101675</v>
+        <v>63250.54712019322</v>
       </c>
       <c r="E38">
-        <v>-20201.1229520368</v>
+        <v>-19471.47728091122</v>
       </c>
       <c r="F38">
-        <v>26267.2441605207</v>
+        <v>26996.88983164627</v>
       </c>
       <c r="G38">
         <v>8730.299999999999</v>
@@ -4409,28 +4409,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M38">
-        <v>1608.517161438993</v>
+        <v>1653.198193701187</v>
       </c>
       <c r="N38">
-        <v>3358.782838561006</v>
+        <v>3314.101806298812</v>
       </c>
       <c r="O38">
-        <v>839.6957096402516</v>
+        <v>828.5254515747031</v>
       </c>
       <c r="P38">
-        <v>2519.087128920755</v>
+        <v>2485.576354724109</v>
       </c>
       <c r="Q38">
-        <v>12024.08712892076</v>
+        <v>11990.57635472411</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08466248478438575</v>
+        <v>0.08517088987052371</v>
       </c>
       <c r="T38">
-        <v>0.7575021631525686</v>
+        <v>0.7674119245752866</v>
       </c>
       <c r="U38">
         <v>0.0612366166625341</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.088123719834118</v>
+        <v>3.004660916595358</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07065082174228315</v>
+        <v>0.07129626672367521</v>
       </c>
       <c r="C39">
-        <v>44983.95728854694</v>
+        <v>43763.53162790969</v>
       </c>
       <c r="D39">
-        <v>63250.54712019322</v>
+        <v>62759.76713068153</v>
       </c>
       <c r="E39">
-        <v>-19471.47728091122</v>
+        <v>-18741.83160978564</v>
       </c>
       <c r="F39">
-        <v>26996.88983164627</v>
+        <v>27726.53550277185</v>
       </c>
       <c r="G39">
         <v>8730.299999999999</v>
@@ -4491,45 +4491,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M39">
-        <v>1653.198193701187</v>
+        <v>1767.195564720311</v>
       </c>
       <c r="N39">
-        <v>3314.101806298812</v>
+        <v>3200.104435279688</v>
       </c>
       <c r="O39">
-        <v>828.5254515747031</v>
+        <v>800.026108819922</v>
       </c>
       <c r="P39">
-        <v>2485.576354724109</v>
+        <v>2400.078326459766</v>
       </c>
       <c r="Q39">
-        <v>11990.57635472411</v>
+        <v>11905.07832645977</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08517088987052371</v>
+        <v>0.08569569512073064</v>
       </c>
       <c r="T39">
-        <v>0.7674119245752866</v>
+        <v>0.7776413557213182</v>
       </c>
       <c r="U39">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.04592746249690057</v>
+        <v>0.04780246249690057</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.004660916595358</v>
+        <v>2.810837747199846</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07129626672367521</v>
+        <v>0.07124796170506728</v>
       </c>
       <c r="C40">
-        <v>43763.53162790969</v>
+        <v>43070.35204511377</v>
       </c>
       <c r="D40">
-        <v>62759.76713068153</v>
+        <v>62796.23321901119</v>
       </c>
       <c r="E40">
-        <v>-18741.83160978564</v>
+        <v>-18012.18593866007</v>
       </c>
       <c r="F40">
-        <v>27726.53550277185</v>
+        <v>28456.18117389742</v>
       </c>
       <c r="G40">
         <v>8730.299999999999</v>
@@ -4573,28 +4573,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M40">
-        <v>1767.195564720311</v>
+        <v>1813.700711160319</v>
       </c>
       <c r="N40">
-        <v>3200.104435279688</v>
+        <v>3153.59928883968</v>
       </c>
       <c r="O40">
-        <v>800.026108819922</v>
+        <v>788.39982220992</v>
       </c>
       <c r="P40">
-        <v>2400.078326459766</v>
+        <v>2365.19946662976</v>
       </c>
       <c r="Q40">
-        <v>11905.07832645977</v>
+        <v>11870.19946662976</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08569569512073064</v>
+        <v>0.08623770710045255</v>
       </c>
       <c r="T40">
-        <v>0.7776413557213182</v>
+        <v>0.7882061780524655</v>
       </c>
       <c r="U40">
         <v>0.06373661666253409</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.810837747199846</v>
+        <v>2.738764984451132</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07124796170506728</v>
+        <v>0.07119965668645933</v>
       </c>
       <c r="C41">
-        <v>43070.35204511377</v>
+        <v>42377.21486364484</v>
       </c>
       <c r="D41">
-        <v>62796.23321901119</v>
+        <v>62832.74170866783</v>
       </c>
       <c r="E41">
-        <v>-18012.18593866007</v>
+        <v>-17282.5402675345</v>
       </c>
       <c r="F41">
-        <v>28456.18117389742</v>
+        <v>29185.826845023</v>
       </c>
       <c r="G41">
         <v>8730.299999999999</v>
@@ -4655,28 +4655,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M41">
-        <v>1813.700711160319</v>
+        <v>1860.205857600327</v>
       </c>
       <c r="N41">
-        <v>3153.59928883968</v>
+        <v>3107.094142399672</v>
       </c>
       <c r="O41">
-        <v>788.39982220992</v>
+        <v>776.773535599918</v>
       </c>
       <c r="P41">
-        <v>2365.19946662976</v>
+        <v>2330.320606799754</v>
       </c>
       <c r="Q41">
-        <v>11870.19946662976</v>
+        <v>11835.32060679975</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08623770710045255</v>
+        <v>0.08679778614616518</v>
       </c>
       <c r="T41">
-        <v>0.7882061780524655</v>
+        <v>0.7991231611279844</v>
       </c>
       <c r="U41">
         <v>0.06373661666253409</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.738764984451132</v>
+        <v>2.670295859839854</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07119965668645933</v>
+        <v>0.07115135166785139</v>
       </c>
       <c r="C42">
-        <v>42377.21486364484</v>
+        <v>41684.12015749978</v>
       </c>
       <c r="D42">
-        <v>62832.74170866783</v>
+        <v>62869.29267364836</v>
       </c>
       <c r="E42">
-        <v>-17282.5402675345</v>
+        <v>-16552.89459640892</v>
       </c>
       <c r="F42">
-        <v>29185.826845023</v>
+        <v>29915.47251614857</v>
       </c>
       <c r="G42">
         <v>8730.299999999999</v>
@@ -4737,28 +4737,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M42">
-        <v>1860.205857600327</v>
+        <v>1906.711004040336</v>
       </c>
       <c r="N42">
-        <v>3107.094142399672</v>
+        <v>3060.588995959663</v>
       </c>
       <c r="O42">
-        <v>776.773535599918</v>
+        <v>765.1472489899159</v>
       </c>
       <c r="P42">
-        <v>2330.320606799754</v>
+        <v>2295.441746969747</v>
       </c>
       <c r="Q42">
-        <v>11835.32060679975</v>
+        <v>11800.44174696975</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08679778614616518</v>
+        <v>0.08737685092224096</v>
       </c>
       <c r="T42">
-        <v>0.7991231611279844</v>
+        <v>0.8104102114264023</v>
       </c>
       <c r="U42">
         <v>0.06373661666253409</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.670295859839854</v>
+        <v>2.605166692526686</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07115135166785139</v>
+        <v>0.07110304664924347</v>
       </c>
       <c r="C43">
-        <v>41684.12015749978</v>
+        <v>40991.06800084776</v>
       </c>
       <c r="D43">
-        <v>62869.29267364836</v>
+        <v>62905.88618812191</v>
       </c>
       <c r="E43">
-        <v>-16552.89459640892</v>
+        <v>-15823.24892528334</v>
       </c>
       <c r="F43">
-        <v>29915.47251614857</v>
+        <v>30645.11818727415</v>
       </c>
       <c r="G43">
         <v>8730.299999999999</v>
@@ -4819,28 +4819,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M43">
-        <v>1906.711004040336</v>
+        <v>1953.216150480344</v>
       </c>
       <c r="N43">
-        <v>3060.588995959663</v>
+        <v>3014.083849519655</v>
       </c>
       <c r="O43">
-        <v>765.1472489899159</v>
+        <v>753.5209623799138</v>
       </c>
       <c r="P43">
-        <v>2295.441746969747</v>
+        <v>2260.562887139742</v>
       </c>
       <c r="Q43">
-        <v>11800.44174696975</v>
+        <v>11765.56288713974</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08737685092224096</v>
+        <v>0.08797588344921591</v>
       </c>
       <c r="T43">
-        <v>0.8104102114264023</v>
+        <v>0.8220864703558001</v>
       </c>
       <c r="U43">
         <v>0.06373661666253409</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.605166692526686</v>
+        <v>2.543138914133194</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07110304664924347</v>
+        <v>0.07218349163063553</v>
       </c>
       <c r="C44">
-        <v>40991.06800084776</v>
+        <v>39452.97884475197</v>
       </c>
       <c r="D44">
-        <v>62905.88618812191</v>
+        <v>62097.44270315168</v>
       </c>
       <c r="E44">
-        <v>-15823.24892528335</v>
+        <v>-15093.60325415777</v>
       </c>
       <c r="F44">
-        <v>30645.11818727414</v>
+        <v>31374.76385839972</v>
       </c>
       <c r="G44">
         <v>8730.299999999999</v>
@@ -4901,45 +4901,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M44">
-        <v>1953.216150480344</v>
+        <v>2109.532970424751</v>
       </c>
       <c r="N44">
-        <v>3014.083849519656</v>
+        <v>2857.767029575248</v>
       </c>
       <c r="O44">
-        <v>753.520962379914</v>
+        <v>714.4417573938121</v>
       </c>
       <c r="P44">
-        <v>2260.562887139742</v>
+        <v>2143.325272181436</v>
       </c>
       <c r="Q44">
-        <v>11765.56288713974</v>
+        <v>11648.32527218144</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08797588344921591</v>
+        <v>0.08859593466134785</v>
       </c>
       <c r="T44">
-        <v>0.8220864703558001</v>
+        <v>0.8341724225809661</v>
       </c>
       <c r="U44">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.04780246249690057</v>
+        <v>0.05042746249690057</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>2.543138914133195</v>
+        <v>2.354691806025597</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07218349163063553</v>
+        <v>0.0721614366120276</v>
       </c>
       <c r="C45">
-        <v>39452.97884475197</v>
+        <v>38739.62804045354</v>
       </c>
       <c r="D45">
-        <v>62097.44270315168</v>
+        <v>62113.73756997883</v>
       </c>
       <c r="E45">
-        <v>-15093.60325415777</v>
+        <v>-14363.9575830322</v>
       </c>
       <c r="F45">
-        <v>31374.76385839972</v>
+        <v>32104.4095295253</v>
       </c>
       <c r="G45">
         <v>8730.299999999999</v>
@@ -4983,28 +4983,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M45">
-        <v>2109.532970424751</v>
+        <v>2158.591876713699</v>
       </c>
       <c r="N45">
-        <v>2857.767029575248</v>
+        <v>2808.7081232863</v>
       </c>
       <c r="O45">
-        <v>714.4417573938121</v>
+        <v>702.177030821575</v>
       </c>
       <c r="P45">
-        <v>2143.325272181436</v>
+        <v>2106.531092464725</v>
       </c>
       <c r="Q45">
-        <v>11648.32527218144</v>
+        <v>11611.53109246473</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08859593466134785</v>
+        <v>0.0892381305596274</v>
       </c>
       <c r="T45">
-        <v>0.8341724225809661</v>
+        <v>0.8466900159570312</v>
       </c>
       <c r="U45">
         <v>0.0672366166625341</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.354691806025597</v>
+        <v>2.301176083161379</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0721614366120276</v>
+        <v>0.07213938159341965</v>
       </c>
       <c r="C46">
-        <v>38739.62804045354</v>
+        <v>38026.28579020719</v>
       </c>
       <c r="D46">
-        <v>62113.73756997883</v>
+        <v>62130.04099085807</v>
       </c>
       <c r="E46">
-        <v>-14363.9575830322</v>
+        <v>-13634.31191190662</v>
       </c>
       <c r="F46">
-        <v>32104.4095295253</v>
+        <v>32834.05520065087</v>
       </c>
       <c r="G46">
         <v>8730.299999999999</v>
@@ -5065,28 +5065,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M46">
-        <v>2158.591876713699</v>
+        <v>2207.650783002647</v>
       </c>
       <c r="N46">
-        <v>2808.7081232863</v>
+        <v>2759.649216997353</v>
       </c>
       <c r="O46">
-        <v>702.177030821575</v>
+        <v>689.9123042493381</v>
       </c>
       <c r="P46">
-        <v>2106.531092464725</v>
+        <v>2069.736912748014</v>
       </c>
       <c r="Q46">
-        <v>11611.53109246473</v>
+        <v>11574.73691274801</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.0892381305596274</v>
+        <v>0.08990367903602617</v>
       </c>
       <c r="T46">
-        <v>0.8466900159570312</v>
+        <v>0.8596627945467711</v>
       </c>
       <c r="U46">
         <v>0.0672366166625341</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.301176083161379</v>
+        <v>2.250038836868903</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07213938159341965</v>
+        <v>0.07308332657481172</v>
       </c>
       <c r="C47">
-        <v>38026.28579020719</v>
+        <v>36606.4315401439</v>
       </c>
       <c r="D47">
-        <v>62130.04099085807</v>
+        <v>61439.83241192035</v>
       </c>
       <c r="E47">
-        <v>-13634.31191190662</v>
+        <v>-12904.66624078104</v>
       </c>
       <c r="F47">
-        <v>32834.05520065087</v>
+        <v>33563.70087177645</v>
       </c>
       <c r="G47">
         <v>8730.299999999999</v>
@@ -5147,45 +5147,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M47">
-        <v>2207.650783002647</v>
+        <v>2350.688051732569</v>
       </c>
       <c r="N47">
-        <v>2759.649216997353</v>
+        <v>2616.611948267431</v>
       </c>
       <c r="O47">
-        <v>689.9123042493381</v>
+        <v>654.1529870668577</v>
       </c>
       <c r="P47">
-        <v>2069.736912748014</v>
+        <v>1962.458961200573</v>
       </c>
       <c r="Q47">
-        <v>11574.73691274801</v>
+        <v>11467.45896120057</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08990367903602617</v>
+        <v>0.09059387745599529</v>
       </c>
       <c r="T47">
-        <v>0.8596627945467711</v>
+        <v>0.8731160464176125</v>
       </c>
       <c r="U47">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.05042746249690057</v>
+        <v>0.05252746249690057</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>2.250038836868903</v>
+        <v>2.113125982981393</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07308332657481172</v>
+        <v>0.07308227155620378</v>
       </c>
       <c r="C48">
-        <v>36606.4315401439</v>
+        <v>35877.54873379942</v>
       </c>
       <c r="D48">
-        <v>61439.83241192035</v>
+        <v>61440.59527670144</v>
       </c>
       <c r="E48">
-        <v>-12904.66624078104</v>
+        <v>-12175.02056965547</v>
       </c>
       <c r="F48">
-        <v>33563.70087177645</v>
+        <v>34293.34654290202</v>
       </c>
       <c r="G48">
         <v>8730.299999999999</v>
@@ -5229,28 +5229,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M48">
-        <v>2350.688051732569</v>
+        <v>2401.789965900668</v>
       </c>
       <c r="N48">
-        <v>2616.611948267431</v>
+        <v>2565.510034099332</v>
       </c>
       <c r="O48">
-        <v>654.1529870668577</v>
+        <v>641.3775085248329</v>
       </c>
       <c r="P48">
-        <v>1962.458961200573</v>
+        <v>1924.132525574499</v>
       </c>
       <c r="Q48">
-        <v>11467.45896120057</v>
+        <v>11429.1325255745</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09059387745599529</v>
+        <v>0.09131012109935946</v>
       </c>
       <c r="T48">
-        <v>0.8731160464176125</v>
+        <v>0.8870769681703726</v>
       </c>
       <c r="U48">
         <v>0.07003661666253409</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.113125982981393</v>
+        <v>2.068165855683917</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07308227155620378</v>
+        <v>0.07308121653759585</v>
       </c>
       <c r="C49">
-        <v>35877.54873379942</v>
+        <v>35148.66594639932</v>
       </c>
       <c r="D49">
-        <v>61440.59527670144</v>
+        <v>61441.35816042691</v>
       </c>
       <c r="E49">
-        <v>-12175.02056965547</v>
+        <v>-11445.3748985299</v>
       </c>
       <c r="F49">
-        <v>34293.34654290202</v>
+        <v>35022.9922140276</v>
       </c>
       <c r="G49">
         <v>8730.299999999999</v>
@@ -5311,28 +5311,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M49">
-        <v>2401.789965900668</v>
+        <v>2452.891880068767</v>
       </c>
       <c r="N49">
-        <v>2565.510034099332</v>
+        <v>2514.408119931232</v>
       </c>
       <c r="O49">
-        <v>641.3775085248329</v>
+        <v>628.6020299828081</v>
       </c>
       <c r="P49">
-        <v>1924.132525574499</v>
+        <v>1885.806089948424</v>
       </c>
       <c r="Q49">
-        <v>11429.1325255745</v>
+        <v>11390.80608994842</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09131012109935946</v>
+        <v>0.09205391257516071</v>
       </c>
       <c r="T49">
-        <v>0.8870769681703726</v>
+        <v>0.901574848452085</v>
       </c>
       <c r="U49">
         <v>0.07003661666253409</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.068165855683917</v>
+        <v>2.025079067023835</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07308121653759585</v>
+        <v>0.07594666151898792</v>
       </c>
       <c r="C50">
-        <v>35148.66594639932</v>
+        <v>32414.58870448064</v>
       </c>
       <c r="D50">
-        <v>61441.35816042691</v>
+        <v>59436.92658963381</v>
       </c>
       <c r="E50">
-        <v>-11445.3748985299</v>
+        <v>-10715.72922740432</v>
       </c>
       <c r="F50">
-        <v>35022.9922140276</v>
+        <v>35752.63788515317</v>
       </c>
       <c r="G50">
         <v>8730.299999999999</v>
@@ -5393,45 +5393,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M50">
-        <v>2452.891880068767</v>
+        <v>2782.864369741062</v>
       </c>
       <c r="N50">
-        <v>2514.408119931232</v>
+        <v>2184.435630258938</v>
       </c>
       <c r="O50">
-        <v>628.6020299828081</v>
+        <v>546.1089075647344</v>
       </c>
       <c r="P50">
-        <v>1885.806089948424</v>
+        <v>1638.326722694203</v>
       </c>
       <c r="Q50">
-        <v>11390.80608994842</v>
+        <v>11143.3267226942</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09205391257516071</v>
+        <v>0.09282687234413065</v>
       </c>
       <c r="T50">
-        <v>0.901574848452085</v>
+        <v>0.9166412730585703</v>
       </c>
       <c r="U50">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V50">
         <v>0.25</v>
       </c>
       <c r="W50">
-        <v>0.05252746249690057</v>
+        <v>0.05837746249690058</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.025079067023835</v>
+        <v>1.784959430294547</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07594666151898792</v>
+        <v>0.07746660650037998</v>
       </c>
       <c r="C51">
-        <v>32414.58870448064</v>
+        <v>30673.89572359161</v>
       </c>
       <c r="D51">
-        <v>59436.92658963381</v>
+        <v>58425.87927987036</v>
       </c>
       <c r="E51">
-        <v>-10715.72922740432</v>
+        <v>-9986.083556278747</v>
       </c>
       <c r="F51">
-        <v>35752.63788515317</v>
+        <v>36482.28355627874</v>
       </c>
       <c r="G51">
         <v>8730.299999999999</v>
@@ -5475,45 +5475,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M51">
-        <v>2782.864369741062</v>
+        <v>2981.938426013427</v>
       </c>
       <c r="N51">
-        <v>2184.435630258938</v>
+        <v>1985.361573986572</v>
       </c>
       <c r="O51">
-        <v>546.1089075647344</v>
+        <v>496.3403934966431</v>
       </c>
       <c r="P51">
-        <v>1638.326722694203</v>
+        <v>1489.021180489929</v>
       </c>
       <c r="Q51">
-        <v>11143.3267226942</v>
+        <v>10994.02118048993</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09282687234413065</v>
+        <v>0.09363075050385938</v>
       </c>
       <c r="T51">
-        <v>0.9166412730585703</v>
+        <v>0.9323103546493152</v>
       </c>
       <c r="U51">
-        <v>0.07783661666253411</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V51">
         <v>0.25</v>
       </c>
       <c r="W51">
-        <v>0.05837746249690058</v>
+        <v>0.06130246249690057</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.784959430294547</v>
+        <v>1.665795630341306</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07746660650037998</v>
+        <v>0.07755330148177204</v>
       </c>
       <c r="C52">
-        <v>30673.89572359161</v>
+        <v>29887.61760733896</v>
       </c>
       <c r="D52">
-        <v>58425.87927987036</v>
+        <v>58369.24683474327</v>
       </c>
       <c r="E52">
-        <v>-9986.083556278747</v>
+        <v>-9256.437885153173</v>
       </c>
       <c r="F52">
-        <v>36482.28355627874</v>
+        <v>37211.92922740432</v>
       </c>
       <c r="G52">
         <v>8730.299999999999</v>
@@ -5557,28 +5557,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M52">
-        <v>2981.938426013427</v>
+        <v>3041.577194533695</v>
       </c>
       <c r="N52">
-        <v>1985.361573986572</v>
+        <v>1925.722805466304</v>
       </c>
       <c r="O52">
-        <v>496.3403934966431</v>
+        <v>481.430701366576</v>
       </c>
       <c r="P52">
-        <v>1489.021180489929</v>
+        <v>1444.292104099728</v>
       </c>
       <c r="Q52">
-        <v>10994.02118048993</v>
+        <v>10949.29210409973</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09363075050385938</v>
+        <v>0.09446744001704643</v>
       </c>
       <c r="T52">
-        <v>0.9323103546493152</v>
+        <v>0.9486189905907026</v>
       </c>
       <c r="U52">
         <v>0.0817366166625341</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.665795630341306</v>
+        <v>1.633132970922849</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07755330148177204</v>
+        <v>0.07763999646316411</v>
       </c>
       <c r="C53">
-        <v>29887.61760733896</v>
+        <v>29101.44917289531</v>
       </c>
       <c r="D53">
-        <v>58369.24683474327</v>
+        <v>58312.7240714252</v>
       </c>
       <c r="E53">
-        <v>-9256.437885153173</v>
+        <v>-8526.792214027599</v>
       </c>
       <c r="F53">
-        <v>37211.92922740432</v>
+        <v>37941.57489852989</v>
       </c>
       <c r="G53">
         <v>8730.299999999999</v>
@@ -5639,28 +5639,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M53">
-        <v>3041.577194533695</v>
+        <v>3101.215963053964</v>
       </c>
       <c r="N53">
-        <v>1925.722805466304</v>
+        <v>1866.084036946036</v>
       </c>
       <c r="O53">
-        <v>481.430701366576</v>
+        <v>466.5210092365089</v>
       </c>
       <c r="P53">
-        <v>1444.292104099728</v>
+        <v>1399.563027709527</v>
       </c>
       <c r="Q53">
-        <v>10949.29210409973</v>
+        <v>10904.56302770953</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09446744001704643</v>
+        <v>0.09533899159328293</v>
       </c>
       <c r="T53">
-        <v>0.9486189905907026</v>
+        <v>0.9656071530296478</v>
       </c>
       <c r="U53">
         <v>0.0817366166625341</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.633132970922849</v>
+        <v>1.601726567635872</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07763999646316411</v>
+        <v>0.07772669144455618</v>
       </c>
       <c r="C54">
-        <v>29101.44917289531</v>
+        <v>28315.3901019327</v>
       </c>
       <c r="D54">
-        <v>58312.7240714252</v>
+        <v>58256.31067158818</v>
       </c>
       <c r="E54">
-        <v>-8526.792214027599</v>
+        <v>-7797.146542902017</v>
       </c>
       <c r="F54">
-        <v>37941.57489852989</v>
+        <v>38671.22056965547</v>
       </c>
       <c r="G54">
         <v>8730.299999999999</v>
@@ -5721,28 +5721,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M54">
-        <v>3101.215963053964</v>
+        <v>3160.854731574233</v>
       </c>
       <c r="N54">
-        <v>1866.084036946036</v>
+        <v>1806.445268425766</v>
       </c>
       <c r="O54">
-        <v>466.5210092365089</v>
+        <v>451.6113171064416</v>
       </c>
       <c r="P54">
-        <v>1399.563027709527</v>
+        <v>1354.833951319325</v>
       </c>
       <c r="Q54">
-        <v>10904.56302770953</v>
+        <v>10859.83395131932</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09533899159328293</v>
+        <v>0.09624763047063589</v>
       </c>
       <c r="T54">
-        <v>0.9656071530296478</v>
+        <v>0.98331821599791</v>
       </c>
       <c r="U54">
         <v>0.0817366166625341</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.601726567635872</v>
+        <v>1.571505311642742</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07772669144455618</v>
+        <v>0.07781338642594823</v>
       </c>
       <c r="C55">
-        <v>28315.3901019327</v>
+        <v>27529.44007735385</v>
       </c>
       <c r="D55">
-        <v>58256.31067158818</v>
+        <v>58200.0063181349</v>
       </c>
       <c r="E55">
-        <v>-7797.146542902017</v>
+        <v>-7067.500871776443</v>
       </c>
       <c r="F55">
-        <v>38671.22056965547</v>
+        <v>39400.86624078105</v>
       </c>
       <c r="G55">
         <v>8730.299999999999</v>
@@ -5803,28 +5803,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M55">
-        <v>3160.854731574233</v>
+        <v>3220.493500094502</v>
       </c>
       <c r="N55">
-        <v>1806.445268425766</v>
+        <v>1746.806499905498</v>
       </c>
       <c r="O55">
-        <v>451.6113171064416</v>
+        <v>436.7016249763744</v>
       </c>
       <c r="P55">
-        <v>1354.833951319325</v>
+        <v>1310.104874929123</v>
       </c>
       <c r="Q55">
-        <v>10859.83395131932</v>
+        <v>10815.10487492912</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09624763047063589</v>
+        <v>0.09719577538613461</v>
       </c>
       <c r="T55">
-        <v>0.98331821599791</v>
+        <v>1.001799325182184</v>
       </c>
       <c r="U55">
         <v>0.0817366166625341</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.571505311642742</v>
+        <v>1.542403361427135</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07781338642594823</v>
+        <v>0.07790008140734028</v>
       </c>
       <c r="C56">
-        <v>27529.44007735385</v>
+        <v>26743.5987832861</v>
       </c>
       <c r="D56">
-        <v>58200.0063181349</v>
+        <v>58143.81069519272</v>
       </c>
       <c r="E56">
-        <v>-7067.500871776443</v>
+        <v>-6337.855200650869</v>
       </c>
       <c r="F56">
-        <v>39400.86624078105</v>
+        <v>40130.51191190662</v>
       </c>
       <c r="G56">
         <v>8730.299999999999</v>
@@ -5885,28 +5885,28 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M56">
-        <v>3220.493500094502</v>
+        <v>3280.13226861477</v>
       </c>
       <c r="N56">
-        <v>1746.806499905498</v>
+        <v>1687.16773138523</v>
       </c>
       <c r="O56">
-        <v>436.7016249763744</v>
+        <v>421.7919328463074</v>
       </c>
       <c r="P56">
-        <v>1310.104874929123</v>
+        <v>1265.375798538922</v>
       </c>
       <c r="Q56">
-        <v>10815.10487492912</v>
+        <v>10770.37579853892</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09719577538613461</v>
+        <v>0.09818606007565552</v>
       </c>
       <c r="T56">
-        <v>1.001799325182184</v>
+        <v>1.021101816996869</v>
       </c>
       <c r="U56">
         <v>0.0817366166625341</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.542403361427135</v>
+        <v>1.514359663946642</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07790008140734028</v>
+        <v>0.08395077638873236</v>
       </c>
       <c r="C57">
-        <v>26743.5987832861</v>
+        <v>22343.06270374682</v>
       </c>
       <c r="D57">
-        <v>58143.81069519272</v>
+        <v>54472.92028677902</v>
       </c>
       <c r="E57">
-        <v>-6337.855200650869</v>
+        <v>-5608.209529525295</v>
       </c>
       <c r="F57">
-        <v>40130.51191190662</v>
+        <v>40860.1575830322</v>
       </c>
       <c r="G57">
         <v>8730.299999999999</v>
@@ -5967,45 +5967,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M57">
-        <v>3280.13226861477</v>
+        <v>3919.985274814096</v>
       </c>
       <c r="N57">
-        <v>1687.16773138523</v>
+        <v>1047.314725185904</v>
       </c>
       <c r="O57">
-        <v>421.7919328463074</v>
+        <v>261.8286812964759</v>
       </c>
       <c r="P57">
-        <v>1265.375798538922</v>
+        <v>785.4860438894277</v>
       </c>
       <c r="Q57">
-        <v>10770.37579853892</v>
+        <v>10290.48604388943</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09818606007565552</v>
+        <v>0.09922135770560916</v>
       </c>
       <c r="T57">
-        <v>1.021101816996869</v>
+        <v>1.041281694803131</v>
       </c>
       <c r="U57">
-        <v>0.0817366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V57">
         <v>0.25</v>
       </c>
       <c r="W57">
-        <v>0.06130246249690057</v>
+        <v>0.07195246249690057</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>1.514359663946642</v>
+        <v>1.267173127387723</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08395077638873236</v>
+        <v>0.09725690970714293</v>
       </c>
       <c r="C58">
-        <v>22343.06270374682</v>
+        <v>14972.43215276071</v>
       </c>
       <c r="D58">
-        <v>54472.92028677902</v>
+        <v>47831.93540691848</v>
       </c>
       <c r="E58">
-        <v>-5608.209529525295</v>
+        <v>-4878.563858399721</v>
       </c>
       <c r="F58">
-        <v>40860.1575830322</v>
+        <v>41589.80325415777</v>
       </c>
       <c r="G58">
         <v>8730.299999999999</v>
@@ -6049,45 +6049,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M58">
-        <v>3919.985274814096</v>
+        <v>5179.453384933259</v>
       </c>
       <c r="N58">
-        <v>1047.314725185904</v>
+        <v>-212.15338493326</v>
       </c>
       <c r="O58">
-        <v>261.8286812964759</v>
+        <v>-53.038346233315</v>
       </c>
       <c r="P58">
-        <v>785.4860438894277</v>
+        <v>-159.115038699945</v>
       </c>
       <c r="Q58">
-        <v>10290.48604388943</v>
+        <v>9345.884961300055</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09922135770560916</v>
+        <v>0.1006758152765464</v>
       </c>
       <c r="T58">
-        <v>1.041281694803131</v>
+        <v>1.069631780041151</v>
       </c>
       <c r="U58">
-        <v>0.0959366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V58">
-        <v>0.25</v>
+        <v>0.2397598564382102</v>
       </c>
       <c r="W58">
-        <v>0.07195246249690057</v>
+        <v>0.09467773533022451</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.267173127387723</v>
+        <v>0.9590394257528406</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09725690970714293</v>
+        <v>0.09804427587376829</v>
       </c>
       <c r="C59">
-        <v>14972.43215276071</v>
+        <v>13900.19788121415</v>
       </c>
       <c r="D59">
-        <v>47831.93540691848</v>
+        <v>47489.3468064975</v>
       </c>
       <c r="E59">
-        <v>-4878.563858399721</v>
+        <v>-4148.918187274139</v>
       </c>
       <c r="F59">
-        <v>41589.80325415777</v>
+        <v>42319.44892528335</v>
       </c>
       <c r="G59">
         <v>8730.299999999999</v>
@@ -6131,37 +6131,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M59">
-        <v>5179.453384933259</v>
+        <v>5270.320988177704</v>
       </c>
       <c r="N59">
-        <v>-212.15338493326</v>
+        <v>-303.0209881777046</v>
       </c>
       <c r="O59">
-        <v>-53.038346233315</v>
+        <v>-75.75524704442614</v>
       </c>
       <c r="P59">
-        <v>-159.115038699945</v>
+        <v>-227.2657411332784</v>
       </c>
       <c r="Q59">
-        <v>9345.884961300055</v>
+        <v>9277.734258866722</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1006758152765464</v>
+        <v>0.1019823823069404</v>
       </c>
       <c r="T59">
-        <v>1.069631780041151</v>
+        <v>1.095099203375465</v>
       </c>
       <c r="U59">
         <v>0.1245366166625341</v>
       </c>
       <c r="V59">
-        <v>0.2397598564382102</v>
+        <v>0.2356260658099651</v>
       </c>
       <c r="W59">
-        <v>0.09467773533022451</v>
+        <v>0.09519254362905745</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.9590394257528406</v>
+        <v>0.9425042632398604</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09804427587376828</v>
+        <v>0.09883164204039362</v>
       </c>
       <c r="C60">
-        <v>13900.19788121417</v>
+        <v>12832.83618294392</v>
       </c>
       <c r="D60">
-        <v>47489.3468064975</v>
+        <v>47151.63077935285</v>
       </c>
       <c r="E60">
-        <v>-4148.918187274154</v>
+        <v>-3419.272516148572</v>
       </c>
       <c r="F60">
-        <v>42319.44892528334</v>
+        <v>43049.09459640892</v>
       </c>
       <c r="G60">
         <v>8730.299999999999</v>
@@ -6213,37 +6213,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M60">
-        <v>5270.320988177702</v>
+        <v>5361.188591422146</v>
       </c>
       <c r="N60">
-        <v>-303.0209881777027</v>
+        <v>-393.8885914221464</v>
       </c>
       <c r="O60">
-        <v>-75.75524704442569</v>
+        <v>-98.4721478555366</v>
       </c>
       <c r="P60">
-        <v>-227.2657411332771</v>
+        <v>-295.4164435666098</v>
       </c>
       <c r="Q60">
-        <v>9277.734258866723</v>
+        <v>9209.58355643339</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1019823823069404</v>
+        <v>0.1033526843144267</v>
       </c>
       <c r="T60">
-        <v>1.095099203375465</v>
+        <v>1.121808940043159</v>
       </c>
       <c r="U60">
         <v>0.1245366166625341</v>
       </c>
       <c r="V60">
-        <v>0.2356260658099651</v>
+        <v>0.2316324036775929</v>
       </c>
       <c r="W60">
-        <v>0.09519254362905744</v>
+        <v>0.09568990079911636</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.9425042632398606</v>
+        <v>0.9265296147103714</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09883164204039362</v>
+        <v>0.09961900820701897</v>
       </c>
       <c r="C61">
-        <v>12832.83618294392</v>
+        <v>11770.24383943784</v>
       </c>
       <c r="D61">
-        <v>47151.63077935285</v>
+        <v>46818.68410697234</v>
       </c>
       <c r="E61">
-        <v>-3419.272516148572</v>
+        <v>-2689.626845022998</v>
       </c>
       <c r="F61">
-        <v>43049.09459640892</v>
+        <v>43778.74026753449</v>
       </c>
       <c r="G61">
         <v>8730.299999999999</v>
@@ -6295,37 +6295,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M61">
-        <v>5361.188591422146</v>
+        <v>5452.056194666588</v>
       </c>
       <c r="N61">
-        <v>-393.8885914221464</v>
+        <v>-484.7561946665892</v>
       </c>
       <c r="O61">
-        <v>-98.4721478555366</v>
+        <v>-121.1890486666473</v>
       </c>
       <c r="P61">
-        <v>-295.4164435666098</v>
+        <v>-363.5671459999419</v>
       </c>
       <c r="Q61">
-        <v>9209.58355643339</v>
+        <v>9141.432854000059</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1033526843144267</v>
+        <v>0.1047915014222874</v>
       </c>
       <c r="T61">
-        <v>1.121808940043159</v>
+        <v>1.149854163544238</v>
       </c>
       <c r="U61">
         <v>0.1245366166625341</v>
       </c>
       <c r="V61">
-        <v>0.2316324036775929</v>
+        <v>0.2277718636162996</v>
       </c>
       <c r="W61">
-        <v>0.09568990079911636</v>
+        <v>0.09617067939684</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.9265296147103714</v>
+        <v>0.9110874544651986</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09961900820701897</v>
+        <v>0.1004063743736443</v>
       </c>
       <c r="C62">
-        <v>11770.24383943784</v>
+        <v>10712.32052712454</v>
       </c>
       <c r="D62">
-        <v>46818.68410697234</v>
+        <v>46490.40646578461</v>
       </c>
       <c r="E62">
-        <v>-2689.626845022998</v>
+        <v>-1959.981173897424</v>
       </c>
       <c r="F62">
-        <v>43778.74026753449</v>
+        <v>44508.38593866007</v>
       </c>
       <c r="G62">
         <v>8730.299999999999</v>
@@ -6377,37 +6377,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M62">
-        <v>5452.056194666588</v>
+        <v>5542.923797911032</v>
       </c>
       <c r="N62">
-        <v>-484.7561946665892</v>
+        <v>-575.6237979110329</v>
       </c>
       <c r="O62">
-        <v>-121.1890486666473</v>
+        <v>-143.9059494777582</v>
       </c>
       <c r="P62">
-        <v>-363.5671459999419</v>
+        <v>-431.7178484332746</v>
       </c>
       <c r="Q62">
-        <v>9141.432854000059</v>
+        <v>9073.282151566726</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1047915014222874</v>
+        <v>0.1063041040228589</v>
       </c>
       <c r="T62">
-        <v>1.149854163544238</v>
+        <v>1.179337603635116</v>
       </c>
       <c r="U62">
         <v>0.1245366166625341</v>
       </c>
       <c r="V62">
-        <v>0.2277718636162996</v>
+        <v>0.2240378986389832</v>
       </c>
       <c r="W62">
-        <v>0.09617067939684</v>
+        <v>0.09663569476185137</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.9110874544651986</v>
+        <v>0.896151594555933</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1004063743736443</v>
+        <v>0.1011937405402696</v>
       </c>
       <c r="C63">
-        <v>10712.32052712454</v>
+        <v>9658.968716588148</v>
       </c>
       <c r="D63">
-        <v>46490.40646578461</v>
+        <v>46166.70032637379</v>
       </c>
       <c r="E63">
-        <v>-1959.981173897424</v>
+        <v>-1230.33550277185</v>
       </c>
       <c r="F63">
-        <v>44508.38593866007</v>
+        <v>45238.03160978564</v>
       </c>
       <c r="G63">
         <v>8730.299999999999</v>
@@ -6459,37 +6459,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M63">
-        <v>5542.923797911032</v>
+        <v>5633.791401155475</v>
       </c>
       <c r="N63">
-        <v>-575.6237979110329</v>
+        <v>-666.4914011554756</v>
       </c>
       <c r="O63">
-        <v>-143.9059494777582</v>
+        <v>-166.6228502888689</v>
       </c>
       <c r="P63">
-        <v>-431.7178484332746</v>
+        <v>-499.8685508666067</v>
       </c>
       <c r="Q63">
-        <v>9073.282151566726</v>
+        <v>9005.131449133394</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1063041040228589</v>
+        <v>0.1078963172866183</v>
       </c>
       <c r="T63">
-        <v>1.179337603635116</v>
+        <v>1.210372803730777</v>
       </c>
       <c r="U63">
         <v>0.1245366166625341</v>
       </c>
       <c r="V63">
-        <v>0.2240378986389832</v>
+        <v>0.2204243841448061</v>
       </c>
       <c r="W63">
-        <v>0.09663569476185137</v>
+        <v>0.09708570963121722</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.896151594555933</v>
+        <v>0.8816975365792245</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1011937405402696</v>
+        <v>0.101981106706895</v>
       </c>
       <c r="C64">
-        <v>9658.968716588148</v>
+        <v>8610.093575964362</v>
       </c>
       <c r="D64">
-        <v>46166.70032637379</v>
+        <v>45847.47085687557</v>
       </c>
       <c r="E64">
-        <v>-1230.33550277185</v>
+        <v>-500.6898316462757</v>
       </c>
       <c r="F64">
-        <v>45238.03160978564</v>
+        <v>45967.67728091122</v>
       </c>
       <c r="G64">
         <v>8730.299999999999</v>
@@ -6541,37 +6541,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M64">
-        <v>5633.791401155475</v>
+        <v>5724.659004399918</v>
       </c>
       <c r="N64">
-        <v>-666.4914011554756</v>
+        <v>-757.3590043999184</v>
       </c>
       <c r="O64">
-        <v>-166.6228502888689</v>
+        <v>-189.3397510999796</v>
       </c>
       <c r="P64">
-        <v>-499.8685508666067</v>
+        <v>-568.0192532999388</v>
       </c>
       <c r="Q64">
-        <v>9005.131449133394</v>
+        <v>8936.980746700061</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1078963172866183</v>
+        <v>0.1095745961322026</v>
       </c>
       <c r="T64">
-        <v>1.210372803730777</v>
+        <v>1.243085582209987</v>
       </c>
       <c r="U64">
         <v>0.1245366166625341</v>
       </c>
       <c r="V64">
-        <v>0.2204243841448061</v>
+        <v>0.2169255843964759</v>
       </c>
       <c r="W64">
-        <v>0.09708570963121722</v>
+        <v>0.09752143831425399</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8816975365792245</v>
+        <v>0.8677023375859034</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.101981106706895</v>
+        <v>0.1027684728735203</v>
       </c>
       <c r="C65">
-        <v>8610.093575964362</v>
+        <v>7565.602878316895</v>
       </c>
       <c r="D65">
-        <v>45847.47085687557</v>
+        <v>45532.62583035369</v>
       </c>
       <c r="E65">
-        <v>-500.6898316462757</v>
+        <v>228.9558394793057</v>
       </c>
       <c r="F65">
-        <v>45967.67728091122</v>
+        <v>46697.3229520368</v>
       </c>
       <c r="G65">
         <v>8730.299999999999</v>
@@ -6623,37 +6623,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M65">
-        <v>5724.659004399918</v>
+        <v>5815.526607644362</v>
       </c>
       <c r="N65">
-        <v>-757.3590043999184</v>
+        <v>-848.226607644363</v>
       </c>
       <c r="O65">
-        <v>-189.3397510999796</v>
+        <v>-212.0566519110907</v>
       </c>
       <c r="P65">
-        <v>-568.0192532999388</v>
+        <v>-636.1699557332722</v>
       </c>
       <c r="Q65">
-        <v>8936.980746700061</v>
+        <v>8868.830044266728</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1095745961322026</v>
+        <v>0.1113461126914305</v>
       </c>
       <c r="T65">
-        <v>1.243085582209987</v>
+        <v>1.277615737271375</v>
       </c>
       <c r="U65">
         <v>0.1245366166625341</v>
       </c>
       <c r="V65">
-        <v>0.2169255843964759</v>
+        <v>0.2135361221402809</v>
       </c>
       <c r="W65">
-        <v>0.09752143831425399</v>
+        <v>0.09794355047594588</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8677023375859034</v>
+        <v>0.8541444885611235</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1027684728735203</v>
+        <v>0.1035558390401457</v>
       </c>
       <c r="C66">
-        <v>7565.602878316895</v>
+        <v>6525.406912804458</v>
       </c>
       <c r="D66">
-        <v>45532.62583035369</v>
+        <v>45222.07553596683</v>
       </c>
       <c r="E66">
-        <v>228.9558394793057</v>
+        <v>958.6015106048799</v>
       </c>
       <c r="F66">
-        <v>46697.3229520368</v>
+        <v>47426.96862316237</v>
       </c>
       <c r="G66">
         <v>8730.299999999999</v>
@@ -6705,37 +6705,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M66">
-        <v>5815.526607644362</v>
+        <v>5906.394210888805</v>
       </c>
       <c r="N66">
-        <v>-848.226607644363</v>
+        <v>-939.0942108888057</v>
       </c>
       <c r="O66">
-        <v>-212.0566519110907</v>
+        <v>-234.7735527222014</v>
       </c>
       <c r="P66">
-        <v>-636.1699557332722</v>
+        <v>-704.3206581666043</v>
       </c>
       <c r="Q66">
-        <v>8868.830044266728</v>
+        <v>8800.679341833396</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1113461126914305</v>
+        <v>0.1132188587683285</v>
       </c>
       <c r="T66">
-        <v>1.277615737271375</v>
+        <v>1.314119044050558</v>
       </c>
       <c r="U66">
         <v>0.1245366166625341</v>
       </c>
       <c r="V66">
-        <v>0.2135361221402809</v>
+        <v>0.2102509510304304</v>
       </c>
       <c r="W66">
-        <v>0.09794355047594588</v>
+        <v>0.09835267457112415</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8541444885611235</v>
+        <v>0.8410038041217216</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1035558390401457</v>
+        <v>0.104343205206771</v>
       </c>
       <c r="C67">
-        <v>6525.406912804458</v>
+        <v>5489.418399458133</v>
       </c>
       <c r="D67">
-        <v>45222.07553596683</v>
+        <v>44915.73269374607</v>
       </c>
       <c r="E67">
-        <v>958.6015106048799</v>
+        <v>1688.247181730454</v>
       </c>
       <c r="F67">
-        <v>47426.96862316237</v>
+        <v>48156.61429428795</v>
       </c>
       <c r="G67">
         <v>8730.299999999999</v>
@@ -6787,37 +6787,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M67">
-        <v>5906.394210888805</v>
+        <v>5997.261814133248</v>
       </c>
       <c r="N67">
-        <v>-939.0942108888057</v>
+        <v>-1029.961814133248</v>
       </c>
       <c r="O67">
-        <v>-234.7735527222014</v>
+        <v>-257.4904535333121</v>
       </c>
       <c r="P67">
-        <v>-704.3206581666043</v>
+        <v>-772.4713605999364</v>
       </c>
       <c r="Q67">
-        <v>8800.679341833396</v>
+        <v>8732.528639400063</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1132188587683285</v>
+        <v>0.1152017663791617</v>
       </c>
       <c r="T67">
-        <v>1.314119044050558</v>
+        <v>1.352769604169692</v>
       </c>
       <c r="U67">
         <v>0.1245366166625341</v>
       </c>
       <c r="V67">
-        <v>0.2102509510304304</v>
+        <v>0.2070653305602724</v>
       </c>
       <c r="W67">
-        <v>0.09835267457112415</v>
+        <v>0.09874940096644856</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8410038041217216</v>
+        <v>0.8282613222410895</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.104343205206771</v>
+        <v>0.1051305713733963</v>
       </c>
       <c r="C68">
-        <v>5489.418399458133</v>
+        <v>4457.552407399526</v>
       </c>
       <c r="D68">
-        <v>44915.73269374607</v>
+        <v>44613.51237281304</v>
       </c>
       <c r="E68">
-        <v>1688.247181730454</v>
+        <v>2417.892852856028</v>
       </c>
       <c r="F68">
-        <v>48156.61429428795</v>
+        <v>48886.25996541352</v>
       </c>
       <c r="G68">
         <v>8730.299999999999</v>
@@ -6869,37 +6869,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M68">
-        <v>5997.261814133248</v>
+        <v>6088.129417377691</v>
       </c>
       <c r="N68">
-        <v>-1029.961814133248</v>
+        <v>-1120.829417377691</v>
       </c>
       <c r="O68">
-        <v>-257.4904535333121</v>
+        <v>-280.2073543444228</v>
       </c>
       <c r="P68">
-        <v>-772.4713605999364</v>
+        <v>-840.6220630332684</v>
       </c>
       <c r="Q68">
-        <v>8732.528639400063</v>
+        <v>8664.377936966732</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1152017663791617</v>
+        <v>0.1173048502088332</v>
       </c>
       <c r="T68">
-        <v>1.352769604169692</v>
+        <v>1.393762622477864</v>
       </c>
       <c r="U68">
         <v>0.1245366166625341</v>
       </c>
       <c r="V68">
-        <v>0.2070653305602724</v>
+        <v>0.2039748032384773</v>
       </c>
       <c r="W68">
-        <v>0.09874940096644856</v>
+        <v>0.09913428478280803</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8282613222410895</v>
+        <v>0.8158992129539091</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1051305713733963</v>
+        <v>0.1059179375400217</v>
       </c>
       <c r="C69">
-        <v>4457.552407399526</v>
+        <v>3429.726276338384</v>
       </c>
       <c r="D69">
-        <v>44613.51237281304</v>
+        <v>44315.33191287747</v>
       </c>
       <c r="E69">
-        <v>2417.892852856028</v>
+        <v>3147.538523981602</v>
       </c>
       <c r="F69">
-        <v>48886.25996541352</v>
+        <v>49615.90563653909</v>
       </c>
       <c r="G69">
         <v>8730.299999999999</v>
@@ -6951,37 +6951,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M69">
-        <v>6088.129417377691</v>
+        <v>6178.997020622134</v>
       </c>
       <c r="N69">
-        <v>-1120.829417377691</v>
+        <v>-1211.697020622135</v>
       </c>
       <c r="O69">
-        <v>-280.2073543444228</v>
+        <v>-302.9242551555337</v>
       </c>
       <c r="P69">
-        <v>-840.6220630332684</v>
+        <v>-908.7727654666012</v>
       </c>
       <c r="Q69">
-        <v>8664.377936966732</v>
+        <v>8596.227234533399</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1173048502088332</v>
+        <v>0.1195393767778593</v>
       </c>
       <c r="T69">
-        <v>1.393762622477864</v>
+        <v>1.437317704430298</v>
       </c>
       <c r="U69">
         <v>0.1245366166625341</v>
       </c>
       <c r="V69">
-        <v>0.2039748032384773</v>
+        <v>0.2009751737790879</v>
       </c>
       <c r="W69">
-        <v>0.09913428478280803</v>
+        <v>0.09950784848692165</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8158992129539091</v>
+        <v>0.8039006951163516</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1059179375400217</v>
+        <v>0.1649084693197916</v>
       </c>
       <c r="C70">
-        <v>3429.726276338384</v>
+        <v>-12086.40139016427</v>
       </c>
       <c r="D70">
-        <v>44315.33191287747</v>
+        <v>29528.8499175004</v>
       </c>
       <c r="E70">
-        <v>3147.538523981602</v>
+        <v>3877.184195107176</v>
       </c>
       <c r="F70">
-        <v>49615.90563653909</v>
+        <v>50345.55130766467</v>
       </c>
       <c r="G70">
         <v>8730.299999999999</v>
@@ -7033,45 +7033,45 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M70">
-        <v>6178.997020622134</v>
+        <v>10408.26894135661</v>
       </c>
       <c r="N70">
-        <v>-1211.697020622135</v>
+        <v>-5440.968941356614</v>
       </c>
       <c r="O70">
-        <v>-302.9242551555337</v>
+        <v>-1360.242235339153</v>
       </c>
       <c r="P70">
-        <v>-908.7727654666012</v>
+        <v>-4080.72670601746</v>
       </c>
       <c r="Q70">
-        <v>8596.227234533399</v>
+        <v>5424.27329398254</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1195393767778593</v>
+        <v>0.1267089231679339</v>
       </c>
       <c r="T70">
-        <v>1.437317704430298</v>
+        <v>1.577065508242531</v>
       </c>
       <c r="U70">
-        <v>0.1245366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.2009751737790879</v>
+        <v>0.1193113866481375</v>
       </c>
       <c r="W70">
-        <v>0.09950784848692165</v>
+        <v>0.1820705842575827</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.8039006951163516</v>
+        <v>0.47724554659255</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1649084693197916</v>
+        <v>0.1665178354864169</v>
       </c>
       <c r="C71">
-        <v>-12086.40139016427</v>
+        <v>-13082.42266904424</v>
       </c>
       <c r="D71">
-        <v>29528.8499175004</v>
+        <v>29262.47430974601</v>
       </c>
       <c r="E71">
-        <v>3877.184195107176</v>
+        <v>4606.829866232758</v>
       </c>
       <c r="F71">
-        <v>50345.55130766467</v>
+        <v>51075.19697879025</v>
       </c>
       <c r="G71">
         <v>8730.299999999999</v>
@@ -7115,37 +7115,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M71">
-        <v>10408.26894135661</v>
+        <v>10559.11341876758</v>
       </c>
       <c r="N71">
-        <v>-5440.968941356614</v>
+        <v>-5591.813418767581</v>
       </c>
       <c r="O71">
-        <v>-1360.242235339153</v>
+        <v>-1397.953354691895</v>
       </c>
       <c r="P71">
-        <v>-4080.72670601746</v>
+        <v>-4193.860064075685</v>
       </c>
       <c r="Q71">
-        <v>5424.27329398254</v>
+        <v>5311.139935924315</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1267089231679339</v>
+        <v>0.1294058872735317</v>
       </c>
       <c r="T71">
-        <v>1.577065508242531</v>
+        <v>1.629634358517282</v>
       </c>
       <c r="U71">
         <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.1193113866481375</v>
+        <v>0.1176069382674498</v>
       </c>
       <c r="W71">
-        <v>0.1820705842575827</v>
+        <v>0.182422956149082</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.47724554659255</v>
+        <v>0.4704277530697993</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1665178354864169</v>
+        <v>0.1681272016530423</v>
       </c>
       <c r="C72">
-        <v>-13082.42266904424</v>
+        <v>-14073.68103956184</v>
       </c>
       <c r="D72">
-        <v>29262.47430974601</v>
+        <v>29000.86161035398</v>
       </c>
       <c r="E72">
-        <v>4606.829866232758</v>
+        <v>5336.475537358332</v>
       </c>
       <c r="F72">
-        <v>51075.19697879025</v>
+        <v>51804.84264991582</v>
       </c>
       <c r="G72">
         <v>8730.299999999999</v>
@@ -7197,37 +7197,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M72">
-        <v>10559.11341876758</v>
+        <v>10709.95789617854</v>
       </c>
       <c r="N72">
-        <v>-5591.813418767581</v>
+        <v>-5742.657896178545</v>
       </c>
       <c r="O72">
-        <v>-1397.953354691895</v>
+        <v>-1435.664474044636</v>
       </c>
       <c r="P72">
-        <v>-4193.860064075685</v>
+        <v>-4306.993422133909</v>
       </c>
       <c r="Q72">
-        <v>5311.139935924315</v>
+        <v>5198.006577866091</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1294058872735317</v>
+        <v>0.1322888489036535</v>
       </c>
       <c r="T72">
-        <v>1.629634358517282</v>
+        <v>1.685828646742016</v>
       </c>
       <c r="U72">
         <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.1176069382674498</v>
+        <v>0.1159505025172041</v>
       </c>
       <c r="W72">
-        <v>0.182422956149082</v>
+        <v>0.1827654020718067</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4704277530697993</v>
+        <v>0.4638020100688163</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1681272016530423</v>
+        <v>0.1697365678196676</v>
       </c>
       <c r="C73">
-        <v>-14073.68103956183</v>
+        <v>-15060.30311399603</v>
       </c>
       <c r="D73">
-        <v>29000.86161035399</v>
+        <v>28743.88520704536</v>
       </c>
       <c r="E73">
-        <v>5336.475537358325</v>
+        <v>6066.121208483899</v>
       </c>
       <c r="F73">
-        <v>51804.84264991582</v>
+        <v>52534.48832104139</v>
       </c>
       <c r="G73">
         <v>8730.299999999999</v>
@@ -7279,37 +7279,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M73">
-        <v>10709.95789617854</v>
+        <v>10860.80237358951</v>
       </c>
       <c r="N73">
-        <v>-5742.657896178544</v>
+        <v>-5893.502373589508</v>
       </c>
       <c r="O73">
-        <v>-1435.664474044636</v>
+        <v>-1473.375593397377</v>
       </c>
       <c r="P73">
-        <v>-4306.993422133908</v>
+        <v>-4420.126780192131</v>
       </c>
       <c r="Q73">
-        <v>5198.006577866092</v>
+        <v>5084.873219807869</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1322888489036535</v>
+        <v>0.1353777363644983</v>
       </c>
       <c r="T73">
-        <v>1.685828646742015</v>
+        <v>1.746036812697087</v>
       </c>
       <c r="U73">
         <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.1159505025172041</v>
+        <v>0.1143400788711318</v>
       </c>
       <c r="W73">
-        <v>0.1827654020718067</v>
+        <v>0.183098335607789</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4638020100688163</v>
+        <v>0.4573603154845273</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1697365678196676</v>
+        <v>0.1713459339862929</v>
       </c>
       <c r="C74">
-        <v>-15060.30311399603</v>
+        <v>-16042.41105639993</v>
       </c>
       <c r="D74">
-        <v>28743.88520704536</v>
+        <v>28491.42293576703</v>
       </c>
       <c r="E74">
-        <v>6066.121208483899</v>
+        <v>6795.766879609473</v>
       </c>
       <c r="F74">
-        <v>52534.48832104139</v>
+        <v>53264.13399216696</v>
       </c>
       <c r="G74">
         <v>8730.299999999999</v>
@@ -7361,37 +7361,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M74">
-        <v>10860.80237358951</v>
+        <v>11011.64685100047</v>
       </c>
       <c r="N74">
-        <v>-5893.502373589508</v>
+        <v>-6044.346851000475</v>
       </c>
       <c r="O74">
-        <v>-1473.375593397377</v>
+        <v>-1511.086712750119</v>
       </c>
       <c r="P74">
-        <v>-4420.126780192131</v>
+        <v>-4533.260138250356</v>
       </c>
       <c r="Q74">
-        <v>5084.873219807869</v>
+        <v>4971.739861749644</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1353777363644983</v>
+        <v>0.1386954303039241</v>
       </c>
       <c r="T74">
-        <v>1.746036812697087</v>
+        <v>1.810704842796979</v>
       </c>
       <c r="U74">
         <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.1143400788711318</v>
+        <v>0.1127737764208423</v>
       </c>
       <c r="W74">
-        <v>0.183098335607789</v>
+        <v>0.1834221476770321</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4573603154845273</v>
+        <v>0.4510951056833693</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1713459339862929</v>
+        <v>0.1729553001529183</v>
       </c>
       <c r="C75">
-        <v>-16042.41105639993</v>
+        <v>-17020.12277624741</v>
       </c>
       <c r="D75">
-        <v>28491.42293576703</v>
+        <v>28243.35688704513</v>
       </c>
       <c r="E75">
-        <v>6795.766879609473</v>
+        <v>7525.412550735047</v>
       </c>
       <c r="F75">
-        <v>53264.13399216696</v>
+        <v>53993.77966329254</v>
       </c>
       <c r="G75">
         <v>8730.299999999999</v>
@@ -7443,37 +7443,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M75">
-        <v>11011.64685100047</v>
+        <v>11162.49132841144</v>
       </c>
       <c r="N75">
-        <v>-6044.346851000475</v>
+        <v>-6195.19132841144</v>
       </c>
       <c r="O75">
-        <v>-1511.086712750119</v>
+        <v>-1548.79783210286</v>
       </c>
       <c r="P75">
-        <v>-4533.260138250356</v>
+        <v>-4646.393496308579</v>
       </c>
       <c r="Q75">
-        <v>4971.739861749644</v>
+        <v>4858.606503691421</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1386954303039241</v>
+        <v>0.1422683314694597</v>
       </c>
       <c r="T75">
-        <v>1.810704842796979</v>
+        <v>1.880347336750709</v>
       </c>
       <c r="U75">
         <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.1127737764208423</v>
+        <v>0.1112498064692093</v>
       </c>
       <c r="W75">
-        <v>0.1834221476770321</v>
+        <v>0.1837372080687281</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4510951056833693</v>
+        <v>0.4449992258768373</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1729553001529183</v>
+        <v>0.1745646663195436</v>
       </c>
       <c r="C76">
-        <v>-17020.12277624741</v>
+        <v>-17993.55211205098</v>
       </c>
       <c r="D76">
-        <v>28243.35688704513</v>
+        <v>27999.57322236714</v>
       </c>
       <c r="E76">
-        <v>7525.412550735047</v>
+        <v>8255.058221860629</v>
       </c>
       <c r="F76">
-        <v>53993.77966329254</v>
+        <v>54723.42533441812</v>
       </c>
       <c r="G76">
         <v>8730.299999999999</v>
@@ -7525,37 +7525,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M76">
-        <v>11162.49132841144</v>
+        <v>11313.33580582241</v>
       </c>
       <c r="N76">
-        <v>-6195.19132841144</v>
+        <v>-6346.035805822406</v>
       </c>
       <c r="O76">
-        <v>-1548.79783210286</v>
+        <v>-1586.508951455602</v>
       </c>
       <c r="P76">
-        <v>-4646.393496308579</v>
+        <v>-4759.526854366804</v>
       </c>
       <c r="Q76">
-        <v>4858.606503691421</v>
+        <v>4745.473145633196</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1422683314694597</v>
+        <v>0.1461270647282381</v>
       </c>
       <c r="T76">
-        <v>1.880347336750709</v>
+        <v>1.955561230220738</v>
       </c>
       <c r="U76">
         <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.1112498064692093</v>
+        <v>0.1097664757162865</v>
       </c>
       <c r="W76">
-        <v>0.1837372080687281</v>
+        <v>0.1840438668499788</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4449992258768373</v>
+        <v>0.439065902865146</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1745646663195436</v>
+        <v>0.1761740324861689</v>
       </c>
       <c r="C77">
-        <v>-17993.55211205098</v>
+        <v>-18962.80900555163</v>
       </c>
       <c r="D77">
-        <v>27999.57322236714</v>
+        <v>27759.96199999207</v>
       </c>
       <c r="E77">
-        <v>8255.058221860629</v>
+        <v>8984.703892986203</v>
       </c>
       <c r="F77">
-        <v>54723.42533441812</v>
+        <v>55453.07100554369</v>
       </c>
       <c r="G77">
         <v>8730.299999999999</v>
@@ -7607,37 +7607,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M77">
-        <v>11313.33580582241</v>
+        <v>11464.18028323337</v>
       </c>
       <c r="N77">
-        <v>-6346.035805822406</v>
+        <v>-6496.880283233371</v>
       </c>
       <c r="O77">
-        <v>-1586.508951455602</v>
+        <v>-1624.220070808343</v>
       </c>
       <c r="P77">
-        <v>-4759.526854366804</v>
+        <v>-4872.660212425028</v>
       </c>
       <c r="Q77">
-        <v>4745.473145633196</v>
+        <v>4632.339787574972</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1461270647282381</v>
+        <v>0.1503073590919146</v>
       </c>
       <c r="T77">
-        <v>1.955561230220738</v>
+        <v>2.037042948146602</v>
       </c>
       <c r="U77">
         <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.1097664757162865</v>
+        <v>0.1083221799831775</v>
       </c>
       <c r="W77">
-        <v>0.1840438668499788</v>
+        <v>0.1843424556633019</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.439065902865146</v>
+        <v>0.4332887199327099</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1761740324861689</v>
+        <v>0.1777833986527943</v>
       </c>
       <c r="C78">
-        <v>-18962.80900555163</v>
+        <v>-19927.99966704048</v>
       </c>
       <c r="D78">
-        <v>27759.96199999207</v>
+        <v>27524.41700962879</v>
       </c>
       <c r="E78">
-        <v>8984.703892986203</v>
+        <v>9714.349564111777</v>
       </c>
       <c r="F78">
-        <v>55453.07100554369</v>
+        <v>56182.71667666927</v>
       </c>
       <c r="G78">
         <v>8730.299999999999</v>
@@ -7689,37 +7689,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M78">
-        <v>11464.18028323337</v>
+        <v>11615.02476064434</v>
       </c>
       <c r="N78">
-        <v>-6496.880283233371</v>
+        <v>-6647.724760644336</v>
       </c>
       <c r="O78">
-        <v>-1624.220070808343</v>
+        <v>-1661.931190161084</v>
       </c>
       <c r="P78">
-        <v>-4872.660212425028</v>
+        <v>-4985.793570483253</v>
       </c>
       <c r="Q78">
-        <v>4632.339787574972</v>
+        <v>4519.206429516747</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1503073590919146</v>
+        <v>0.1548511573133022</v>
       </c>
       <c r="T78">
-        <v>2.037042948146602</v>
+        <v>2.125610032848628</v>
       </c>
       <c r="U78">
         <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.1083221799831775</v>
+        <v>0.1069153984249544</v>
       </c>
       <c r="W78">
-        <v>0.1843424556633019</v>
+        <v>0.1846332889230322</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4332887199327099</v>
+        <v>0.4276615936998176</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1777833986527943</v>
+        <v>0.1793927648194197</v>
       </c>
       <c r="C79">
-        <v>-19927.99966704048</v>
+        <v>-20889.22673233481</v>
       </c>
       <c r="D79">
-        <v>27524.41700962879</v>
+        <v>27292.83561546003</v>
       </c>
       <c r="E79">
-        <v>9714.349564111777</v>
+        <v>10443.99523523735</v>
       </c>
       <c r="F79">
-        <v>56182.71667666927</v>
+        <v>56912.36234779484</v>
       </c>
       <c r="G79">
         <v>8730.299999999999</v>
@@ -7771,37 +7771,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M79">
-        <v>11615.02476064434</v>
+        <v>11765.8692380553</v>
       </c>
       <c r="N79">
-        <v>-6647.724760644336</v>
+        <v>-6798.569238055303</v>
       </c>
       <c r="O79">
-        <v>-1661.931190161084</v>
+        <v>-1699.642309513826</v>
       </c>
       <c r="P79">
-        <v>-4985.793570483253</v>
+        <v>-5098.926928541478</v>
       </c>
       <c r="Q79">
-        <v>4519.206429516747</v>
+        <v>4406.073071458522</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1548511573133022</v>
+        <v>0.1598080281002705</v>
       </c>
       <c r="T79">
-        <v>2.125610032848628</v>
+        <v>2.222228670705384</v>
       </c>
       <c r="U79">
         <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.1069153984249544</v>
+        <v>0.105544688188737</v>
       </c>
       <c r="W79">
-        <v>0.1846332889230322</v>
+        <v>0.1849166649196925</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4276615936998176</v>
+        <v>0.4221787527549481</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1793927648194197</v>
+        <v>0.181002130986045</v>
       </c>
       <c r="C80">
-        <v>-20889.22673233481</v>
+        <v>-21846.58941189566</v>
       </c>
       <c r="D80">
-        <v>27292.83561546003</v>
+        <v>27065.11860702475</v>
       </c>
       <c r="E80">
-        <v>10443.99523523735</v>
+        <v>11173.64090636293</v>
       </c>
       <c r="F80">
-        <v>56912.36234779484</v>
+        <v>57642.00801892042</v>
       </c>
       <c r="G80">
         <v>8730.299999999999</v>
@@ -7853,37 +7853,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M80">
-        <v>11765.8692380553</v>
+        <v>11916.71371546627</v>
       </c>
       <c r="N80">
-        <v>-6798.569238055303</v>
+        <v>-6949.413715466268</v>
       </c>
       <c r="O80">
-        <v>-1699.642309513826</v>
+        <v>-1737.353428866567</v>
       </c>
       <c r="P80">
-        <v>-5098.926928541478</v>
+        <v>-5212.060286599701</v>
       </c>
       <c r="Q80">
-        <v>4406.073071458522</v>
+        <v>4292.939713400299</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1598080281002705</v>
+        <v>0.165236981819331</v>
       </c>
       <c r="T80">
-        <v>2.222228670705384</v>
+        <v>2.328049083596117</v>
       </c>
       <c r="U80">
         <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.105544688188737</v>
+        <v>0.1042086794774872</v>
       </c>
       <c r="W80">
-        <v>0.1849166649196925</v>
+        <v>0.1851928668404879</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4221787527549481</v>
+        <v>0.4168347179099489</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.181002130986045</v>
+        <v>0.1826114971526703</v>
       </c>
       <c r="C81">
-        <v>-21846.58941189566</v>
+        <v>-22800.18363254223</v>
       </c>
       <c r="D81">
-        <v>27065.11860702475</v>
+        <v>26841.17005750376</v>
       </c>
       <c r="E81">
-        <v>11173.64090636293</v>
+        <v>11903.2865774885</v>
       </c>
       <c r="F81">
-        <v>57642.00801892042</v>
+        <v>58371.65369004599</v>
       </c>
       <c r="G81">
         <v>8730.299999999999</v>
@@ -7935,37 +7935,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M81">
-        <v>11916.71371546627</v>
+        <v>12067.55819287723</v>
       </c>
       <c r="N81">
-        <v>-6949.413715466268</v>
+        <v>-7100.258192877232</v>
       </c>
       <c r="O81">
-        <v>-1737.353428866567</v>
+        <v>-1775.064548219308</v>
       </c>
       <c r="P81">
-        <v>-5212.060286599701</v>
+        <v>-5325.193644657924</v>
       </c>
       <c r="Q81">
-        <v>4292.939713400299</v>
+        <v>4179.806355342076</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.165236981819331</v>
+        <v>0.1712088309102976</v>
       </c>
       <c r="T81">
-        <v>2.328049083596117</v>
+        <v>2.444451537775923</v>
       </c>
       <c r="U81">
         <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.1042086794774872</v>
+        <v>0.1029060709840186</v>
       </c>
       <c r="W81">
-        <v>0.1851928668404879</v>
+        <v>0.1854621637132635</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4168347179099489</v>
+        <v>0.4116242839360744</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1826114971526703</v>
+        <v>0.1842208633192957</v>
       </c>
       <c r="C82">
-        <v>-22800.18363254223</v>
+        <v>-23750.10217218843</v>
       </c>
       <c r="D82">
-        <v>26841.17005750376</v>
+        <v>26620.89718898314</v>
       </c>
       <c r="E82">
-        <v>11903.2865774885</v>
+        <v>12632.93224861408</v>
       </c>
       <c r="F82">
-        <v>58371.65369004599</v>
+        <v>59101.29936117157</v>
       </c>
       <c r="G82">
         <v>8730.299999999999</v>
@@ -8017,37 +8017,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M82">
-        <v>12067.55819287723</v>
+        <v>12218.4026702882</v>
       </c>
       <c r="N82">
-        <v>-7100.258192877232</v>
+        <v>-7251.102670288199</v>
       </c>
       <c r="O82">
-        <v>-1775.064548219308</v>
+        <v>-1812.77566757205</v>
       </c>
       <c r="P82">
-        <v>-5325.193644657924</v>
+        <v>-5438.327002716149</v>
       </c>
       <c r="Q82">
-        <v>4179.806355342076</v>
+        <v>4066.672997283851</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1712088309102976</v>
+        <v>0.1778092956950501</v>
       </c>
       <c r="T82">
-        <v>2.444451537775923</v>
+        <v>2.573106881869392</v>
       </c>
       <c r="U82">
         <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.1029060709840186</v>
+        <v>0.1016356256632283</v>
       </c>
       <c r="W82">
-        <v>0.1854621637132635</v>
+        <v>0.1857248112805385</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4116242839360744</v>
+        <v>0.406542502652913</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1842208633192957</v>
+        <v>0.185830229485921</v>
       </c>
       <c r="C83">
-        <v>-23750.10217218843</v>
+        <v>-24696.4347879991</v>
       </c>
       <c r="D83">
-        <v>26620.89718898314</v>
+        <v>26404.21024429805</v>
       </c>
       <c r="E83">
-        <v>12632.93224861408</v>
+        <v>13362.57791973966</v>
       </c>
       <c r="F83">
-        <v>59101.29936117157</v>
+        <v>59830.94503229715</v>
       </c>
       <c r="G83">
         <v>8730.299999999999</v>
@@ -8099,37 +8099,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M83">
-        <v>12218.4026702882</v>
+        <v>12369.24714769916</v>
       </c>
       <c r="N83">
-        <v>-7251.102670288199</v>
+        <v>-7401.947147699164</v>
       </c>
       <c r="O83">
-        <v>-1812.77566757205</v>
+        <v>-1850.486786924791</v>
       </c>
       <c r="P83">
-        <v>-5438.327002716149</v>
+        <v>-5551.460360774373</v>
       </c>
       <c r="Q83">
-        <v>4066.672997283851</v>
+        <v>3953.539639225627</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1778092956950501</v>
+        <v>0.1851431454558863</v>
       </c>
       <c r="T83">
-        <v>2.573106881869392</v>
+        <v>2.71605726419547</v>
       </c>
       <c r="U83">
         <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.1016356256632283</v>
+        <v>0.1003961668136767</v>
       </c>
       <c r="W83">
-        <v>0.1857248112805385</v>
+        <v>0.1859810528095872</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.406542502652913</v>
+        <v>0.4015846672547068</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.185830229485921</v>
+        <v>0.1874395956525464</v>
       </c>
       <c r="C84">
-        <v>-24696.4347879991</v>
+        <v>-25639.26833833775</v>
       </c>
       <c r="D84">
-        <v>26404.21024429805</v>
+        <v>26191.02236508497</v>
       </c>
       <c r="E84">
-        <v>13362.57791973966</v>
+        <v>14092.22359086523</v>
       </c>
       <c r="F84">
-        <v>59830.94503229715</v>
+        <v>60560.59070342272</v>
       </c>
       <c r="G84">
         <v>8730.299999999999</v>
@@ -8181,37 +8181,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M84">
-        <v>12369.24714769916</v>
+        <v>12520.09162511013</v>
       </c>
       <c r="N84">
-        <v>-7401.947147699164</v>
+        <v>-7552.791625110131</v>
       </c>
       <c r="O84">
-        <v>-1850.486786924791</v>
+        <v>-1888.197906277533</v>
       </c>
       <c r="P84">
-        <v>-5551.460360774373</v>
+        <v>-5664.593718832598</v>
       </c>
       <c r="Q84">
-        <v>3953.539639225627</v>
+        <v>3840.406281167402</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1851431454558863</v>
+        <v>0.1933398010709384</v>
       </c>
       <c r="T84">
-        <v>2.71605726419547</v>
+        <v>2.87582533855991</v>
       </c>
       <c r="U84">
         <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.1003961668136767</v>
+        <v>0.09918657444242757</v>
       </c>
       <c r="W84">
-        <v>0.1859810528095872</v>
+        <v>0.18623111984396</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4015846672547068</v>
+        <v>0.3967462977697103</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1874395956525464</v>
+        <v>0.1890489618191717</v>
       </c>
       <c r="C85">
-        <v>-25639.26833833775</v>
+        <v>-26578.68689885415</v>
       </c>
       <c r="D85">
-        <v>26191.02236508497</v>
+        <v>25981.24947569414</v>
       </c>
       <c r="E85">
-        <v>14092.22359086523</v>
+        <v>14821.8692619908</v>
       </c>
       <c r="F85">
-        <v>60560.59070342272</v>
+        <v>61290.23637454829</v>
       </c>
       <c r="G85">
         <v>8730.299999999999</v>
@@ -8263,37 +8263,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M85">
-        <v>12520.09162511013</v>
+        <v>12670.93610252109</v>
       </c>
       <c r="N85">
-        <v>-7552.791625110131</v>
+        <v>-7703.636102521095</v>
       </c>
       <c r="O85">
-        <v>-1888.197906277533</v>
+        <v>-1925.909025630274</v>
       </c>
       <c r="P85">
-        <v>-5664.593718832598</v>
+        <v>-5777.727076890822</v>
       </c>
       <c r="Q85">
-        <v>3840.406281167402</v>
+        <v>3727.272923109178</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1933398010709384</v>
+        <v>0.2025610386378721</v>
       </c>
       <c r="T85">
-        <v>2.87582533855991</v>
+        <v>3.055564422219904</v>
       </c>
       <c r="U85">
         <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.09918657444242757</v>
+        <v>0.09800578188954152</v>
       </c>
       <c r="W85">
-        <v>0.18623111984396</v>
+        <v>0.186475232901324</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3967462977697103</v>
+        <v>0.3920231275581662</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1890489618191717</v>
+        <v>0.190658327985797</v>
       </c>
       <c r="C86">
-        <v>-26578.68689885415</v>
+        <v>-27514.77187303732</v>
       </c>
       <c r="D86">
-        <v>25981.24947569414</v>
+        <v>25774.81017263655</v>
       </c>
       <c r="E86">
-        <v>14821.8692619908</v>
+        <v>15551.51493311637</v>
       </c>
       <c r="F86">
-        <v>61290.23637454829</v>
+        <v>62019.88204567386</v>
       </c>
       <c r="G86">
         <v>8730.299999999999</v>
@@ -8345,37 +8345,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M86">
-        <v>12670.93610252109</v>
+        <v>12821.78057993206</v>
       </c>
       <c r="N86">
-        <v>-7703.636102521094</v>
+        <v>-7854.480579932058</v>
       </c>
       <c r="O86">
-        <v>-1925.909025630273</v>
+        <v>-1963.620144983015</v>
       </c>
       <c r="P86">
-        <v>-5777.72707689082</v>
+        <v>-5890.860434949043</v>
       </c>
       <c r="Q86">
-        <v>3727.27292310918</v>
+        <v>3614.139565050957</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2025610386378719</v>
+        <v>0.2130117745470634</v>
       </c>
       <c r="T86">
-        <v>3.055564422219902</v>
+        <v>3.259268717034562</v>
       </c>
       <c r="U86">
         <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.09800578188954154</v>
+        <v>0.09685277269084105</v>
       </c>
       <c r="W86">
-        <v>0.186475232901324</v>
+        <v>0.1867136021220441</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3920231275581662</v>
+        <v>0.3874110907633642</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.190658327985797</v>
+        <v>0.1922676941524224</v>
       </c>
       <c r="C87">
-        <v>-27514.77187303732</v>
+        <v>-28447.60209753968</v>
       </c>
       <c r="D87">
-        <v>25774.81017263655</v>
+        <v>25571.62561925976</v>
       </c>
       <c r="E87">
-        <v>15551.51493311637</v>
+        <v>16281.16060424194</v>
       </c>
       <c r="F87">
-        <v>62019.88204567386</v>
+        <v>62749.52771679944</v>
       </c>
       <c r="G87">
         <v>8730.299999999999</v>
@@ -8427,37 +8427,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M87">
-        <v>12821.78057993206</v>
+        <v>12972.62505734302</v>
       </c>
       <c r="N87">
-        <v>-7854.480579932058</v>
+        <v>-8005.325057343023</v>
       </c>
       <c r="O87">
-        <v>-1963.620144983015</v>
+        <v>-2001.331264335756</v>
       </c>
       <c r="P87">
-        <v>-5890.860434949043</v>
+        <v>-6003.993793007267</v>
       </c>
       <c r="Q87">
-        <v>3614.139565050957</v>
+        <v>3501.006206992733</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2130117745470634</v>
+        <v>0.2249554727289965</v>
       </c>
       <c r="T87">
-        <v>3.259268717034562</v>
+        <v>3.492073625394174</v>
       </c>
       <c r="U87">
         <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.09685277269084105</v>
+        <v>0.09572657765955221</v>
       </c>
       <c r="W87">
-        <v>0.1867136021220441</v>
+        <v>0.1869464278725149</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3874110907633642</v>
+        <v>0.3829063106382089</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1922676941524224</v>
+        <v>0.1938770603190477</v>
       </c>
       <c r="C88">
-        <v>-28447.60209753968</v>
+        <v>-29377.25394255846</v>
       </c>
       <c r="D88">
-        <v>25571.62561925976</v>
+        <v>25371.61944536655</v>
       </c>
       <c r="E88">
-        <v>16281.16060424194</v>
+        <v>17010.80627536753</v>
       </c>
       <c r="F88">
-        <v>62749.52771679944</v>
+        <v>63479.17338792502</v>
       </c>
       <c r="G88">
         <v>8730.299999999999</v>
@@ -8509,37 +8509,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M88">
-        <v>12972.62505734302</v>
+        <v>13123.46953475399</v>
       </c>
       <c r="N88">
-        <v>-8005.325057343023</v>
+        <v>-8156.16953475399</v>
       </c>
       <c r="O88">
-        <v>-2001.331264335756</v>
+        <v>-2039.042383688497</v>
       </c>
       <c r="P88">
-        <v>-6003.993793007267</v>
+        <v>-6117.127151065492</v>
       </c>
       <c r="Q88">
-        <v>3501.006206992733</v>
+        <v>3387.872848934508</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2249554727289965</v>
+        <v>0.2387366629389193</v>
       </c>
       <c r="T88">
-        <v>3.492073625394174</v>
+        <v>3.760694673501418</v>
       </c>
       <c r="U88">
         <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.09572657765955221</v>
+        <v>0.09462627216921252</v>
       </c>
       <c r="W88">
-        <v>0.1869464278725149</v>
+        <v>0.187173901306883</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3829063106382089</v>
+        <v>0.3785050886768501</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1938770603190477</v>
+        <v>0.195486426485673</v>
       </c>
       <c r="C89">
-        <v>-29377.25394255846</v>
+        <v>-30303.80140754292</v>
       </c>
       <c r="D89">
-        <v>25371.61944536655</v>
+        <v>25174.71765150768</v>
       </c>
       <c r="E89">
-        <v>17010.80627536753</v>
+        <v>17740.4519464931</v>
       </c>
       <c r="F89">
-        <v>63479.17338792502</v>
+        <v>64208.81905905059</v>
       </c>
       <c r="G89">
         <v>8730.299999999999</v>
@@ -8591,37 +8591,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M89">
-        <v>13123.46953475399</v>
+        <v>13274.31401216496</v>
       </c>
       <c r="N89">
-        <v>-8156.16953475399</v>
+        <v>-8307.014012164957</v>
       </c>
       <c r="O89">
-        <v>-2039.042383688497</v>
+        <v>-2076.753503041239</v>
       </c>
       <c r="P89">
-        <v>-6117.127151065492</v>
+        <v>-6230.260509123717</v>
       </c>
       <c r="Q89">
-        <v>3387.872848934508</v>
+        <v>3274.739490876283</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2387366629389193</v>
+        <v>0.2548147181838293</v>
       </c>
       <c r="T89">
-        <v>3.760694673501418</v>
+        <v>4.074085896293204</v>
       </c>
       <c r="U89">
         <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.09462627216921252</v>
+        <v>0.09355097362183509</v>
       </c>
       <c r="W89">
-        <v>0.187173901306883</v>
+        <v>0.1873962048904699</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3785050886768501</v>
+        <v>0.3742038944873404</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.195486426485673</v>
+        <v>0.1970957926522984</v>
       </c>
       <c r="C90">
-        <v>-30303.80140754292</v>
+        <v>-31227.31621247932</v>
       </c>
       <c r="D90">
-        <v>25174.71765150768</v>
+        <v>24980.84851769684</v>
       </c>
       <c r="E90">
-        <v>17740.4519464931</v>
+        <v>18470.09761761867</v>
       </c>
       <c r="F90">
-        <v>64208.81905905059</v>
+        <v>64938.46473017617</v>
       </c>
       <c r="G90">
         <v>8730.299999999999</v>
@@ -8673,37 +8673,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M90">
-        <v>13274.31401216496</v>
+        <v>13425.15848957592</v>
       </c>
       <c r="N90">
-        <v>-8307.014012164957</v>
+        <v>-8457.858489575921</v>
       </c>
       <c r="O90">
-        <v>-2076.753503041239</v>
+        <v>-2114.46462239398</v>
       </c>
       <c r="P90">
-        <v>-6230.260509123717</v>
+        <v>-6343.393867181941</v>
       </c>
       <c r="Q90">
-        <v>3274.739490876283</v>
+        <v>3161.606132818059</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2548147181838293</v>
+        <v>0.2738160562005411</v>
       </c>
       <c r="T90">
-        <v>4.074085896293204</v>
+        <v>4.444457341410769</v>
       </c>
       <c r="U90">
         <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.09355097362183509</v>
+        <v>0.09249983908675831</v>
       </c>
       <c r="W90">
-        <v>0.1873962048904699</v>
+        <v>0.1876135128879089</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3742038944873404</v>
+        <v>0.3699993563470332</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1970957926522984</v>
+        <v>0.1987051588189237</v>
       </c>
       <c r="C91">
-        <v>-31227.31621247932</v>
+        <v>-32147.86788499037</v>
       </c>
       <c r="D91">
-        <v>24980.84851769684</v>
+        <v>24789.94251631138</v>
       </c>
       <c r="E91">
-        <v>18470.09761761867</v>
+        <v>19199.74328874426</v>
       </c>
       <c r="F91">
-        <v>64938.46473017617</v>
+        <v>65668.11040130175</v>
       </c>
       <c r="G91">
         <v>8730.299999999999</v>
@@ -8755,37 +8755,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M91">
-        <v>13425.15848957592</v>
+        <v>13576.00296698689</v>
       </c>
       <c r="N91">
-        <v>-8457.858489575921</v>
+        <v>-8608.702966986888</v>
       </c>
       <c r="O91">
-        <v>-2114.46462239398</v>
+        <v>-2152.175741746722</v>
       </c>
       <c r="P91">
-        <v>-6343.393867181941</v>
+        <v>-6456.527225240166</v>
       </c>
       <c r="Q91">
-        <v>3161.606132818059</v>
+        <v>3048.472774759834</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2738160562005411</v>
+        <v>0.2966176618205952</v>
       </c>
       <c r="T91">
-        <v>4.444457341410769</v>
+        <v>4.888903075551846</v>
       </c>
       <c r="U91">
         <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.09249983908675831</v>
+        <v>0.09147206309690542</v>
       </c>
       <c r="W91">
-        <v>0.1876135128879089</v>
+        <v>0.187825991818738</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3699993563470332</v>
+        <v>0.3658882523876217</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1987051588189237</v>
+        <v>0.2003145249855491</v>
       </c>
       <c r="C92">
-        <v>-32147.86788499037</v>
+        <v>-33065.52384347105</v>
       </c>
       <c r="D92">
-        <v>24789.94251631138</v>
+        <v>24601.93222895628</v>
       </c>
       <c r="E92">
-        <v>19199.74328874426</v>
+        <v>19929.38895986983</v>
       </c>
       <c r="F92">
-        <v>65668.11040130175</v>
+        <v>66397.75607242732</v>
       </c>
       <c r="G92">
         <v>8730.299999999999</v>
@@ -8837,37 +8837,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M92">
-        <v>13576.00296698689</v>
+        <v>13726.84744439785</v>
       </c>
       <c r="N92">
-        <v>-8608.702966986888</v>
+        <v>-8759.547444397853</v>
       </c>
       <c r="O92">
-        <v>-2152.175741746722</v>
+        <v>-2189.886861099463</v>
       </c>
       <c r="P92">
-        <v>-6456.527225240166</v>
+        <v>-6569.66058329839</v>
       </c>
       <c r="Q92">
-        <v>3048.472774759834</v>
+        <v>2935.33941670161</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2966176618205952</v>
+        <v>0.3244862909117724</v>
       </c>
       <c r="T92">
-        <v>4.888903075551846</v>
+        <v>5.432114528390939</v>
       </c>
       <c r="U92">
         <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.09147206309690542</v>
+        <v>0.09046687559034602</v>
       </c>
       <c r="W92">
-        <v>0.187825991818738</v>
+        <v>0.1880338008829556</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3658882523876217</v>
+        <v>0.3618675023613841</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2003145249855491</v>
+        <v>0.2019238911521744</v>
       </c>
       <c r="C93">
-        <v>-33065.52384347105</v>
+        <v>-33980.34947646994</v>
       </c>
       <c r="D93">
-        <v>24601.93222895628</v>
+        <v>24416.75226708296</v>
       </c>
       <c r="E93">
-        <v>19929.38895986983</v>
+        <v>20659.0346309954</v>
       </c>
       <c r="F93">
-        <v>66397.75607242732</v>
+        <v>67127.40174355289</v>
       </c>
       <c r="G93">
         <v>8730.299999999999</v>
@@ -8919,37 +8919,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M93">
-        <v>13726.84744439785</v>
+        <v>13877.69192180882</v>
       </c>
       <c r="N93">
-        <v>-8759.547444397853</v>
+        <v>-8910.391921808818</v>
       </c>
       <c r="O93">
-        <v>-2189.886861099463</v>
+        <v>-2227.597980452204</v>
       </c>
       <c r="P93">
-        <v>-6569.66058329839</v>
+        <v>-6682.793941356613</v>
       </c>
       <c r="Q93">
-        <v>2935.33941670161</v>
+        <v>2822.206058643387</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3244862909117724</v>
+        <v>0.3593220772757441</v>
       </c>
       <c r="T93">
-        <v>5.432114528390939</v>
+        <v>6.11112884443981</v>
       </c>
       <c r="U93">
         <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.09046687559034602</v>
+        <v>0.08948353998610314</v>
       </c>
       <c r="W93">
-        <v>0.1880338008829556</v>
+        <v>0.1882370923588206</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3618675023613841</v>
+        <v>0.3579341599444126</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2019238911521744</v>
+        <v>0.2035332573187998</v>
       </c>
       <c r="C94">
-        <v>-33980.34947646994</v>
+        <v>-34892.40821851234</v>
       </c>
       <c r="D94">
-        <v>24416.75226708296</v>
+        <v>24234.33919616613</v>
       </c>
       <c r="E94">
-        <v>20659.0346309954</v>
+        <v>21388.68030212098</v>
       </c>
       <c r="F94">
-        <v>67127.40174355289</v>
+        <v>67857.04741467847</v>
       </c>
       <c r="G94">
         <v>8730.299999999999</v>
@@ -9001,37 +9001,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M94">
-        <v>13877.69192180882</v>
+        <v>14028.53639921978</v>
       </c>
       <c r="N94">
-        <v>-8910.391921808818</v>
+        <v>-9061.236399219784</v>
       </c>
       <c r="O94">
-        <v>-2227.597980452204</v>
+        <v>-2265.309099804946</v>
       </c>
       <c r="P94">
-        <v>-6682.793941356613</v>
+        <v>-6795.927299414838</v>
       </c>
       <c r="Q94">
-        <v>2822.206058643387</v>
+        <v>2709.072700585162</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3593220772757441</v>
+        <v>0.4041109454579934</v>
       </c>
       <c r="T94">
-        <v>6.11112884443981</v>
+        <v>6.984147250788355</v>
       </c>
       <c r="U94">
         <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.08948353998610314</v>
+        <v>0.08852135138410203</v>
       </c>
       <c r="W94">
-        <v>0.1882370923588206</v>
+        <v>0.1884360119749895</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3579341599444126</v>
+        <v>0.3540854055364081</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2035332573187998</v>
+        <v>0.2051426234854251</v>
       </c>
       <c r="C95">
-        <v>-34892.40821851234</v>
+        <v>-35801.76162254963</v>
       </c>
       <c r="D95">
-        <v>24234.33919616613</v>
+        <v>24054.63146325441</v>
       </c>
       <c r="E95">
-        <v>21388.68030212098</v>
+        <v>22118.32597324655</v>
       </c>
       <c r="F95">
-        <v>67857.04741467847</v>
+        <v>68586.69308580404</v>
       </c>
       <c r="G95">
         <v>8730.299999999999</v>
@@ -9083,37 +9083,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M95">
-        <v>14028.53639921978</v>
+        <v>14179.38087663075</v>
       </c>
       <c r="N95">
-        <v>-9061.236399219784</v>
+        <v>-9212.080876630749</v>
       </c>
       <c r="O95">
-        <v>-2265.309099804946</v>
+        <v>-2303.020219157687</v>
       </c>
       <c r="P95">
-        <v>-6795.927299414838</v>
+        <v>-6909.060657473062</v>
       </c>
       <c r="Q95">
-        <v>2709.072700585162</v>
+        <v>2595.939342526938</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4041109454579934</v>
+        <v>0.463829436367659</v>
       </c>
       <c r="T95">
-        <v>6.984147250788355</v>
+        <v>8.148171792586416</v>
       </c>
       <c r="U95">
         <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.08852135138410203</v>
+        <v>0.08757963488001584</v>
       </c>
       <c r="W95">
-        <v>0.1884360119749895</v>
+        <v>0.1886306992588996</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3540854055364081</v>
+        <v>0.3503185395200633</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2051426234854251</v>
+        <v>0.2067519896520504</v>
       </c>
       <c r="C96">
-        <v>-35801.76162254963</v>
+        <v>-36708.46942920914</v>
       </c>
       <c r="D96">
-        <v>24054.63146325441</v>
+        <v>23877.56932772047</v>
       </c>
       <c r="E96">
-        <v>22118.32597324655</v>
+        <v>22847.97164437213</v>
       </c>
       <c r="F96">
-        <v>68586.69308580404</v>
+        <v>69316.33875692962</v>
       </c>
       <c r="G96">
         <v>8730.299999999999</v>
@@ -9165,37 +9165,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M96">
-        <v>14179.38087663075</v>
+        <v>14330.22535404171</v>
       </c>
       <c r="N96">
-        <v>-9212.080876630749</v>
+        <v>-9362.925354041714</v>
       </c>
       <c r="O96">
-        <v>-2303.020219157687</v>
+        <v>-2340.731338510428</v>
       </c>
       <c r="P96">
-        <v>-6909.060657473062</v>
+        <v>-7022.194015531286</v>
       </c>
       <c r="Q96">
-        <v>2595.939342526938</v>
+        <v>2482.805984468714</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.463829436367659</v>
+        <v>0.5474353236411909</v>
       </c>
       <c r="T96">
-        <v>8.148171792586416</v>
+        <v>9.777806151103702</v>
       </c>
       <c r="U96">
         <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.08757963488001584</v>
+        <v>0.08665774398654198</v>
       </c>
       <c r="W96">
-        <v>0.1886306992588996</v>
+        <v>0.1888212878631483</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3503185395200633</v>
+        <v>0.346630975946168</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2067519896520504</v>
+        <v>0.2083613558186758</v>
       </c>
       <c r="C97">
-        <v>-36708.46942920914</v>
+        <v>-37612.5896330078</v>
       </c>
       <c r="D97">
-        <v>23877.56932772047</v>
+        <v>23703.0947950474</v>
       </c>
       <c r="E97">
-        <v>22847.97164437213</v>
+        <v>23577.6173154977</v>
       </c>
       <c r="F97">
-        <v>69316.33875692962</v>
+        <v>70045.98442805519</v>
       </c>
       <c r="G97">
         <v>8730.299999999999</v>
@@ -9247,37 +9247,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M97">
-        <v>14330.22535404171</v>
+        <v>14481.06983145268</v>
       </c>
       <c r="N97">
-        <v>-9362.925354041714</v>
+        <v>-9513.769831452679</v>
       </c>
       <c r="O97">
-        <v>-2340.731338510428</v>
+        <v>-2378.44245786317</v>
       </c>
       <c r="P97">
-        <v>-7022.194015531286</v>
+        <v>-7135.327373589509</v>
       </c>
       <c r="Q97">
-        <v>2482.805984468714</v>
+        <v>2369.672626410491</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5474353236411909</v>
+        <v>0.6728441545514889</v>
       </c>
       <c r="T97">
-        <v>9.777806151103702</v>
+        <v>12.22225768887963</v>
       </c>
       <c r="U97">
         <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.08665774398654198</v>
+        <v>0.08575505915334884</v>
       </c>
       <c r="W97">
-        <v>0.1888212878631483</v>
+        <v>0.1890079058714753</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.346630975946168</v>
+        <v>0.3430202366133954</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2083613558186758</v>
+        <v>0.2099707219853011</v>
       </c>
       <c r="C98">
-        <v>-37612.5896330078</v>
+        <v>-38514.17854568391</v>
       </c>
       <c r="D98">
-        <v>23703.0947950474</v>
+        <v>23531.15155349686</v>
       </c>
       <c r="E98">
-        <v>23577.6173154977</v>
+        <v>24307.26298662327</v>
       </c>
       <c r="F98">
-        <v>70045.98442805519</v>
+        <v>70775.63009918077</v>
       </c>
       <c r="G98">
         <v>8730.299999999999</v>
@@ -9329,37 +9329,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M98">
-        <v>14481.06983145268</v>
+        <v>14631.91430886364</v>
       </c>
       <c r="N98">
-        <v>-9513.769831452679</v>
+        <v>-9664.614308863645</v>
       </c>
       <c r="O98">
-        <v>-2378.44245786317</v>
+        <v>-2416.153577215911</v>
       </c>
       <c r="P98">
-        <v>-7135.327373589509</v>
+        <v>-7248.460731647734</v>
       </c>
       <c r="Q98">
-        <v>2369.672626410491</v>
+        <v>2256.539268352266</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6728441545514873</v>
+        <v>0.8818588727353165</v>
       </c>
       <c r="T98">
-        <v>12.2222576888796</v>
+        <v>16.2963435851728</v>
       </c>
       <c r="U98">
         <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.08575505915334884</v>
+        <v>0.08487098637857204</v>
       </c>
       <c r="W98">
-        <v>0.1890079058714753</v>
+        <v>0.1891906760858161</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3430202366133954</v>
+        <v>0.3394839455142882</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2099707219853011</v>
+        <v>0.2115800881519265</v>
       </c>
       <c r="C99">
-        <v>-38514.17854568391</v>
+        <v>-39413.29085679233</v>
       </c>
       <c r="D99">
-        <v>23531.15155349686</v>
+        <v>23361.68491351401</v>
       </c>
       <c r="E99">
-        <v>24307.26298662327</v>
+        <v>25036.90865774885</v>
       </c>
       <c r="F99">
-        <v>70775.63009918077</v>
+        <v>71505.27577030634</v>
       </c>
       <c r="G99">
         <v>8730.299999999999</v>
@@ -9411,37 +9411,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M99">
-        <v>14631.91430886364</v>
+        <v>14782.75878627461</v>
       </c>
       <c r="N99">
-        <v>-9664.614308863645</v>
+        <v>-9815.45878627461</v>
       </c>
       <c r="O99">
-        <v>-2416.153577215911</v>
+        <v>-2453.864696568653</v>
       </c>
       <c r="P99">
-        <v>-7248.460731647734</v>
+        <v>-7361.594089705957</v>
       </c>
       <c r="Q99">
-        <v>2256.539268352266</v>
+        <v>2143.405910294043</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8818588727353165</v>
+        <v>1.299888309102975</v>
       </c>
       <c r="T99">
-        <v>16.2963435851728</v>
+        <v>24.4445153777592</v>
       </c>
       <c r="U99">
         <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.08487098637857204</v>
+        <v>0.08400495590532131</v>
       </c>
       <c r="W99">
-        <v>0.1891906760858161</v>
+        <v>0.1893697162957826</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3394839455142882</v>
+        <v>0.3360198236212852</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2115800881519265</v>
+        <v>0.2131894543185518</v>
       </c>
       <c r="C100">
-        <v>-39413.29085679233</v>
+        <v>-40309.97969170005</v>
       </c>
       <c r="D100">
-        <v>23361.68491351401</v>
+        <v>23194.64174973187</v>
       </c>
       <c r="E100">
-        <v>25036.90865774885</v>
+        <v>25766.55432887442</v>
       </c>
       <c r="F100">
-        <v>71505.27577030634</v>
+        <v>72234.92144143191</v>
       </c>
       <c r="G100">
         <v>8730.299999999999</v>
@@ -9493,37 +9493,37 @@
         <v>4967.299999999999</v>
       </c>
       <c r="M100">
-        <v>14782.75878627461</v>
+        <v>14933.60326368557</v>
       </c>
       <c r="N100">
-        <v>-9815.45878627461</v>
+        <v>-9966.303263685575</v>
       </c>
       <c r="O100">
-        <v>-2453.864696568653</v>
+        <v>-2491.575815921394</v>
       </c>
       <c r="P100">
-        <v>-7361.594089705957</v>
+        <v>-7474.727447764181</v>
       </c>
       <c r="Q100">
-        <v>2143.405910294043</v>
+        <v>2030.272552235819</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.299888309102975</v>
+        <v>2.553976618205949</v>
       </c>
       <c r="T100">
-        <v>24.4445153777592</v>
+        <v>48.8890307555184</v>
       </c>
       <c r="U100">
         <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.08400495590532131</v>
+        <v>0.08315642099718676</v>
       </c>
       <c r="W100">
-        <v>0.1893697162957826</v>
+        <v>0.1895451395318104</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3360198236212852</v>
+        <v>0.332625683988747</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2131894543185518</v>
-      </c>
-      <c r="C101">
-        <v>-40309.97969170005</v>
-      </c>
-      <c r="D101">
-        <v>23194.64174973187</v>
-      </c>
-      <c r="E101">
-        <v>25766.55432887442</v>
-      </c>
-      <c r="F101">
-        <v>72234.92144143191</v>
-      </c>
-      <c r="G101">
-        <v>8730.299999999999</v>
-      </c>
-      <c r="H101">
-        <v>26496.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>14472.3</v>
-      </c>
-      <c r="K101">
-        <v>9505</v>
-      </c>
-      <c r="L101">
-        <v>4967.299999999999</v>
-      </c>
-      <c r="M101">
-        <v>14933.60326368557</v>
-      </c>
-      <c r="N101">
-        <v>-9966.303263685575</v>
-      </c>
-      <c r="O101">
-        <v>-2491.575815921394</v>
-      </c>
-      <c r="P101">
-        <v>-7474.727447764181</v>
-      </c>
-      <c r="Q101">
-        <v>2030.272552235819</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.553976618205949</v>
-      </c>
-      <c r="T101">
-        <v>48.8890307555184</v>
-      </c>
-      <c r="U101">
-        <v>0.2067366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.08315642099718676</v>
-      </c>
-      <c r="W101">
-        <v>0.1895451395318104</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.332625683988747</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
